--- a/data/rateBuildUp/File1/RPT_RPT5713512752455CZ_rateBuildUp.xlsx
+++ b/data/rateBuildUp/File1/RPT_RPT5713512752455CZ_rateBuildUp.xlsx
@@ -2964,13 +2964,13 @@
         <v>24089.16055757216</v>
       </c>
       <c r="F11" s="368" t="n">
-        <v>22910.89281965234</v>
+        <v>22910.89281965233</v>
       </c>
       <c r="G11" s="370" t="n">
         <v>22576.04277835388</v>
       </c>
       <c r="H11" s="371" t="n">
-        <v>7.761100220022191</v>
+        <v>7.761100220022192</v>
       </c>
       <c r="I11" s="372" t="n">
         <v>2.931419663211911</v>
@@ -2979,13 +2979,13 @@
         <v>2.514564832336909</v>
       </c>
       <c r="K11" s="372" t="n">
-        <v>2.001503637594364</v>
+        <v>2.001503637594363</v>
       </c>
       <c r="L11" s="373" t="n">
         <v>1.647935614197367</v>
       </c>
       <c r="M11" s="371" t="n">
-        <v>7.723846962299836</v>
+        <v>7.723846962299837</v>
       </c>
       <c r="N11" s="372" t="n">
         <v>2.911509283748617</v>
@@ -2994,7 +2994,7 @@
         <v>2.489159532177251</v>
       </c>
       <c r="P11" s="372" t="n">
-        <v>1.981659250849849</v>
+        <v>1.981659250849848</v>
       </c>
       <c r="Q11" s="373" t="n">
         <v>1.63262170296351</v>
@@ -3014,13 +3014,13 @@
         <v>24089.16055757216</v>
       </c>
       <c r="W11" s="375" t="n">
-        <v>22910.89281965234</v>
+        <v>22910.89281965233</v>
       </c>
       <c r="X11" s="376" t="n">
         <v>22576.04277835388</v>
       </c>
       <c r="Y11" s="377" t="n">
-        <v>7.761100220022191</v>
+        <v>7.761100220022192</v>
       </c>
       <c r="Z11" s="372" t="n">
         <v>2.931419663211911</v>
@@ -3029,13 +3029,13 @@
         <v>2.514564832336909</v>
       </c>
       <c r="AB11" s="372" t="n">
-        <v>2.001503637594364</v>
+        <v>2.001503637594363</v>
       </c>
       <c r="AC11" s="378" t="n">
         <v>1.647935614197367</v>
       </c>
       <c r="AD11" s="377" t="n">
-        <v>7.723846962299836</v>
+        <v>7.723846962299837</v>
       </c>
       <c r="AE11" s="372" t="n">
         <v>2.911509283748617</v>
@@ -3044,7 +3044,7 @@
         <v>2.489159532177251</v>
       </c>
       <c r="AG11" s="372" t="n">
-        <v>1.981659250849849</v>
+        <v>1.981659250849848</v>
       </c>
       <c r="AH11" s="378" t="n">
         <v>1.63262170296351</v>
@@ -3064,7 +3064,7 @@
         <v>24089.16055757216</v>
       </c>
       <c r="AN11" s="368" t="n">
-        <v>22910.89281965234</v>
+        <v>22910.89281965233</v>
       </c>
       <c r="AO11" s="380" t="n">
         <v>22576.04277835388</v>
@@ -3079,7 +3079,7 @@
         <v>10.71013651140517</v>
       </c>
       <c r="AS11" s="372" t="n">
-        <v>8.63109151199057</v>
+        <v>8.631091511990569</v>
       </c>
       <c r="AT11" s="382" t="n">
         <v>7.16987807277479</v>
@@ -3094,7 +3094,7 @@
         <v>10.26394816952058</v>
       </c>
       <c r="AX11" s="372" t="n">
-        <v>8.27379971493869</v>
+        <v>8.273799714938688</v>
       </c>
       <c r="AY11" s="382" t="n">
         <v>6.888744838814787</v>
@@ -3132,7 +3132,7 @@
         <v>9.798754511136686</v>
       </c>
       <c r="BK11" s="387" t="n">
-        <v>8.344508632115225</v>
+        <v>8.344508632115227</v>
       </c>
       <c r="BL11" s="388" t="n">
         <v>28.5843924318418</v>
@@ -3155,64 +3155,64 @@
         </is>
       </c>
       <c r="BS11" s="391" t="n">
-        <v>26198.6081714332</v>
+        <v>26198.60817143319</v>
       </c>
       <c r="BT11" s="375" t="n">
-        <v>24909.12870060275</v>
+        <v>24909.12870060274</v>
       </c>
       <c r="BU11" s="375" t="n">
-        <v>26539.93282039779</v>
+        <v>26539.93282039778</v>
       </c>
       <c r="BV11" s="375" t="n">
-        <v>25920.71737475279</v>
+        <v>25920.71737475278</v>
       </c>
       <c r="BW11" s="392" t="n">
-        <v>26207.86114920854</v>
+        <v>26207.86114920853</v>
       </c>
       <c r="BX11" s="386" t="n">
-        <v>29.06346128541952</v>
+        <v>29.06346128541951</v>
       </c>
       <c r="BY11" s="372" t="n">
         <v>12.93325813107621</v>
       </c>
       <c r="BZ11" s="372" t="n">
-        <v>11.75360713701505</v>
+        <v>11.75360713701504</v>
       </c>
       <c r="CA11" s="372" t="n">
-        <v>9.716298370749909</v>
+        <v>9.716298370749906</v>
       </c>
       <c r="CB11" s="387" t="n">
-        <v>8.273045295813482</v>
+        <v>8.27304529581348</v>
       </c>
       <c r="CC11" s="388" t="n">
-        <v>28.62013109797842</v>
+        <v>28.62013109797841</v>
       </c>
       <c r="CD11" s="389" t="n">
-        <v>12.61536042613422</v>
+        <v>12.61536042613421</v>
       </c>
       <c r="CE11" s="389" t="n">
         <v>11.31085694480147</v>
       </c>
       <c r="CF11" s="389" t="n">
-        <v>9.362594739250378</v>
+        <v>9.362594739250374</v>
       </c>
       <c r="CG11" s="390" t="n">
-        <v>7.99824980305196</v>
+        <v>7.998249803051958</v>
       </c>
       <c r="CW11" s="91" t="n">
-        <v>0.01960206557254196</v>
+        <v>0.01960206557255262</v>
       </c>
       <c r="CX11" s="92" t="n">
-        <v>0.1034158876016509</v>
+        <v>0.1034158876016562</v>
       </c>
       <c r="CY11" s="92" t="n">
-        <v>0.09322766312648412</v>
+        <v>0.09322766312648945</v>
       </c>
       <c r="CZ11" s="92" t="n">
-        <v>0.08245614038677651</v>
+        <v>0.08245614038678006</v>
       </c>
       <c r="DA11" s="93" t="n">
-        <v>0.0714633363017434</v>
+        <v>0.07146333630174695</v>
       </c>
       <c r="DC11" s="393" t="n">
         <v>0.007228790260420208</v>
@@ -3224,10 +3224,10 @@
         <v>0.007522316429608733</v>
       </c>
       <c r="DF11" s="394" t="n">
-        <v>0.008028176757755748</v>
+        <v>0.00802817675775575</v>
       </c>
       <c r="DG11" s="395" t="n">
-        <v>0.008141014872206944</v>
+        <v>0.008141014872206942</v>
       </c>
     </row>
     <row r="12">
@@ -3258,7 +3258,7 @@
         <v>48.60506797411139</v>
       </c>
       <c r="J12" s="372" t="n">
-        <v>48.43431448055417</v>
+        <v>48.43431448055416</v>
       </c>
       <c r="K12" s="372" t="n">
         <v>47.1858589007192</v>
@@ -3279,7 +3279,7 @@
         <v>41.80661445744698</v>
       </c>
       <c r="Q12" s="373" t="n">
-        <v>39.07415789224061</v>
+        <v>39.07415789224062</v>
       </c>
       <c r="S12" s="99" t="inlineStr">
         <is>
@@ -3308,7 +3308,7 @@
         <v>48.60506797411139</v>
       </c>
       <c r="AA12" s="372" t="n">
-        <v>48.43431448055417</v>
+        <v>48.43431448055416</v>
       </c>
       <c r="AB12" s="372" t="n">
         <v>47.1858589007192</v>
@@ -3329,7 +3329,7 @@
         <v>41.80661445744698</v>
       </c>
       <c r="AH12" s="378" t="n">
-        <v>39.07415789224061</v>
+        <v>39.07415789224062</v>
       </c>
       <c r="AJ12" s="100" t="inlineStr">
         <is>
@@ -3358,7 +3358,7 @@
         <v>117.5849669349315</v>
       </c>
       <c r="AR12" s="372" t="n">
-        <v>130.6718745273438</v>
+        <v>130.6718745273437</v>
       </c>
       <c r="AS12" s="372" t="n">
         <v>135.183613510871</v>
@@ -3373,13 +3373,13 @@
         <v>91.68070187940798</v>
       </c>
       <c r="AW12" s="372" t="n">
-        <v>94.54366504470521</v>
+        <v>94.54366504470519</v>
       </c>
       <c r="AX12" s="372" t="n">
         <v>97.61824166146388</v>
       </c>
       <c r="AY12" s="382" t="n">
-        <v>95.95531583833851</v>
+        <v>95.95531583833852</v>
       </c>
       <c r="BA12" s="101" t="inlineStr">
         <is>
@@ -3399,7 +3399,7 @@
         <v>29559.11465242037</v>
       </c>
       <c r="BF12" s="385" t="n">
-        <v>32791.7293542301</v>
+        <v>32791.72935423009</v>
       </c>
       <c r="BG12" s="386" t="n">
         <v>147.6625874216905</v>
@@ -3414,7 +3414,7 @@
         <v>152.7417600362848</v>
       </c>
       <c r="BK12" s="387" t="n">
-        <v>152.457581469484</v>
+        <v>152.4575814694839</v>
       </c>
       <c r="BL12" s="386" t="n">
         <v>125.1692943803673</v>
@@ -3449,7 +3449,7 @@
         <v>29667.1745980313</v>
       </c>
       <c r="BW12" s="392" t="n">
-        <v>32976.10897116543</v>
+        <v>32976.10897116541</v>
       </c>
       <c r="BX12" s="386" t="n">
         <v>147.523880579784</v>
@@ -3464,7 +3464,7 @@
         <v>152.3124872651066</v>
       </c>
       <c r="CB12" s="387" t="n">
-        <v>152.1157564838712</v>
+        <v>152.1157564838711</v>
       </c>
       <c r="CC12" s="386" t="n">
         <v>125.2960999358579</v>
@@ -3482,19 +3482,19 @@
         <v>111.840659449201</v>
       </c>
       <c r="CW12" s="102" t="n">
-        <v>0.1387068419064974</v>
+        <v>0.1387068419065258</v>
       </c>
       <c r="CX12" s="103" t="n">
         <v>0.3881823835003502</v>
       </c>
       <c r="CY12" s="103" t="n">
-        <v>0.4216943228359753</v>
+        <v>0.4216943228360037</v>
       </c>
       <c r="CZ12" s="103" t="n">
         <v>0.4292727711782618</v>
       </c>
       <c r="DA12" s="104" t="n">
-        <v>0.3418249856127602</v>
+        <v>0.3418249856127886</v>
       </c>
       <c r="DC12" s="396" t="n">
         <v>0.002321834056615353</v>
@@ -3503,7 +3503,7 @@
         <v>0.002251743842844422</v>
       </c>
       <c r="DE12" s="397" t="n">
-        <v>0.002098746103403243</v>
+        <v>0.002098746103403244</v>
       </c>
       <c r="DF12" s="397" t="n">
         <v>0.001947812748621549</v>
@@ -3519,7 +3519,7 @@
         </is>
       </c>
       <c r="C13" s="369" t="n">
-        <v>39440.70190063954</v>
+        <v>39440.70190063955</v>
       </c>
       <c r="D13" s="368" t="n">
         <v>43593.55950295802</v>
@@ -3531,7 +3531,7 @@
         <v>59687.99695787529</v>
       </c>
       <c r="G13" s="370" t="n">
-        <v>64429.26290344836</v>
+        <v>64429.26290344837</v>
       </c>
       <c r="H13" s="371" t="n">
         <v>163.8007665957055</v>
@@ -3546,7 +3546,7 @@
         <v>103.1425517002979</v>
       </c>
       <c r="L13" s="373" t="n">
-        <v>95.37324288713465</v>
+        <v>95.37324288713467</v>
       </c>
       <c r="M13" s="371" t="n">
         <v>153.2686370389475</v>
@@ -3558,10 +3558,10 @@
         <v>93.01800358039037</v>
       </c>
       <c r="P13" s="372" t="n">
-        <v>93.88451418630078</v>
+        <v>93.88451418630076</v>
       </c>
       <c r="Q13" s="373" t="n">
-        <v>86.61450650418847</v>
+        <v>86.61450650418848</v>
       </c>
       <c r="S13" s="109" t="inlineStr">
         <is>
@@ -3569,7 +3569,7 @@
         </is>
       </c>
       <c r="T13" s="374" t="n">
-        <v>39440.70190063954</v>
+        <v>39440.70190063955</v>
       </c>
       <c r="U13" s="375" t="n">
         <v>43593.55950295802</v>
@@ -3581,7 +3581,7 @@
         <v>59687.99695787529</v>
       </c>
       <c r="X13" s="376" t="n">
-        <v>64429.26290344836</v>
+        <v>64429.26290344837</v>
       </c>
       <c r="Y13" s="377" t="n">
         <v>163.8007665957055</v>
@@ -3596,7 +3596,7 @@
         <v>103.1425517002979</v>
       </c>
       <c r="AC13" s="378" t="n">
-        <v>95.37324288713465</v>
+        <v>95.37324288713467</v>
       </c>
       <c r="AD13" s="377" t="n">
         <v>153.2686370389475</v>
@@ -3608,10 +3608,10 @@
         <v>93.01800358039037</v>
       </c>
       <c r="AG13" s="372" t="n">
-        <v>93.88451418630078</v>
+        <v>93.88451418630076</v>
       </c>
       <c r="AH13" s="378" t="n">
-        <v>86.61450650418847</v>
+        <v>86.61450650418848</v>
       </c>
       <c r="AJ13" s="110" t="inlineStr">
         <is>
@@ -3625,7 +3625,7 @@
         <v>43976.3503288433</v>
       </c>
       <c r="AM13" s="368" t="n">
-        <v>51065.77533142248</v>
+        <v>51065.77533142247</v>
       </c>
       <c r="AN13" s="368" t="n">
         <v>59932.20549313851</v>
@@ -3643,7 +3643,7 @@
         <v>278.3276406966011</v>
       </c>
       <c r="AS13" s="372" t="n">
-        <v>303.5509509432739</v>
+        <v>303.5509509432738</v>
       </c>
       <c r="AT13" s="382" t="n">
         <v>293.5776241007592</v>
@@ -3675,7 +3675,7 @@
         <v>46646.50320841985</v>
       </c>
       <c r="BD13" s="384" t="n">
-        <v>55924.15283488185</v>
+        <v>55924.15283488184</v>
       </c>
       <c r="BE13" s="384" t="n">
         <v>67485.43947806672</v>
@@ -3687,10 +3687,10 @@
         <v>307.3051522628174</v>
       </c>
       <c r="BH13" s="372" t="n">
-        <v>265.6277937976782</v>
+        <v>265.6277937976781</v>
       </c>
       <c r="BI13" s="372" t="n">
-        <v>304.8076214542658</v>
+        <v>304.8076214542656</v>
       </c>
       <c r="BJ13" s="372" t="n">
         <v>341.8073665040947</v>
@@ -3699,7 +3699,7 @@
         <v>338.7855254633852</v>
       </c>
       <c r="BL13" s="386" t="n">
-        <v>273.825365414749</v>
+        <v>273.8253654147491</v>
       </c>
       <c r="BM13" s="372" t="n">
         <v>228.4189552512156</v>
@@ -3725,7 +3725,7 @@
         <v>46780.86563448362</v>
       </c>
       <c r="BU13" s="375" t="n">
-        <v>56170.65521150504</v>
+        <v>56170.65521150502</v>
       </c>
       <c r="BV13" s="375" t="n">
         <v>67885.43870174915</v>
@@ -3740,7 +3740,7 @@
         <v>265.5809127461571</v>
       </c>
       <c r="BZ13" s="372" t="n">
-        <v>304.7626318059581</v>
+        <v>304.7626318059579</v>
       </c>
       <c r="CA13" s="372" t="n">
         <v>341.7608589849468</v>
@@ -3755,7 +3755,7 @@
         <v>229.1618792055127</v>
       </c>
       <c r="CE13" s="372" t="n">
-        <v>246.6689628544317</v>
+        <v>246.6689628544316</v>
       </c>
       <c r="CF13" s="372" t="n">
         <v>266.8165636938714</v>
@@ -3767,7 +3767,7 @@
         <v>-0.4071193850408008</v>
       </c>
       <c r="CX13" s="103" t="n">
-        <v>0.04688105152109756</v>
+        <v>0.04688105152104072</v>
       </c>
       <c r="CY13" s="103" t="n">
         <v>0.04498964830770547</v>
@@ -4001,64 +4001,64 @@
         </is>
       </c>
       <c r="BS14" s="419" t="n">
-        <v>687.6601186702486</v>
+        <v>687.6601186702484</v>
       </c>
       <c r="BT14" s="420" t="n">
-        <v>771.0902486687166</v>
+        <v>771.0902486687163</v>
       </c>
       <c r="BU14" s="420" t="n">
-        <v>869.2810738962293</v>
+        <v>869.2810738962289</v>
       </c>
       <c r="BV14" s="420" t="n">
-        <v>957.4795767063711</v>
+        <v>957.4795767063707</v>
       </c>
       <c r="BW14" s="421" t="n">
         <v>1052.062863383992</v>
       </c>
       <c r="BX14" s="416" t="n">
-        <v>79.66361321140545</v>
+        <v>79.66361321140543</v>
       </c>
       <c r="BY14" s="417" t="n">
         <v>101.9262551993843</v>
       </c>
       <c r="BZ14" s="417" t="n">
-        <v>112.8247865600319</v>
+        <v>112.8247865600318</v>
       </c>
       <c r="CA14" s="417" t="n">
-        <v>121.1482847990558</v>
+        <v>121.1482847990557</v>
       </c>
       <c r="CB14" s="418" t="n">
         <v>129.3107001526823</v>
       </c>
       <c r="CC14" s="417" t="n">
-        <v>79.66361321140545</v>
+        <v>79.66361321140543</v>
       </c>
       <c r="CD14" s="417" t="n">
         <v>101.9262551993843</v>
       </c>
       <c r="CE14" s="417" t="n">
-        <v>112.8247865600319</v>
+        <v>112.8247865600318</v>
       </c>
       <c r="CF14" s="417" t="n">
-        <v>121.1482847990558</v>
+        <v>121.1482847990557</v>
       </c>
       <c r="CG14" s="418" t="n">
         <v>129.3107001526823</v>
       </c>
       <c r="CW14" s="132" t="n">
-        <v>0.4317330834502258</v>
+        <v>0.43173308345024</v>
       </c>
       <c r="CX14" s="133" t="n">
-        <v>0.5397637059620308</v>
+        <v>0.5397637059620735</v>
       </c>
       <c r="CY14" s="133" t="n">
-        <v>0.5963543019979198</v>
+        <v>0.5963543019979625</v>
       </c>
       <c r="CZ14" s="133" t="n">
-        <v>0.6409081959648546</v>
+        <v>0.6409081959648972</v>
       </c>
       <c r="DA14" s="134" t="n">
-        <v>0.685071409381294</v>
+        <v>0.6850714093813224</v>
       </c>
       <c r="DC14" s="422" t="n">
         <v>0</v>
@@ -4083,13 +4083,13 @@
         </is>
       </c>
       <c r="C15" s="425" t="n">
-        <v>87054.89916619583</v>
+        <v>87054.89916619584</v>
       </c>
       <c r="D15" s="425" t="n">
         <v>88288.66723237108</v>
       </c>
       <c r="E15" s="425" t="n">
-        <v>98816.77292604015</v>
+        <v>98816.77292604014</v>
       </c>
       <c r="F15" s="425" t="n">
         <v>109590.6802201316</v>
@@ -4104,7 +4104,7 @@
         <v>9.994995455743462</v>
       </c>
       <c r="J15" s="427" t="n">
-        <v>9.350722312571559</v>
+        <v>9.350722312571557</v>
       </c>
       <c r="K15" s="427" t="n">
         <v>8.706051845429034</v>
@@ -4133,13 +4133,13 @@
         </is>
       </c>
       <c r="T15" s="429" t="n">
-        <v>87054.89916619583</v>
+        <v>87054.89916619584</v>
       </c>
       <c r="U15" s="430" t="n">
         <v>88288.66723237108</v>
       </c>
       <c r="V15" s="430" t="n">
-        <v>98816.77292604015</v>
+        <v>98816.77292604014</v>
       </c>
       <c r="W15" s="430" t="n">
         <v>109590.6802201316</v>
@@ -4154,7 +4154,7 @@
         <v>9.994995455743462</v>
       </c>
       <c r="AA15" s="433" t="n">
-        <v>9.350722312571559</v>
+        <v>9.350722312571557</v>
       </c>
       <c r="AB15" s="433" t="n">
         <v>8.706051845429034</v>
@@ -4189,10 +4189,10 @@
         <v>88671.45805825636</v>
       </c>
       <c r="AM15" s="408" t="n">
-        <v>99126.17020106611</v>
+        <v>99126.1702010661</v>
       </c>
       <c r="AN15" s="408" t="n">
-        <v>109834.8887553949</v>
+        <v>109834.8887553948</v>
       </c>
       <c r="AO15" s="409" t="n">
         <v>115776.9673300603</v>
@@ -4201,25 +4201,25 @@
         <v>73.25241386005487</v>
       </c>
       <c r="AQ15" s="437" t="n">
-        <v>38.90342809245881</v>
+        <v>38.90342809245882</v>
       </c>
       <c r="AR15" s="437" t="n">
-        <v>37.8649061726212</v>
+        <v>37.86490617262119</v>
       </c>
       <c r="AS15" s="437" t="n">
-        <v>35.97214949404539</v>
+        <v>35.97214949404538</v>
       </c>
       <c r="AT15" s="438" t="n">
         <v>32.24980724680013</v>
       </c>
       <c r="AU15" s="437" t="n">
-        <v>69.7965086948781</v>
+        <v>69.79650869487811</v>
       </c>
       <c r="AV15" s="437" t="n">
         <v>36.76387591143335</v>
       </c>
       <c r="AW15" s="437" t="n">
-        <v>35.05394694093656</v>
+        <v>35.05394694093655</v>
       </c>
       <c r="AX15" s="437" t="n">
         <v>33.2883702961454</v>
@@ -4251,7 +4251,7 @@
         <v>75.6976594482273</v>
       </c>
       <c r="BH15" s="443" t="n">
-        <v>41.45609287492059</v>
+        <v>41.4560928749206</v>
       </c>
       <c r="BI15" s="443" t="n">
         <v>41.62000973455422</v>
@@ -4263,7 +4263,7 @@
         <v>37.32410199783979</v>
       </c>
       <c r="BL15" s="443" t="n">
-        <v>72.12639239375586</v>
+        <v>72.12639239375588</v>
       </c>
       <c r="BM15" s="443" t="n">
         <v>39.17615307844483</v>
@@ -4283,7 +4283,7 @@
         </is>
       </c>
       <c r="BS15" s="439" t="n">
-        <v>90786.47095502257</v>
+        <v>90786.47095502255</v>
       </c>
       <c r="BT15" s="440" t="n">
         <v>94496.35629231625</v>
@@ -4298,19 +4298,19 @@
         <v>134649.2830262009</v>
       </c>
       <c r="BX15" s="442" t="n">
-        <v>75.89417816631916</v>
+        <v>75.89417816631914</v>
       </c>
       <c r="BY15" s="443" t="n">
         <v>41.34127517246636</v>
       </c>
       <c r="BZ15" s="443" t="n">
-        <v>41.52477957589833</v>
+        <v>41.52477957589831</v>
       </c>
       <c r="CA15" s="443" t="n">
         <v>40.54345786920423</v>
       </c>
       <c r="CB15" s="444" t="n">
-        <v>37.27353150655127</v>
+        <v>37.27353150655126</v>
       </c>
       <c r="CC15" s="443" t="n">
         <v>72.44476821545784</v>
@@ -4319,13 +4319,13 @@
         <v>39.1906414254394</v>
       </c>
       <c r="CE15" s="443" t="n">
-        <v>38.60702661544716</v>
+        <v>38.60702661544715</v>
       </c>
       <c r="CF15" s="443" t="n">
         <v>37.72024445483262</v>
       </c>
       <c r="CG15" s="444" t="n">
-        <v>34.82942512433014</v>
+        <v>34.82942512433012</v>
       </c>
     </row>
     <row r="16" ht="15.75" customHeight="1" thickBot="1">
@@ -5061,7 +5061,7 @@
         <v>0</v>
       </c>
       <c r="H20" s="371" t="n">
-        <v>5.977296871566291</v>
+        <v>5.977296871566293</v>
       </c>
       <c r="I20" s="372" t="n">
         <v>0</v>
@@ -5076,7 +5076,7 @@
         <v>0</v>
       </c>
       <c r="M20" s="371" t="n">
-        <v>5.948605864553519</v>
+        <v>5.948605864553521</v>
       </c>
       <c r="N20" s="372" t="n">
         <v>0</v>
@@ -5111,7 +5111,7 @@
         <v>0</v>
       </c>
       <c r="Y20" s="377" t="n">
-        <v>5.977296871566291</v>
+        <v>5.977296871566293</v>
       </c>
       <c r="Z20" s="372" t="n">
         <v>0</v>
@@ -5126,7 +5126,7 @@
         <v>0</v>
       </c>
       <c r="AD20" s="377" t="n">
-        <v>5.948605864553519</v>
+        <v>5.948605864553521</v>
       </c>
       <c r="AE20" s="372" t="n">
         <v>0</v>
@@ -5246,7 +5246,7 @@
         </is>
       </c>
       <c r="BS20" s="391" t="n">
-        <v>4326.533035412037</v>
+        <v>4326.533035412035</v>
       </c>
       <c r="BT20" s="375" t="n">
         <v>0</v>
@@ -5261,7 +5261,7 @@
         <v>0</v>
       </c>
       <c r="BX20" s="386" t="n">
-        <v>4.799645254128303</v>
+        <v>4.799645254128301</v>
       </c>
       <c r="BY20" s="372" t="n">
         <v>0</v>
@@ -5276,7 +5276,7 @@
         <v>0</v>
       </c>
       <c r="CC20" s="388" t="n">
-        <v>4.726432101391022</v>
+        <v>4.72643210139102</v>
       </c>
       <c r="CD20" s="389" t="n">
         <v>0</v>
@@ -5291,7 +5291,7 @@
         <v>0</v>
       </c>
       <c r="CW20" s="91" t="n">
-        <v>0.005749963029404448</v>
+        <v>0.005749963029406224</v>
       </c>
       <c r="CX20" s="92" t="n">
         <v>0</v>
@@ -5343,7 +5343,7 @@
         <v>0</v>
       </c>
       <c r="H21" s="371" t="n">
-        <v>9.154306936871935</v>
+        <v>9.154306936871937</v>
       </c>
       <c r="I21" s="372" t="n">
         <v>0</v>
@@ -5358,7 +5358,7 @@
         <v>0</v>
       </c>
       <c r="M21" s="371" t="n">
-        <v>8.359723385456329</v>
+        <v>8.359723385456331</v>
       </c>
       <c r="N21" s="372" t="n">
         <v>0</v>
@@ -5393,7 +5393,7 @@
         <v>0</v>
       </c>
       <c r="Y21" s="377" t="n">
-        <v>9.154306936871935</v>
+        <v>9.154306936871937</v>
       </c>
       <c r="Z21" s="372" t="n">
         <v>0</v>
@@ -5408,7 +5408,7 @@
         <v>0</v>
       </c>
       <c r="AD21" s="377" t="n">
-        <v>8.359723385456329</v>
+        <v>8.359723385456331</v>
       </c>
       <c r="AE21" s="372" t="n">
         <v>0</v>
@@ -5528,7 +5528,7 @@
         </is>
       </c>
       <c r="BS21" s="391" t="n">
-        <v>510.2510503017755</v>
+        <v>510.2510503017754</v>
       </c>
       <c r="BT21" s="375" t="n">
         <v>0</v>
@@ -5558,7 +5558,7 @@
         <v>0</v>
       </c>
       <c r="CC21" s="386" t="n">
-        <v>2.873833781895743</v>
+        <v>2.873833781895742</v>
       </c>
       <c r="CD21" s="372" t="n">
         <v>0</v>
@@ -5573,7 +5573,7 @@
         <v>0</v>
       </c>
       <c r="CW21" s="102" t="n">
-        <v>0.02930111296264037</v>
+        <v>0.02930111296264082</v>
       </c>
       <c r="CX21" s="103" t="n">
         <v>0</v>
@@ -5588,7 +5588,7 @@
         <v>0</v>
       </c>
       <c r="DC21" s="396" t="n">
-        <v>0.009957156313779797</v>
+        <v>0.009957156313779799</v>
       </c>
       <c r="DD21" s="397" t="n">
         <v>0</v>
@@ -5610,7 +5610,7 @@
         </is>
       </c>
       <c r="C22" s="369" t="n">
-        <v>1753.879886754616</v>
+        <v>1753.879886754615</v>
       </c>
       <c r="D22" s="368" t="n">
         <v>0</v>
@@ -5625,7 +5625,7 @@
         <v>0</v>
       </c>
       <c r="H22" s="371" t="n">
-        <v>7.28402021573903</v>
+        <v>7.284020215739028</v>
       </c>
       <c r="I22" s="372" t="n">
         <v>0</v>
@@ -5640,7 +5640,7 @@
         <v>0</v>
       </c>
       <c r="M22" s="371" t="n">
-        <v>6.815669265980904</v>
+        <v>6.815669265980903</v>
       </c>
       <c r="N22" s="372" t="n">
         <v>0</v>
@@ -5660,7 +5660,7 @@
         </is>
       </c>
       <c r="T22" s="374" t="n">
-        <v>1753.879886754616</v>
+        <v>1753.879886754615</v>
       </c>
       <c r="U22" s="375" t="n">
         <v>0</v>
@@ -5675,7 +5675,7 @@
         <v>0</v>
       </c>
       <c r="Y22" s="377" t="n">
-        <v>7.28402021573903</v>
+        <v>7.284020215739028</v>
       </c>
       <c r="Z22" s="372" t="n">
         <v>0</v>
@@ -5690,7 +5690,7 @@
         <v>0</v>
       </c>
       <c r="AD22" s="377" t="n">
-        <v>6.815669265980904</v>
+        <v>6.815669265980903</v>
       </c>
       <c r="AE22" s="372" t="n">
         <v>0</v>
@@ -6189,7 +6189,7 @@
         <v>0</v>
       </c>
       <c r="H24" s="427" t="n">
-        <v>6.259559967555728</v>
+        <v>6.259559967555729</v>
       </c>
       <c r="I24" s="427" t="n">
         <v>0</v>
@@ -6204,7 +6204,7 @@
         <v>0</v>
       </c>
       <c r="M24" s="427" t="n">
-        <v>6.167525551438875</v>
+        <v>6.167525551438876</v>
       </c>
       <c r="N24" s="427" t="n">
         <v>0</v>
@@ -6239,7 +6239,7 @@
         <v>0</v>
       </c>
       <c r="Y24" s="432" t="n">
-        <v>6.259559967555728</v>
+        <v>6.259559967555729</v>
       </c>
       <c r="Z24" s="433" t="n">
         <v>0</v>
@@ -6254,7 +6254,7 @@
         <v>0</v>
       </c>
       <c r="AD24" s="433" t="n">
-        <v>6.167525551438875</v>
+        <v>6.167525551438876</v>
       </c>
       <c r="AE24" s="433" t="n">
         <v>0</v>
@@ -6274,7 +6274,7 @@
         </is>
       </c>
       <c r="AK24" s="435" t="n">
-        <v>5258.720237329034</v>
+        <v>5258.720237329033</v>
       </c>
       <c r="AL24" s="408" t="n">
         <v>0</v>
@@ -6289,7 +6289,7 @@
         <v>0</v>
       </c>
       <c r="AP24" s="436" t="n">
-        <v>4.37902041561962</v>
+        <v>4.379020415619619</v>
       </c>
       <c r="AQ24" s="437" t="n">
         <v>0</v>
@@ -6324,7 +6324,7 @@
         </is>
       </c>
       <c r="BB24" s="439" t="n">
-        <v>5258.720237329034</v>
+        <v>5258.720237329033</v>
       </c>
       <c r="BC24" s="440" t="n">
         <v>0</v>
@@ -6339,7 +6339,7 @@
         <v>0</v>
       </c>
       <c r="BG24" s="442" t="n">
-        <v>4.37902041561962</v>
+        <v>4.379020415619619</v>
       </c>
       <c r="BH24" s="443" t="n">
         <v>0</v>
@@ -6374,7 +6374,7 @@
         </is>
       </c>
       <c r="BS24" s="439" t="n">
-        <v>5224.706779851274</v>
+        <v>5224.706779851273</v>
       </c>
       <c r="BT24" s="440" t="n">
         <v>0</v>
@@ -6389,7 +6389,7 @@
         <v>0</v>
       </c>
       <c r="BX24" s="442" t="n">
-        <v>4.367664290125944</v>
+        <v>4.367664290125942</v>
       </c>
       <c r="BY24" s="443" t="n">
         <v>0</v>
@@ -6404,7 +6404,7 @@
         <v>0</v>
       </c>
       <c r="CC24" s="443" t="n">
-        <v>4.169152822864703</v>
+        <v>4.169152822864702</v>
       </c>
       <c r="CD24" s="443" t="n">
         <v>0</v>
@@ -7336,7 +7336,7 @@
         </is>
       </c>
       <c r="BS29" s="391" t="n">
-        <v>9.772854192859578</v>
+        <v>9.772854192859572</v>
       </c>
       <c r="BT29" s="375" t="n">
         <v>0</v>
@@ -7381,7 +7381,7 @@
         <v>0</v>
       </c>
       <c r="CW29" s="91" t="n">
-        <v>-7.1111847940324e-05</v>
+        <v>-7.1111847940319e-05</v>
       </c>
       <c r="CX29" s="92" t="n">
         <v>0</v>
@@ -7618,7 +7618,7 @@
         </is>
       </c>
       <c r="BS30" s="391" t="n">
-        <v>55.984431488026</v>
+        <v>55.98443148802599</v>
       </c>
       <c r="BT30" s="375" t="n">
         <v>0</v>
@@ -7633,7 +7633,7 @@
         <v>0</v>
       </c>
       <c r="BX30" s="386" t="n">
-        <v>0.3712528407756716</v>
+        <v>0.3712528407756715</v>
       </c>
       <c r="BY30" s="372" t="n">
         <v>0</v>
@@ -7648,7 +7648,7 @@
         <v>0</v>
       </c>
       <c r="CC30" s="386" t="n">
-        <v>0.3153152754420838</v>
+        <v>0.3153152754420837</v>
       </c>
       <c r="CD30" s="372" t="n">
         <v>0</v>
@@ -7663,7 +7663,7 @@
         <v>0</v>
       </c>
       <c r="CW30" s="102" t="n">
-        <v>-0.000513733733200739</v>
+        <v>-0.0005137337332006831</v>
       </c>
       <c r="CX30" s="103" t="n">
         <v>0</v>
@@ -8394,7 +8394,7 @@
         <v>0</v>
       </c>
       <c r="AU33" s="437" t="n">
-        <v>0.0529610604169776</v>
+        <v>0.05296106041697761</v>
       </c>
       <c r="AV33" s="437" t="n">
         <v>0</v>
@@ -8444,7 +8444,7 @@
         <v>0</v>
       </c>
       <c r="BL33" s="443" t="n">
-        <v>0.05211583008878913</v>
+        <v>0.05211583008878914</v>
       </c>
       <c r="BM33" s="443" t="n">
         <v>0</v>
@@ -8464,7 +8464,7 @@
         </is>
       </c>
       <c r="BS33" s="439" t="n">
-        <v>65.75728568088559</v>
+        <v>65.75728568088556</v>
       </c>
       <c r="BT33" s="440" t="n">
         <v>0</v>
@@ -8479,7 +8479,7 @@
         <v>0</v>
       </c>
       <c r="BX33" s="442" t="n">
-        <v>0.05497069224853028</v>
+        <v>0.05497069224853025</v>
       </c>
       <c r="BY33" s="443" t="n">
         <v>0</v>
@@ -8494,7 +8494,7 @@
         <v>0</v>
       </c>
       <c r="CC33" s="443" t="n">
-        <v>0.05247226012331142</v>
+        <v>0.0524722601233114</v>
       </c>
       <c r="CD33" s="443" t="n">
         <v>0</v>
@@ -9229,7 +9229,7 @@
         <v>133.4764622992034</v>
       </c>
       <c r="D38" s="368" t="n">
-        <v>76.38905038910424</v>
+        <v>76.38905038910423</v>
       </c>
       <c r="E38" s="368" t="n">
         <v>36.27632243820575</v>
@@ -9244,7 +9244,7 @@
         <v>0.0407272708519966</v>
       </c>
       <c r="I38" s="372" t="n">
-        <v>0.009592419027212555</v>
+        <v>0.009592419027212553</v>
       </c>
       <c r="J38" s="372" t="n">
         <v>0.003786730734415433</v>
@@ -9259,7 +9259,7 @@
         <v>0.04053178007435358</v>
       </c>
       <c r="N38" s="372" t="n">
-        <v>0.009527266737624152</v>
+        <v>0.009527266737624151</v>
       </c>
       <c r="O38" s="372" t="n">
         <v>0.003748472412460687</v>
@@ -9279,7 +9279,7 @@
         <v>133.4764622992034</v>
       </c>
       <c r="U38" s="375" t="n">
-        <v>76.38905038910424</v>
+        <v>76.38905038910423</v>
       </c>
       <c r="V38" s="375" t="n">
         <v>36.27632243820575</v>
@@ -9294,7 +9294,7 @@
         <v>0.0407272708519966</v>
       </c>
       <c r="Z38" s="372" t="n">
-        <v>0.009592419027212555</v>
+        <v>0.009592419027212553</v>
       </c>
       <c r="AA38" s="372" t="n">
         <v>0.003786730734415433</v>
@@ -9309,7 +9309,7 @@
         <v>0.04053178007435358</v>
       </c>
       <c r="AE38" s="372" t="n">
-        <v>0.009527266737624152</v>
+        <v>0.009527266737624151</v>
       </c>
       <c r="AF38" s="372" t="n">
         <v>0.003748472412460687</v>
@@ -9329,7 +9329,7 @@
         <v>133.4764622992034</v>
       </c>
       <c r="AL38" s="368" t="n">
-        <v>76.38905038910424</v>
+        <v>76.38905038910423</v>
       </c>
       <c r="AM38" s="368" t="n">
         <v>36.27632243820575</v>
@@ -9359,7 +9359,7 @@
         <v>0.1447866785703222</v>
       </c>
       <c r="AV38" s="372" t="n">
-        <v>0.03867670552533663</v>
+        <v>0.03867670552533662</v>
       </c>
       <c r="AW38" s="372" t="n">
         <v>0.01545667365189776</v>
@@ -9379,7 +9379,7 @@
         <v>132.9163127847999</v>
       </c>
       <c r="BC38" s="375" t="n">
-        <v>70.62874672220299</v>
+        <v>70.62874672220298</v>
       </c>
       <c r="BD38" s="375" t="n">
         <v>32.45283468400488</v>
@@ -9394,13 +9394,13 @@
         <v>0.1466943498732974</v>
       </c>
       <c r="BH38" s="372" t="n">
-        <v>0.03677416462690203</v>
+        <v>0.03677416462690202</v>
       </c>
       <c r="BI38" s="372" t="n">
         <v>0.01442865926428062</v>
       </c>
       <c r="BJ38" s="372" t="n">
-        <v>0.005505546010806094</v>
+        <v>0.005505546010806092</v>
       </c>
       <c r="BK38" s="387" t="n">
         <v>0.005090021898555216</v>
@@ -9409,16 +9409,16 @@
         <v>0.1441790644165138</v>
       </c>
       <c r="BM38" s="389" t="n">
-        <v>0.03576019370163376</v>
+        <v>0.03576019370163375</v>
       </c>
       <c r="BN38" s="389" t="n">
         <v>0.0138275558566918</v>
       </c>
       <c r="BO38" s="389" t="n">
-        <v>0.005277638981293084</v>
+        <v>0.005277638981293083</v>
       </c>
       <c r="BP38" s="390" t="n">
-        <v>0.00489044049664802</v>
+        <v>0.004890440496648021</v>
       </c>
       <c r="BR38" s="83" t="inlineStr">
         <is>
@@ -9426,31 +9426,31 @@
         </is>
       </c>
       <c r="BS38" s="391" t="n">
-        <v>132.6378209519391</v>
+        <v>132.637820951939</v>
       </c>
       <c r="BT38" s="375" t="n">
-        <v>70.55321621334859</v>
+        <v>70.55321621334855</v>
       </c>
       <c r="BU38" s="375" t="n">
-        <v>32.3305694056821</v>
+        <v>32.33056940568208</v>
       </c>
       <c r="BV38" s="375" t="n">
-        <v>14.43683763070941</v>
+        <v>14.43683763070939</v>
       </c>
       <c r="BW38" s="392" t="n">
         <v>15.8487641383771</v>
       </c>
       <c r="BX38" s="386" t="n">
-        <v>0.147141945442066</v>
+        <v>0.1471419454420659</v>
       </c>
       <c r="BY38" s="372" t="n">
-        <v>0.03663247190347484</v>
+        <v>0.03663247190347481</v>
       </c>
       <c r="BZ38" s="372" t="n">
-        <v>0.01431807736221278</v>
+        <v>0.01431807736221277</v>
       </c>
       <c r="CA38" s="372" t="n">
-        <v>0.005411602615854708</v>
+        <v>0.005411602615854703</v>
       </c>
       <c r="CB38" s="387" t="n">
         <v>0.005002985281895763</v>
@@ -9459,37 +9459,37 @@
         <v>0.1448974617030969</v>
       </c>
       <c r="CD38" s="389" t="n">
-        <v>0.03573205078557531</v>
+        <v>0.03573205078557529</v>
       </c>
       <c r="CE38" s="389" t="n">
-        <v>0.01377872536326053</v>
+        <v>0.01377872536326052</v>
       </c>
       <c r="CF38" s="389" t="n">
-        <v>0.0052146033652736</v>
+        <v>0.005214603365273595</v>
       </c>
       <c r="CG38" s="390" t="n">
-        <v>0.00483680732001359</v>
+        <v>0.004836807320013589</v>
       </c>
       <c r="CW38" s="91" t="n">
-        <v>-0.000447595568768555</v>
+        <v>-0.0004475955687685</v>
       </c>
       <c r="CX38" s="92" t="n">
-        <v>0.000141692723427192</v>
+        <v>0.000141692723427213</v>
       </c>
       <c r="CY38" s="92" t="n">
-        <v>0.000110581902067839</v>
+        <v>0.000110581902067846</v>
       </c>
       <c r="CZ38" s="92" t="n">
-        <v>9.3943394951386e-05</v>
+        <v>9.394339495138899e-05</v>
       </c>
       <c r="DA38" s="93" t="n">
-        <v>8.7036616659452e-05</v>
+        <v>8.703661665945399e-05</v>
       </c>
       <c r="DC38" s="393" t="n">
-        <v>0.003528009884850774</v>
+        <v>0.003528009884850775</v>
       </c>
       <c r="DD38" s="394" t="n">
-        <v>0.003547964645490738</v>
+        <v>0.003547964645490739</v>
       </c>
       <c r="DE38" s="394" t="n">
         <v>0.00731687483938503</v>
@@ -9664,13 +9664,13 @@
         <v>68.33664616587697</v>
       </c>
       <c r="BD39" s="375" t="n">
-        <v>76.79979343970206</v>
+        <v>76.79979343970204</v>
       </c>
       <c r="BE39" s="375" t="n">
         <v>84.04164482688762</v>
       </c>
       <c r="BF39" s="392" t="n">
-        <v>91.85091082748838</v>
+        <v>91.85091082748846</v>
       </c>
       <c r="BG39" s="386" t="n">
         <v>0.8543472862021683</v>
@@ -9679,13 +9679,13 @@
         <v>0.3894198903507362</v>
       </c>
       <c r="BI39" s="372" t="n">
-        <v>0.4326438787548664</v>
+        <v>0.4326438787548663</v>
       </c>
       <c r="BJ39" s="372" t="n">
         <v>0.4342710834930928</v>
       </c>
       <c r="BK39" s="387" t="n">
-        <v>0.4270396223772717</v>
+        <v>0.4270396223772721</v>
       </c>
       <c r="BL39" s="386" t="n">
         <v>0.7242054256053126</v>
@@ -9700,7 +9700,7 @@
         <v>0.313594070124523</v>
       </c>
       <c r="BP39" s="387" t="n">
-        <v>0.3114401757853605</v>
+        <v>0.3114401757853608</v>
       </c>
       <c r="BR39" s="101" t="inlineStr">
         <is>
@@ -9708,7 +9708,7 @@
         </is>
       </c>
       <c r="BS39" s="391" t="n">
-        <v>127.4348547561338</v>
+        <v>127.4348547561337</v>
       </c>
       <c r="BT39" s="375" t="n">
         <v>66.89145973609607</v>
@@ -9717,13 +9717,13 @@
         <v>75.30150517013892</v>
       </c>
       <c r="BV39" s="375" t="n">
-        <v>82.5164404216678</v>
+        <v>82.51644042166778</v>
       </c>
       <c r="BW39" s="392" t="n">
-        <v>90.30068098406994</v>
+        <v>90.30068098407001</v>
       </c>
       <c r="BX39" s="386" t="n">
-        <v>0.845066219028563</v>
+        <v>0.8450662190285628</v>
       </c>
       <c r="BY39" s="372" t="n">
         <v>0.3798975964538547</v>
@@ -9732,13 +9732,13 @@
         <v>0.4220668701846503</v>
       </c>
       <c r="CA39" s="372" t="n">
-        <v>0.4236427786325573</v>
+        <v>0.4236427786325572</v>
       </c>
       <c r="CB39" s="387" t="n">
-        <v>0.4165487326267489</v>
+        <v>0.4165487326267492</v>
       </c>
       <c r="CC39" s="386" t="n">
-        <v>0.7177380436013975</v>
+        <v>0.7177380436013974</v>
       </c>
       <c r="CD39" s="372" t="n">
         <v>0.297315247957744</v>
@@ -9747,25 +9747,25 @@
         <v>0.307023106800737</v>
       </c>
       <c r="CF39" s="372" t="n">
-        <v>0.3080006976337506</v>
+        <v>0.3080006976337505</v>
       </c>
       <c r="CG39" s="387" t="n">
-        <v>0.3062607452808094</v>
+        <v>0.3062607452808096</v>
       </c>
       <c r="CW39" s="102" t="n">
-        <v>0.009281067173605217</v>
+        <v>0.00928106717360544</v>
       </c>
       <c r="CX39" s="103" t="n">
         <v>0.009522293896881528</v>
       </c>
       <c r="CY39" s="103" t="n">
-        <v>0.01057700857021604</v>
+        <v>0.01057700857021598</v>
       </c>
       <c r="CZ39" s="103" t="n">
-        <v>0.01062830486053551</v>
+        <v>0.01062830486053556</v>
       </c>
       <c r="DA39" s="104" t="n">
-        <v>0.01049088975052281</v>
+        <v>0.01049088975052287</v>
       </c>
       <c r="DC39" s="396" t="n">
         <v>0.01223209394752628</v>
@@ -9940,49 +9940,49 @@
         </is>
       </c>
       <c r="BB40" s="391" t="n">
-        <v>52.54416165784014</v>
+        <v>52.54416165784013</v>
       </c>
       <c r="BC40" s="375" t="n">
-        <v>66.76208474063301</v>
+        <v>66.76208474063299</v>
       </c>
       <c r="BD40" s="375" t="n">
-        <v>59.40875543046739</v>
+        <v>59.4087554304674</v>
       </c>
       <c r="BE40" s="375" t="n">
-        <v>58.184555292402</v>
+        <v>58.18455529240202</v>
       </c>
       <c r="BF40" s="392" t="n">
-        <v>64.22022148442252</v>
+        <v>64.22022148442255</v>
       </c>
       <c r="BG40" s="386" t="n">
-        <v>0.3882771896730686</v>
+        <v>0.3882771896730685</v>
       </c>
       <c r="BH40" s="372" t="n">
-        <v>0.3801756628948547</v>
+        <v>0.3801756628948545</v>
       </c>
       <c r="BI40" s="372" t="n">
-        <v>0.3238000133821287</v>
+        <v>0.3238000133821288</v>
       </c>
       <c r="BJ40" s="372" t="n">
-        <v>0.2946992680127916</v>
+        <v>0.2946992680127917</v>
       </c>
       <c r="BK40" s="387" t="n">
-        <v>0.2945340722527586</v>
+        <v>0.2945340722527587</v>
       </c>
       <c r="BL40" s="386" t="n">
         <v>0.3459757916896601</v>
       </c>
       <c r="BM40" s="372" t="n">
-        <v>0.3269210894268252</v>
+        <v>0.326921089426825</v>
       </c>
       <c r="BN40" s="372" t="n">
-        <v>0.2608026397506416</v>
+        <v>0.2608026397506417</v>
       </c>
       <c r="BO40" s="372" t="n">
         <v>0.2286206564721464</v>
       </c>
       <c r="BP40" s="387" t="n">
-        <v>0.224268885986085</v>
+        <v>0.2242688859860851</v>
       </c>
       <c r="BR40" s="111" t="inlineStr">
         <is>
@@ -9990,49 +9990,49 @@
         </is>
       </c>
       <c r="BS40" s="391" t="n">
-        <v>51.96879991723807</v>
+        <v>51.96879991723806</v>
       </c>
       <c r="BT40" s="375" t="n">
-        <v>66.17075728781755</v>
+        <v>66.17075728781752</v>
       </c>
       <c r="BU40" s="375" t="n">
-        <v>58.79476078607205</v>
+        <v>58.79476078607207</v>
       </c>
       <c r="BV40" s="375" t="n">
-        <v>57.56892998018631</v>
+        <v>57.56892998018633</v>
       </c>
       <c r="BW40" s="392" t="n">
-        <v>63.63131279334116</v>
+        <v>63.63131279334119</v>
       </c>
       <c r="BX40" s="386" t="n">
-        <v>0.3839130617067616</v>
+        <v>0.3839130617067615</v>
       </c>
       <c r="BY40" s="372" t="n">
-        <v>0.3756597890879749</v>
+        <v>0.3756597890879748</v>
       </c>
       <c r="BZ40" s="372" t="n">
-        <v>0.3190001249957816</v>
+        <v>0.3190001249957817</v>
       </c>
       <c r="CA40" s="372" t="n">
-        <v>0.2898236696578317</v>
+        <v>0.2898236696578319</v>
       </c>
       <c r="CB40" s="387" t="n">
-        <v>0.2896500274801809</v>
+        <v>0.289650027480181</v>
       </c>
       <c r="CC40" s="386" t="n">
         <v>0.3427834229845441</v>
       </c>
       <c r="CD40" s="372" t="n">
-        <v>0.3241456711598434</v>
+        <v>0.3241456711598433</v>
       </c>
       <c r="CE40" s="372" t="n">
-        <v>0.258192513684695</v>
+        <v>0.2581925136846951</v>
       </c>
       <c r="CF40" s="372" t="n">
-        <v>0.2262686132195626</v>
+        <v>0.2262686132195627</v>
       </c>
       <c r="CG40" s="387" t="n">
-        <v>0.2222703138770042</v>
+        <v>0.2222703138770043</v>
       </c>
       <c r="CW40" s="102" t="n">
         <v>0.004364127966306974</v>
@@ -10044,7 +10044,7 @@
         <v>0.004799888386347151</v>
       </c>
       <c r="CZ40" s="103" t="n">
-        <v>0.004875598354959876</v>
+        <v>0.00487559835495982</v>
       </c>
       <c r="DA40" s="104" t="n">
         <v>0.004884044772577756</v>
@@ -10272,64 +10272,64 @@
         </is>
       </c>
       <c r="BS41" s="419" t="n">
-        <v>67.54914673800951</v>
+        <v>67.54914673800948</v>
       </c>
       <c r="BT41" s="420" t="n">
-        <v>72.21928580121335</v>
+        <v>72.21928580121332</v>
       </c>
       <c r="BU41" s="420" t="n">
-        <v>77.49861864591595</v>
+        <v>77.49861864591594</v>
       </c>
       <c r="BV41" s="420" t="n">
-        <v>82.5476181488975</v>
+        <v>82.54761814889747</v>
       </c>
       <c r="BW41" s="421" t="n">
-        <v>87.95482401348623</v>
+        <v>87.9548240134862</v>
       </c>
       <c r="BX41" s="416" t="n">
-        <v>7.825390701591194</v>
+        <v>7.82539070159119</v>
       </c>
       <c r="BY41" s="417" t="n">
-        <v>9.546277323050761</v>
+        <v>9.546277323050758</v>
       </c>
       <c r="BZ41" s="417" t="n">
         <v>10.05861667760935</v>
       </c>
       <c r="CA41" s="417" t="n">
-        <v>10.44461166199181</v>
+        <v>10.4446116619918</v>
       </c>
       <c r="CB41" s="418" t="n">
         <v>10.810665665364</v>
       </c>
       <c r="CC41" s="417" t="n">
-        <v>7.825390701591194</v>
+        <v>7.82539070159119</v>
       </c>
       <c r="CD41" s="417" t="n">
-        <v>9.546277323050761</v>
+        <v>9.546277323050758</v>
       </c>
       <c r="CE41" s="417" t="n">
         <v>10.05861667760935</v>
       </c>
       <c r="CF41" s="417" t="n">
-        <v>10.44461166199181</v>
+        <v>10.4446116619918</v>
       </c>
       <c r="CG41" s="418" t="n">
         <v>10.810665665364</v>
       </c>
       <c r="CW41" s="132" t="n">
-        <v>0.04240932491770177</v>
+        <v>0.04240932491770533</v>
       </c>
       <c r="CX41" s="133" t="n">
-        <v>0.05055354987732841</v>
+        <v>0.05055354987733196</v>
       </c>
       <c r="CY41" s="133" t="n">
-        <v>0.05316650277595514</v>
+        <v>0.05316650277595691</v>
       </c>
       <c r="CZ41" s="133" t="n">
-        <v>0.05525490706652292</v>
+        <v>0.05525490706652647</v>
       </c>
       <c r="DA41" s="134" t="n">
-        <v>0.0572735122072352</v>
+        <v>0.05727351220723875</v>
       </c>
       <c r="DC41" s="422" t="n">
         <v>0</v>
@@ -10472,7 +10472,7 @@
         <v>0.3221593245948865</v>
       </c>
       <c r="AQ42" s="437" t="n">
-        <v>0.1298940007785931</v>
+        <v>0.1298940007785932</v>
       </c>
       <c r="AR42" s="437" t="n">
         <v>0.1029765250769197</v>
@@ -10484,7 +10484,7 @@
         <v>0.08317698217566019</v>
       </c>
       <c r="AU42" s="437" t="n">
-        <v>0.3069604797349159</v>
+        <v>0.306960479734916</v>
       </c>
       <c r="AV42" s="437" t="n">
         <v>0.1227502860394328</v>
@@ -10507,7 +10507,7 @@
         <v>382.3016453287519</v>
       </c>
       <c r="BC42" s="440" t="n">
-        <v>278.3905927485726</v>
+        <v>278.3905927485725</v>
       </c>
       <c r="BD42" s="440" t="n">
         <v>246.6362760752477</v>
@@ -10516,7 +10516,7 @@
         <v>239.8953764326034</v>
       </c>
       <c r="BF42" s="441" t="n">
-        <v>260.5936174274627</v>
+        <v>260.5936174274628</v>
       </c>
       <c r="BG42" s="442" t="n">
         <v>0.3183486921277779</v>
@@ -10525,13 +10525,13 @@
         <v>0.1221401862986806</v>
       </c>
       <c r="BI42" s="443" t="n">
-        <v>0.09421184570543926</v>
+        <v>0.09421184570543928</v>
       </c>
       <c r="BJ42" s="443" t="n">
         <v>0.07856840792347992</v>
       </c>
       <c r="BK42" s="444" t="n">
-        <v>0.07258865148733268</v>
+        <v>0.07258865148733271</v>
       </c>
       <c r="BL42" s="443" t="n">
         <v>0.3033296254311704</v>
@@ -10540,13 +10540,13 @@
         <v>0.1154229041772921</v>
       </c>
       <c r="BN42" s="443" t="n">
-        <v>0.08721788522360291</v>
+        <v>0.08721788522360292</v>
       </c>
       <c r="BO42" s="443" t="n">
         <v>0.07270664370413406</v>
       </c>
       <c r="BP42" s="444" t="n">
-        <v>0.06739509341296374</v>
+        <v>0.06739509341296376</v>
       </c>
       <c r="BR42" s="155" t="inlineStr">
         <is>
@@ -10554,10 +10554,10 @@
         </is>
       </c>
       <c r="BS42" s="439" t="n">
-        <v>379.5906223633204</v>
+        <v>379.5906223633203</v>
       </c>
       <c r="BT42" s="440" t="n">
-        <v>275.8347190384756</v>
+        <v>275.8347190384754</v>
       </c>
       <c r="BU42" s="440" t="n">
         <v>243.925454007809</v>
@@ -10566,10 +10566,10 @@
         <v>237.069826181461</v>
       </c>
       <c r="BW42" s="441" t="n">
-        <v>257.7355819292744</v>
+        <v>257.7355819292745</v>
       </c>
       <c r="BX42" s="442" t="n">
-        <v>0.3173239142446481</v>
+        <v>0.3173239142446479</v>
       </c>
       <c r="BY42" s="443" t="n">
         <v>0.1206751188015574</v>
@@ -10581,10 +10581,10 @@
         <v>0.07724477957220309</v>
       </c>
       <c r="CB42" s="444" t="n">
-        <v>0.07134620487753211</v>
+        <v>0.07134620487753213</v>
       </c>
       <c r="CC42" s="443" t="n">
-        <v>0.3029014605876229</v>
+        <v>0.3029014605876228</v>
       </c>
       <c r="CD42" s="443" t="n">
         <v>0.1143974221935446</v>
@@ -10593,7 +10593,7 @@
         <v>0.08628124753884053</v>
       </c>
       <c r="CF42" s="443" t="n">
-        <v>0.07186589702641837</v>
+        <v>0.07186589702641835</v>
       </c>
       <c r="CG42" s="444" t="n">
         <v>0.06666787933014512</v>
@@ -11234,7 +11234,7 @@
         </is>
       </c>
       <c r="C47" s="454" t="n">
-        <v>45168.45494875785</v>
+        <v>45168.45494875786</v>
       </c>
       <c r="D47" s="375" t="n">
         <v>23420.69497879438</v>
@@ -11243,7 +11243,7 @@
         <v>24125.43688001037</v>
       </c>
       <c r="F47" s="375" t="n">
-        <v>22927.57119851041</v>
+        <v>22927.5711985104</v>
       </c>
       <c r="G47" s="455" t="n">
         <v>22594.86520251621</v>
@@ -11264,7 +11264,7 @@
         <v>1.649309554857701</v>
       </c>
       <c r="M47" s="371" t="n">
-        <v>13.71596048281185</v>
+        <v>13.71596048281186</v>
       </c>
       <c r="N47" s="372" t="n">
         <v>2.921036550486241</v>
@@ -11273,7 +11273,7 @@
         <v>2.492908004589712</v>
       </c>
       <c r="P47" s="372" t="n">
-        <v>1.983101833817411</v>
+        <v>1.98310183381741</v>
       </c>
       <c r="Q47" s="373" t="n">
         <v>1.633982875888787</v>
@@ -11284,7 +11284,7 @@
         </is>
       </c>
       <c r="T47" s="374" t="n">
-        <v>45168.45494875785</v>
+        <v>45168.45494875786</v>
       </c>
       <c r="U47" s="375" t="n">
         <v>23420.69497879438</v>
@@ -11293,7 +11293,7 @@
         <v>24125.43688001037</v>
       </c>
       <c r="W47" s="375" t="n">
-        <v>22927.57119851041</v>
+        <v>22927.5711985104</v>
       </c>
       <c r="X47" s="376" t="n">
         <v>22594.86520251621</v>
@@ -11314,7 +11314,7 @@
         <v>1.649309554857701</v>
       </c>
       <c r="AD47" s="377" t="n">
-        <v>13.71596048281185</v>
+        <v>13.71596048281186</v>
       </c>
       <c r="AE47" s="372" t="n">
         <v>2.921036550486241</v>
@@ -11323,7 +11323,7 @@
         <v>2.492908004589712</v>
       </c>
       <c r="AG47" s="372" t="n">
-        <v>1.983101833817411</v>
+        <v>1.98310183381741</v>
       </c>
       <c r="AH47" s="378" t="n">
         <v>1.633982875888787</v>
@@ -11334,7 +11334,7 @@
         </is>
       </c>
       <c r="AK47" s="379" t="n">
-        <v>29932.97244112921</v>
+        <v>29932.97244112922</v>
       </c>
       <c r="AL47" s="375" t="n">
         <v>23420.69497879438</v>
@@ -11343,7 +11343,7 @@
         <v>24125.43688001037</v>
       </c>
       <c r="AN47" s="375" t="n">
-        <v>22927.57119851041</v>
+        <v>22927.5711985104</v>
       </c>
       <c r="AO47" s="456" t="n">
         <v>22594.86520251621</v>
@@ -11358,13 +11358,13 @@
         <v>10.72626510851906</v>
       </c>
       <c r="AS47" s="372" t="n">
-        <v>8.637374663648115</v>
+        <v>8.637374663648114</v>
       </c>
       <c r="AT47" s="382" t="n">
         <v>7.175855846984508</v>
       </c>
       <c r="AU47" s="372" t="n">
-        <v>32.46936264892264</v>
+        <v>32.46936264892265</v>
       </c>
       <c r="AV47" s="372" t="n">
         <v>11.858182792946</v>
@@ -11373,7 +11373,7 @@
         <v>10.27940484317248</v>
       </c>
       <c r="AX47" s="372" t="n">
-        <v>8.279822769881497</v>
+        <v>8.279822769881495</v>
       </c>
       <c r="AY47" s="382" t="n">
         <v>6.894488222567875</v>
@@ -11390,13 +11390,13 @@
         <v>25108.96630535545</v>
       </c>
       <c r="BD47" s="375" t="n">
-        <v>26678.26685355692</v>
+        <v>26678.26685355693</v>
       </c>
       <c r="BE47" s="375" t="n">
         <v>26025.02256328181</v>
       </c>
       <c r="BF47" s="392" t="n">
-        <v>26290.66972712829</v>
+        <v>26290.6697271283</v>
       </c>
       <c r="BG47" s="386" t="n">
         <v>34.04592333514582</v>
@@ -11411,7 +11411,7 @@
         <v>9.804260057147491</v>
       </c>
       <c r="BK47" s="387" t="n">
-        <v>8.34959865401378</v>
+        <v>8.349598654013782</v>
       </c>
       <c r="BL47" s="388" t="n">
         <v>33.46215704897577</v>
@@ -11434,13 +11434,13 @@
         </is>
       </c>
       <c r="BS47" s="391" t="n">
-        <v>30667.55188199004</v>
+        <v>30667.55188199002</v>
       </c>
       <c r="BT47" s="375" t="n">
-        <v>24979.6819168161</v>
+        <v>24979.68191681609</v>
       </c>
       <c r="BU47" s="375" t="n">
-        <v>26572.26338980347</v>
+        <v>26572.26338980346</v>
       </c>
       <c r="BV47" s="375" t="n">
         <v>25935.1542123835</v>
@@ -11452,31 +11452,31 @@
         <v>34.02109001396057</v>
       </c>
       <c r="BY47" s="372" t="n">
-        <v>12.96989060297969</v>
+        <v>12.96989060297968</v>
       </c>
       <c r="BZ47" s="372" t="n">
         <v>11.76792521437726</v>
       </c>
       <c r="CA47" s="372" t="n">
-        <v>9.721709973365764</v>
+        <v>9.72170997336576</v>
       </c>
       <c r="CB47" s="387" t="n">
-        <v>8.278048281095378</v>
+        <v>8.278048281095376</v>
       </c>
       <c r="CC47" s="388" t="n">
-        <v>33.50213681479684</v>
+        <v>33.50213681479683</v>
       </c>
       <c r="CD47" s="389" t="n">
-        <v>12.6510924769198</v>
+        <v>12.65109247691979</v>
       </c>
       <c r="CE47" s="389" t="n">
-        <v>11.32463567016474</v>
+        <v>11.32463567016473</v>
       </c>
       <c r="CF47" s="389" t="n">
-        <v>9.367809342615651</v>
+        <v>9.367809342615649</v>
       </c>
       <c r="CG47" s="390" t="n">
-        <v>8.003086610371973</v>
+        <v>8.003086610371971</v>
       </c>
     </row>
     <row r="48">
@@ -11486,7 +11486,7 @@
         </is>
       </c>
       <c r="C48" s="454" t="n">
-        <v>24017.87191294128</v>
+        <v>24017.87191294129</v>
       </c>
       <c r="D48" s="375" t="n">
         <v>20708.96112639768</v>
@@ -11501,13 +11501,13 @@
         <v>28412.3764402447</v>
       </c>
       <c r="H48" s="371" t="n">
-        <v>94.92008800030385</v>
+        <v>94.92008800030386</v>
       </c>
       <c r="I48" s="372" t="n">
         <v>48.78120631869076</v>
       </c>
       <c r="J48" s="372" t="n">
-        <v>48.61761759979124</v>
+        <v>48.61761759979122</v>
       </c>
       <c r="K48" s="372" t="n">
         <v>47.36635144520058</v>
@@ -11516,7 +11516,7 @@
         <v>43.87553385734083</v>
       </c>
       <c r="M48" s="371" t="n">
-        <v>86.68113106516144</v>
+        <v>86.68113106516145</v>
       </c>
       <c r="N48" s="372" t="n">
         <v>43.96589733391431</v>
@@ -11528,7 +11528,7 @@
         <v>41.96653063562768</v>
       </c>
       <c r="Q48" s="373" t="n">
-        <v>39.23009108195268</v>
+        <v>39.23009108195269</v>
       </c>
       <c r="S48" s="99" t="inlineStr">
         <is>
@@ -11536,7 +11536,7 @@
         </is>
       </c>
       <c r="T48" s="374" t="n">
-        <v>24017.87191294128</v>
+        <v>24017.87191294129</v>
       </c>
       <c r="U48" s="375" t="n">
         <v>20708.96112639768</v>
@@ -11551,13 +11551,13 @@
         <v>28412.3764402447</v>
       </c>
       <c r="Y48" s="377" t="n">
-        <v>94.92008800030385</v>
+        <v>94.92008800030386</v>
       </c>
       <c r="Z48" s="372" t="n">
         <v>48.78120631869076</v>
       </c>
       <c r="AA48" s="372" t="n">
-        <v>48.61761759979124</v>
+        <v>48.61761759979122</v>
       </c>
       <c r="AB48" s="372" t="n">
         <v>47.36635144520058</v>
@@ -11566,7 +11566,7 @@
         <v>43.87553385734083</v>
       </c>
       <c r="AD48" s="377" t="n">
-        <v>86.68113106516144</v>
+        <v>86.68113106516145</v>
       </c>
       <c r="AE48" s="372" t="n">
         <v>43.96589733391431</v>
@@ -11578,7 +11578,7 @@
         <v>41.96653063562768</v>
       </c>
       <c r="AH48" s="378" t="n">
-        <v>39.23009108195268</v>
+        <v>39.23009108195269</v>
       </c>
       <c r="AJ48" s="100" t="inlineStr">
         <is>
@@ -11622,13 +11622,13 @@
         <v>92.01294063005669</v>
       </c>
       <c r="AW48" s="372" t="n">
-        <v>94.90147229133727</v>
+        <v>94.90147229133726</v>
       </c>
       <c r="AX48" s="372" t="n">
         <v>97.99164516064249</v>
       </c>
       <c r="AY48" s="382" t="n">
-        <v>96.33824458909406</v>
+        <v>96.33824458909407</v>
       </c>
       <c r="BA48" s="101" t="inlineStr">
         <is>
@@ -11648,7 +11648,7 @@
         <v>29643.15629724725</v>
       </c>
       <c r="BF48" s="392" t="n">
-        <v>32883.58026505759</v>
+        <v>32883.58026505758</v>
       </c>
       <c r="BG48" s="386" t="n">
         <v>152.3006326144784</v>
@@ -11686,7 +11686,7 @@
         </is>
       </c>
       <c r="BS48" s="391" t="n">
-        <v>22940.07407560083</v>
+        <v>22940.07407560082</v>
       </c>
       <c r="BT48" s="375" t="n">
         <v>22102.16316829728</v>
@@ -11698,10 +11698,10 @@
         <v>29749.69103845297</v>
       </c>
       <c r="BW48" s="392" t="n">
-        <v>33066.4096521495</v>
+        <v>33066.40965214949</v>
       </c>
       <c r="BX48" s="386" t="n">
-        <v>152.1238573261689</v>
+        <v>152.1238573261688</v>
       </c>
       <c r="BY48" s="372" t="n">
         <v>125.5251222980276</v>
@@ -11738,7 +11738,7 @@
         </is>
       </c>
       <c r="C49" s="454" t="n">
-        <v>41248.29742286653</v>
+        <v>41248.29742286654</v>
       </c>
       <c r="D49" s="375" t="n">
         <v>43664.72019961729</v>
@@ -11747,10 +11747,10 @@
         <v>50822.11816509515</v>
       </c>
       <c r="F49" s="375" t="n">
-        <v>59754.71047330757</v>
+        <v>59754.71047330756</v>
       </c>
       <c r="G49" s="455" t="n">
-        <v>64504.55260009767</v>
+        <v>64504.55260009768</v>
       </c>
       <c r="H49" s="371" t="n">
         <v>171.3078726553709</v>
@@ -11762,10 +11762,10 @@
         <v>101.3718552237967</v>
       </c>
       <c r="K49" s="372" t="n">
-        <v>103.2578345471899</v>
+        <v>103.2578345471898</v>
       </c>
       <c r="L49" s="373" t="n">
-        <v>95.48469259495133</v>
+        <v>95.48469259495134</v>
       </c>
       <c r="M49" s="371" t="n">
         <v>160.2930480828327</v>
@@ -11780,7 +11780,7 @@
         <v>93.98944928724644</v>
       </c>
       <c r="Q49" s="373" t="n">
-        <v>86.71572107077294</v>
+        <v>86.71572107077296</v>
       </c>
       <c r="S49" s="109" t="inlineStr">
         <is>
@@ -11788,7 +11788,7 @@
         </is>
       </c>
       <c r="T49" s="374" t="n">
-        <v>41248.29742286653</v>
+        <v>41248.29742286654</v>
       </c>
       <c r="U49" s="375" t="n">
         <v>43664.72019961729</v>
@@ -11797,10 +11797,10 @@
         <v>50822.11816509515</v>
       </c>
       <c r="W49" s="375" t="n">
-        <v>59754.71047330757</v>
+        <v>59754.71047330756</v>
       </c>
       <c r="X49" s="376" t="n">
-        <v>64504.55260009767</v>
+        <v>64504.55260009768</v>
       </c>
       <c r="Y49" s="377" t="n">
         <v>171.3078726553709</v>
@@ -11812,10 +11812,10 @@
         <v>101.3718552237967</v>
       </c>
       <c r="AB49" s="372" t="n">
-        <v>103.2578345471899</v>
+        <v>103.2578345471898</v>
       </c>
       <c r="AC49" s="378" t="n">
-        <v>95.48469259495133</v>
+        <v>95.48469259495134</v>
       </c>
       <c r="AD49" s="377" t="n">
         <v>160.2930480828327</v>
@@ -11830,7 +11830,7 @@
         <v>93.98944928724644</v>
       </c>
       <c r="AH49" s="378" t="n">
-        <v>86.71572107077294</v>
+        <v>86.71572107077296</v>
       </c>
       <c r="AJ49" s="110" t="inlineStr">
         <is>
@@ -11847,7 +11847,7 @@
         <v>51131.5154401211</v>
       </c>
       <c r="AN49" s="375" t="n">
-        <v>59998.91900857079</v>
+        <v>59998.91900857078</v>
       </c>
       <c r="AO49" s="456" t="n">
         <v>64086.96718583906</v>
@@ -11859,7 +11859,7 @@
         <v>250.8278728569565</v>
       </c>
       <c r="AR49" s="372" t="n">
-        <v>278.6859489614708</v>
+        <v>278.6859489614707</v>
       </c>
       <c r="AS49" s="372" t="n">
         <v>303.8888485875138</v>
@@ -11877,7 +11877,7 @@
         <v>224.4658065062812</v>
       </c>
       <c r="AX49" s="372" t="n">
-        <v>235.7497136899115</v>
+        <v>235.7497136899114</v>
       </c>
       <c r="AY49" s="382" t="n">
         <v>223.8035373403563</v>
@@ -11888,13 +11888,13 @@
         </is>
       </c>
       <c r="BB49" s="391" t="n">
-        <v>42028.87492654035</v>
+        <v>42028.87492654036</v>
       </c>
       <c r="BC49" s="375" t="n">
-        <v>46713.26529316049</v>
+        <v>46713.26529316048</v>
       </c>
       <c r="BD49" s="375" t="n">
-        <v>55983.56159031232</v>
+        <v>55983.5615903123</v>
       </c>
       <c r="BE49" s="375" t="n">
         <v>67543.62403335913</v>
@@ -11909,7 +11909,7 @@
         <v>266.007969460573</v>
       </c>
       <c r="BI49" s="372" t="n">
-        <v>305.1314214676479</v>
+        <v>305.1314214676478</v>
       </c>
       <c r="BJ49" s="372" t="n">
         <v>342.1020657721074</v>
@@ -11918,13 +11918,13 @@
         <v>339.0800595356379</v>
       </c>
       <c r="BL49" s="386" t="n">
-        <v>276.7381345091047</v>
+        <v>276.7381345091048</v>
       </c>
       <c r="BM49" s="372" t="n">
         <v>228.7458763406424</v>
       </c>
       <c r="BN49" s="372" t="n">
-        <v>245.7661423741631</v>
+        <v>245.766142374163</v>
       </c>
       <c r="BO49" s="372" t="n">
         <v>265.3946152791319</v>
@@ -11944,7 +11944,7 @@
         <v>46847.03639177143</v>
       </c>
       <c r="BU49" s="375" t="n">
-        <v>56229.44997229111</v>
+        <v>56229.44997229109</v>
       </c>
       <c r="BV49" s="375" t="n">
         <v>67943.00763172934</v>
@@ -11959,7 +11959,7 @@
         <v>265.9565725352451</v>
       </c>
       <c r="BZ49" s="372" t="n">
-        <v>305.0816319309538</v>
+        <v>305.0816319309537</v>
       </c>
       <c r="CA49" s="372" t="n">
         <v>342.0506826546047</v>
@@ -11974,7 +11974,7 @@
         <v>229.4860248766726</v>
       </c>
       <c r="CE49" s="372" t="n">
-        <v>246.9271553681164</v>
+        <v>246.9271553681163</v>
       </c>
       <c r="CF49" s="372" t="n">
         <v>267.042832307091</v>
@@ -12190,25 +12190,25 @@
         </is>
       </c>
       <c r="BS50" s="419" t="n">
-        <v>755.2092654082581</v>
+        <v>755.2092654082578</v>
       </c>
       <c r="BT50" s="420" t="n">
-        <v>843.30953446993</v>
+        <v>843.3095344699296</v>
       </c>
       <c r="BU50" s="420" t="n">
-        <v>946.7796925421452</v>
+        <v>946.7796925421449</v>
       </c>
       <c r="BV50" s="420" t="n">
-        <v>1040.027194855269</v>
+        <v>1040.027194855268</v>
       </c>
       <c r="BW50" s="421" t="n">
-        <v>1140.017687397479</v>
+        <v>1140.017687397478</v>
       </c>
       <c r="BX50" s="416" t="n">
-        <v>87.48900391299664</v>
+        <v>87.48900391299662</v>
       </c>
       <c r="BY50" s="417" t="n">
-        <v>111.4725325224351</v>
+        <v>111.472532522435</v>
       </c>
       <c r="BZ50" s="417" t="n">
         <v>122.8834032376412</v>
@@ -12220,16 +12220,16 @@
         <v>140.1213658180463</v>
       </c>
       <c r="CC50" s="417" t="n">
-        <v>87.48900391299665</v>
+        <v>87.48900391299661</v>
       </c>
       <c r="CD50" s="417" t="n">
-        <v>111.4725325224351</v>
+        <v>111.472532522435</v>
       </c>
       <c r="CE50" s="417" t="n">
         <v>122.8834032376412</v>
       </c>
       <c r="CF50" s="417" t="n">
-        <v>131.5928964610476</v>
+        <v>131.5928964610475</v>
       </c>
       <c r="CG50" s="418" t="n">
         <v>140.1213658180463</v>
@@ -12263,7 +12263,7 @@
         <v>10.028512268339</v>
       </c>
       <c r="J51" s="427" t="n">
-        <v>9.376231943061763</v>
+        <v>9.376231943061761</v>
       </c>
       <c r="K51" s="427" t="n">
         <v>8.72741590426809</v>
@@ -12272,7 +12272,7 @@
         <v>7.750271164065368</v>
       </c>
       <c r="M51" s="427" t="n">
-        <v>28.9788796702568</v>
+        <v>28.97887967025681</v>
       </c>
       <c r="N51" s="427" t="n">
         <v>9.883547487939863</v>
@@ -12307,7 +12307,7 @@
         <v>116493.1585212238</v>
       </c>
       <c r="Y51" s="432" t="n">
-        <v>29.41131472835728</v>
+        <v>29.41131472835729</v>
       </c>
       <c r="Z51" s="433" t="n">
         <v>10.028512268339</v>
@@ -12316,10 +12316,10 @@
         <v>9.376231943061763</v>
       </c>
       <c r="AB51" s="433" t="n">
-        <v>8.72741590426809</v>
+        <v>8.727415904268089</v>
       </c>
       <c r="AC51" s="434" t="n">
-        <v>7.750271164065367</v>
+        <v>7.750271164065368</v>
       </c>
       <c r="AD51" s="433" t="n">
         <v>28.97887967025681</v>
@@ -12345,10 +12345,10 @@
         <v>93680.41222049405</v>
       </c>
       <c r="AL51" s="408" t="n">
-        <v>88967.52169600788</v>
+        <v>88967.5216960079</v>
       </c>
       <c r="AM51" s="408" t="n">
-        <v>99395.75144616292</v>
+        <v>99395.7514461629</v>
       </c>
       <c r="AN51" s="408" t="n">
         <v>110103.8168277293</v>
@@ -12360,19 +12360,19 @@
         <v>78.00917697526444</v>
       </c>
       <c r="AQ51" s="437" t="n">
-        <v>39.03332209323739</v>
+        <v>39.03332209323741</v>
       </c>
       <c r="AR51" s="437" t="n">
-        <v>37.96788269769812</v>
+        <v>37.96788269769811</v>
       </c>
       <c r="AS51" s="437" t="n">
         <v>36.06022643326553</v>
       </c>
       <c r="AT51" s="438" t="n">
-        <v>32.33298422897579</v>
+        <v>32.3329842289758</v>
       </c>
       <c r="AU51" s="437" t="n">
-        <v>74.32885705904914</v>
+        <v>74.32885705904916</v>
       </c>
       <c r="AV51" s="437" t="n">
         <v>36.88662619747279</v>
@@ -12392,10 +12392,10 @@
         </is>
       </c>
       <c r="BB51" s="439" t="n">
-        <v>96611.24087174266</v>
+        <v>96611.24087174267</v>
       </c>
       <c r="BC51" s="440" t="n">
-        <v>94768.06363341992</v>
+        <v>94768.06363341994</v>
       </c>
       <c r="BD51" s="440" t="n">
         <v>109203.2556298702</v>
@@ -12407,13 +12407,13 @@
         <v>134254.3041707362</v>
       </c>
       <c r="BG51" s="442" t="n">
-        <v>80.449724849897</v>
+        <v>80.44972484989701</v>
       </c>
       <c r="BH51" s="443" t="n">
-        <v>41.57823306121927</v>
+        <v>41.57823306121928</v>
       </c>
       <c r="BI51" s="443" t="n">
-        <v>41.71422158025966</v>
+        <v>41.71422158025965</v>
       </c>
       <c r="BJ51" s="443" t="n">
         <v>40.69595167795416</v>
@@ -12422,10 +12422,10 @@
         <v>37.39669064932712</v>
       </c>
       <c r="BL51" s="443" t="n">
-        <v>76.65426467329495</v>
+        <v>76.65426467329497</v>
       </c>
       <c r="BM51" s="443" t="n">
-        <v>39.29157598262211</v>
+        <v>39.29157598262212</v>
       </c>
       <c r="BN51" s="443" t="n">
         <v>38.61750253098985</v>
@@ -12442,10 +12442,10 @@
         </is>
       </c>
       <c r="BS51" s="439" t="n">
-        <v>96456.52564291804</v>
+        <v>96456.52564291802</v>
       </c>
       <c r="BT51" s="440" t="n">
-        <v>94772.19101135475</v>
+        <v>94772.19101135473</v>
       </c>
       <c r="BU51" s="440" t="n">
         <v>109389.7336532371</v>
@@ -12454,37 +12454,37 @@
         <v>124667.8800774211</v>
       </c>
       <c r="BW51" s="441" t="n">
-        <v>134907.0186081302</v>
+        <v>134907.0186081301</v>
       </c>
       <c r="BX51" s="416" t="n">
-        <v>80.63413706293828</v>
+        <v>80.63413706293825</v>
       </c>
       <c r="BY51" s="417" t="n">
         <v>41.46195029126793</v>
       </c>
       <c r="BZ51" s="417" t="n">
-        <v>41.61758158889122</v>
+        <v>41.61758158889121</v>
       </c>
       <c r="CA51" s="417" t="n">
-        <v>40.62070264877643</v>
+        <v>40.62070264877642</v>
       </c>
       <c r="CB51" s="418" t="n">
-        <v>37.3448777114288</v>
+        <v>37.34487771142879</v>
       </c>
       <c r="CC51" s="417" t="n">
-        <v>76.96929475903349</v>
+        <v>76.96929475903346</v>
       </c>
       <c r="CD51" s="417" t="n">
-        <v>39.30503884763296</v>
+        <v>39.30503884763295</v>
       </c>
       <c r="CE51" s="417" t="n">
-        <v>38.693307862986</v>
+        <v>38.69330786298599</v>
       </c>
       <c r="CF51" s="417" t="n">
         <v>37.79211035185904</v>
       </c>
       <c r="CG51" s="418" t="n">
-        <v>34.89609300366028</v>
+        <v>34.89609300366027</v>
       </c>
     </row>
     <row r="52">
@@ -13596,7 +13596,7 @@
         <v>108.83806653774</v>
       </c>
       <c r="BX58" s="197" t="n">
-        <v>901.4276694075818</v>
+        <v>901.4276694075817</v>
       </c>
       <c r="BY58" s="190" t="n">
         <v>1925.974758112246</v>
@@ -13611,7 +13611,7 @@
         <v>3167.861435796906</v>
       </c>
       <c r="CC58" s="199" t="n">
-        <v>915.3909212276018</v>
+        <v>915.3909212276017</v>
       </c>
       <c r="CD58" s="200" t="n">
         <v>1974.507890317626</v>
@@ -13653,19 +13653,19 @@
         <v>6817</v>
       </c>
       <c r="CW58" s="91" t="n">
-        <v>6.49266376239819</v>
+        <v>6.492663762398219</v>
       </c>
       <c r="CX58" s="92" t="n">
-        <v>0.5582212223740186</v>
+        <v>0.5582212223740207</v>
       </c>
       <c r="CY58" s="92" t="n">
-        <v>0.5560499977934452</v>
+        <v>0.5560499977934472</v>
       </c>
       <c r="CZ58" s="92" t="n">
-        <v>0.5496802400906832</v>
+        <v>0.5496802400906852</v>
       </c>
       <c r="DA58" s="93" t="n">
-        <v>0.5365263753544579</v>
+        <v>0.5365263753544597</v>
       </c>
       <c r="DC58" s="393" t="n">
         <v>0.006431830911075009</v>
@@ -13962,22 +13962,22 @@
         <v>12808</v>
       </c>
       <c r="CW59" s="102" t="n">
-        <v>0.4056209815029401</v>
+        <v>0.4056209815029412</v>
       </c>
       <c r="CX59" s="103" t="n">
-        <v>0.08078411315882889</v>
+        <v>0.08078411315882925</v>
       </c>
       <c r="CY59" s="103" t="n">
-        <v>0.08279381105870622</v>
+        <v>0.08279381105870662</v>
       </c>
       <c r="CZ59" s="103" t="n">
-        <v>0.08509236834521014</v>
+        <v>0.08509236834521057</v>
       </c>
       <c r="DA59" s="104" t="n">
-        <v>0.07410678027569523</v>
+        <v>0.07410678027569567</v>
       </c>
       <c r="DC59" s="396" t="n">
-        <v>0.002257409169499338</v>
+        <v>0.002257409169499339</v>
       </c>
       <c r="DD59" s="397" t="n">
         <v>0.000343546109869965</v>
@@ -14271,19 +14271,19 @@
         <v>8351</v>
       </c>
       <c r="CW60" s="102" t="n">
-        <v>0.2641001573489117</v>
+        <v>0.2641001573489154</v>
       </c>
       <c r="CX60" s="103" t="n">
-        <v>0.07572616131653595</v>
+        <v>0.07572616131653802</v>
       </c>
       <c r="CY60" s="103" t="n">
-        <v>0.07524928641776088</v>
+        <v>0.07524928641776313</v>
       </c>
       <c r="CZ60" s="103" t="n">
-        <v>0.07523867193467433</v>
+        <v>0.0752386719346768</v>
       </c>
       <c r="DA60" s="104" t="n">
-        <v>0.074729758622644</v>
+        <v>0.07472975862264647</v>
       </c>
       <c r="DC60" s="396" t="n">
         <v>0.001826142062889297</v>
@@ -14580,19 +14580,19 @@
         <v>948</v>
       </c>
       <c r="CW61" s="132" t="n">
-        <v>0.006234181061802669</v>
+        <v>0.006234181061802624</v>
       </c>
       <c r="CX61" s="133" t="n">
-        <v>0.006396145085788303</v>
+        <v>0.006396145085788257</v>
       </c>
       <c r="CY61" s="133" t="n">
-        <v>0.006590523934945409</v>
+        <v>0.00659052393494536</v>
       </c>
       <c r="CZ61" s="133" t="n">
-        <v>0.006724179760346102</v>
+        <v>0.006724179760346054</v>
       </c>
       <c r="DA61" s="134" t="n">
-        <v>0.006860546125885921</v>
+        <v>0.006860546125885872</v>
       </c>
       <c r="DC61" s="422" t="n">
         <v>0</v>
@@ -14717,7 +14717,7 @@
         </is>
       </c>
       <c r="AK62" s="220" t="n">
-        <v>59.46086383000001</v>
+        <v>59.46086382999999</v>
       </c>
       <c r="AL62" s="209" t="n">
         <v>132.64704174</v>
@@ -14767,7 +14767,7 @@
         </is>
       </c>
       <c r="BB62" s="221" t="n">
-        <v>59.46086383000001</v>
+        <v>59.46086382999999</v>
       </c>
       <c r="BC62" s="222" t="n">
         <v>132.64704174</v>
@@ -14817,7 +14817,7 @@
         </is>
       </c>
       <c r="BS62" s="221" t="n">
-        <v>56.95743939234</v>
+        <v>56.95743939234001</v>
       </c>
       <c r="BT62" s="222" t="n">
         <v>125.43400213578</v>
@@ -14844,7 +14844,7 @@
         <v>3069.072466701319</v>
       </c>
       <c r="CB62" s="214" t="n">
-        <v>3612.463793577881</v>
+        <v>3612.463793577882</v>
       </c>
       <c r="CC62" s="222" t="n">
         <v>1253.181881747688</v>
@@ -14859,7 +14859,7 @@
         <v>3298.780589829869</v>
       </c>
       <c r="CG62" s="214" t="n">
-        <v>3865.963407249621</v>
+        <v>3865.963407249622</v>
       </c>
       <c r="CI62" s="349" t="n">
         <v>0</v>
@@ -14889,19 +14889,19 @@
         <v>28924</v>
       </c>
       <c r="CW62" s="132" t="n">
-        <v>7.168619082311845</v>
+        <v>7.168619082311878</v>
       </c>
       <c r="CX62" s="133" t="n">
-        <v>0.7211276419351718</v>
+        <v>0.7211276419351762</v>
       </c>
       <c r="CY62" s="133" t="n">
-        <v>0.7206836192048578</v>
+        <v>0.7206836192048623</v>
       </c>
       <c r="CZ62" s="133" t="n">
-        <v>0.7167354601309137</v>
+        <v>0.7167354601309186</v>
       </c>
       <c r="DA62" s="134" t="n">
-        <v>0.692223460378683</v>
+        <v>0.6922234603786876</v>
       </c>
     </row>
     <row r="63" ht="15.75" customHeight="1" thickBot="1">
@@ -15754,25 +15754,25 @@
         </is>
       </c>
       <c r="BS67" s="236" t="n">
-        <v>755.3202508115063</v>
+        <v>755.3202508115062</v>
       </c>
       <c r="BT67" s="237" t="n">
         <v>56.33223463137914</v>
       </c>
       <c r="BU67" s="237" t="n">
-        <v>55.65626850157529</v>
+        <v>55.6562685015753</v>
       </c>
       <c r="BV67" s="237" t="n">
-        <v>51.23859989215605</v>
+        <v>51.23859989215606</v>
       </c>
       <c r="BW67" s="238" t="n">
         <v>45.51792185462426</v>
       </c>
       <c r="BX67" s="462" t="n">
-        <v>0.8324179598605017</v>
+        <v>0.8324179598605016</v>
       </c>
       <c r="BY67" s="463" t="n">
-        <v>0.02904908370918016</v>
+        <v>0.02904908370918015</v>
       </c>
       <c r="BZ67" s="463" t="n">
         <v>0.02450483665090967</v>
@@ -15781,13 +15781,13 @@
         <v>0.01910076030576746</v>
       </c>
       <c r="CB67" s="464" t="n">
-        <v>0.01428902418466365</v>
+        <v>0.01428902418466364</v>
       </c>
       <c r="CC67" s="199" t="n">
-        <v>750.3645815300661</v>
+        <v>750.3645815300658</v>
       </c>
       <c r="CD67" s="200" t="n">
-        <v>55.94780197017064</v>
+        <v>55.94780197017062</v>
       </c>
       <c r="CE67" s="200" t="n">
         <v>55.33252140458465</v>
@@ -15796,7 +15796,7 @@
         <v>50.95617596709133</v>
       </c>
       <c r="CG67" s="201" t="n">
-        <v>45.26564866976531</v>
+        <v>45.26564866976528</v>
       </c>
       <c r="CW67" s="465" t="n"/>
       <c r="CX67" s="465" t="n"/>
@@ -16017,7 +16017,7 @@
         </is>
       </c>
       <c r="BS68" s="236" t="n">
-        <v>51.13856851003995</v>
+        <v>51.13856851003994</v>
       </c>
       <c r="BT68" s="237" t="n">
         <v>16.0958098959233</v>
@@ -16032,22 +16032,22 @@
         <v>19.75993719002158</v>
       </c>
       <c r="BX68" s="462" t="n">
-        <v>0.3372284849560063</v>
+        <v>0.3372284849560062</v>
       </c>
       <c r="BY68" s="463" t="n">
         <v>0.09130608387099554</v>
       </c>
       <c r="BZ68" s="463" t="n">
-        <v>0.09766948450038207</v>
+        <v>0.0976694845003821</v>
       </c>
       <c r="CA68" s="463" t="n">
         <v>0.09748899078933781</v>
       </c>
       <c r="CB68" s="464" t="n">
-        <v>0.091558827428478</v>
+        <v>0.09155882742847801</v>
       </c>
       <c r="CC68" s="197" t="n">
-        <v>50.85360417009778</v>
+        <v>50.85360417009777</v>
       </c>
       <c r="CD68" s="190" t="n">
         <v>16.07695676395043</v>
@@ -16059,7 +16059,7 @@
         <v>18.9887445413396</v>
       </c>
       <c r="CG68" s="198" t="n">
-        <v>19.848396644392</v>
+        <v>19.84839664439201</v>
       </c>
       <c r="CW68" s="465" t="n"/>
       <c r="CX68" s="465" t="n"/>
@@ -16283,46 +16283,46 @@
         <v>84.40848126919825</v>
       </c>
       <c r="BT69" s="237" t="n">
-        <v>46.47854001102073</v>
+        <v>46.47854001102072</v>
       </c>
       <c r="BU69" s="237" t="n">
-        <v>50.4514222620171</v>
+        <v>50.45142226201709</v>
       </c>
       <c r="BV69" s="237" t="n">
-        <v>55.51399834326028</v>
+        <v>55.51399834326029</v>
       </c>
       <c r="BW69" s="238" t="n">
-        <v>55.46093120356361</v>
+        <v>55.4609312035636</v>
       </c>
       <c r="BX69" s="462" t="n">
-        <v>0.6230057710226438</v>
+        <v>0.6230057710226437</v>
       </c>
       <c r="BY69" s="463" t="n">
         <v>0.2643552069928728</v>
       </c>
       <c r="BZ69" s="463" t="n">
-        <v>0.2746831767837289</v>
+        <v>0.2746831767837288</v>
       </c>
       <c r="CA69" s="463" t="n">
         <v>0.2809008726198391</v>
       </c>
       <c r="CB69" s="464" t="n">
-        <v>0.2541075764162453</v>
+        <v>0.2541075764162452</v>
       </c>
       <c r="CC69" s="197" t="n">
-        <v>84.33383880616788</v>
+        <v>84.33383880616786</v>
       </c>
       <c r="CD69" s="190" t="n">
         <v>46.56496316032273</v>
       </c>
       <c r="CE69" s="190" t="n">
-        <v>50.62672521263509</v>
+        <v>50.62672521263508</v>
       </c>
       <c r="CF69" s="190" t="n">
         <v>55.79655618299417</v>
       </c>
       <c r="CG69" s="198" t="n">
-        <v>55.82322507877655</v>
+        <v>55.82322507877652</v>
       </c>
       <c r="CW69" s="465" t="n"/>
       <c r="CX69" s="465" t="n"/>
@@ -16724,7 +16724,7 @@
         <v>2.50342443766</v>
       </c>
       <c r="AQ71" s="207" t="n">
-        <v>7.213039604219999</v>
+        <v>7.21303960422</v>
       </c>
       <c r="AR71" s="207" t="n">
         <v>11.28042547872</v>
@@ -16774,7 +16774,7 @@
         <v>2.50342443766</v>
       </c>
       <c r="BH71" s="222" t="n">
-        <v>7.213039604219999</v>
+        <v>7.21303960422</v>
       </c>
       <c r="BI71" s="222" t="n">
         <v>11.28042547872</v>
@@ -16806,7 +16806,7 @@
         </is>
       </c>
       <c r="BS71" s="271" t="n">
-        <v>893.0380461265416</v>
+        <v>893.0380461265415</v>
       </c>
       <c r="BT71" s="272" t="n">
         <v>121.1337260431404</v>
@@ -16821,22 +16821,22 @@
         <v>123.1276364700726</v>
       </c>
       <c r="BX71" s="466" t="n">
-        <v>0.7420986433893346</v>
+        <v>0.7420986433893343</v>
       </c>
       <c r="BY71" s="467" t="n">
-        <v>0.0528534534709378</v>
+        <v>0.05285345347093779</v>
       </c>
       <c r="BZ71" s="467" t="n">
-        <v>0.04781252069995717</v>
+        <v>0.04781252069995718</v>
       </c>
       <c r="CA71" s="467" t="n">
         <v>0.04173121269501602</v>
       </c>
       <c r="CB71" s="468" t="n">
-        <v>0.03413716042992708</v>
+        <v>0.03413716042992706</v>
       </c>
       <c r="CC71" s="212" t="n">
-        <v>887.7165358610671</v>
+        <v>887.7165358610669</v>
       </c>
       <c r="CD71" s="212" t="n">
         <v>120.8104672541753</v>
@@ -18557,13 +18557,13 @@
         <v>181.719816238</v>
       </c>
       <c r="H80" s="495" t="n">
-        <v>0.01470301692033978</v>
+        <v>0.01470301692033977</v>
       </c>
       <c r="I80" s="495" t="n">
         <v>0.01445526280670818</v>
       </c>
       <c r="J80" s="495" t="n">
-        <v>0.01919454004357722</v>
+        <v>0.01919454004357723</v>
       </c>
       <c r="K80" s="495" t="n">
         <v>0.01894119589469867</v>
@@ -18575,7 +18575,7 @@
         <v>0.01270752050175844</v>
       </c>
       <c r="N80" s="495" t="n">
-        <v>0.01145779712646461</v>
+        <v>0.01145779712646462</v>
       </c>
       <c r="O80" s="495" t="n">
         <v>0.01519740279998345</v>
@@ -18607,13 +18607,13 @@
         <v>181.719816238</v>
       </c>
       <c r="Y80" s="497" t="n">
-        <v>0.01470301692033978</v>
+        <v>0.01470301692033977</v>
       </c>
       <c r="Z80" s="498" t="n">
         <v>0.01445526280670818</v>
       </c>
       <c r="AA80" s="498" t="n">
-        <v>0.01919454004357722</v>
+        <v>0.01919454004357723</v>
       </c>
       <c r="AB80" s="498" t="n">
         <v>0.01894119589469867</v>
@@ -18625,7 +18625,7 @@
         <v>0.01270752050175844</v>
       </c>
       <c r="AE80" s="498" t="n">
-        <v>0.01145779712646461</v>
+        <v>0.01145779712646462</v>
       </c>
       <c r="AF80" s="498" t="n">
         <v>0.01519740279998345</v>
@@ -18642,7 +18642,7 @@
         </is>
       </c>
       <c r="AK80" s="206" t="n">
-        <v>56.95743939234</v>
+        <v>56.95743939234001</v>
       </c>
       <c r="AL80" s="207" t="n">
         <v>125.43400213578</v>
@@ -18669,19 +18669,19 @@
         <v>0.07460714012500795</v>
       </c>
       <c r="AT80" s="502" t="n">
-        <v>0.07154779663147842</v>
+        <v>0.07154779663147844</v>
       </c>
       <c r="AU80" s="501" t="n">
-        <v>0.04519174575233703</v>
+        <v>0.04519174575233705</v>
       </c>
       <c r="AV80" s="501" t="n">
-        <v>0.052005912506419</v>
+        <v>0.05200591250641899</v>
       </c>
       <c r="AW80" s="501" t="n">
         <v>0.07024743746163575</v>
       </c>
       <c r="AX80" s="501" t="n">
-        <v>0.06961912694030155</v>
+        <v>0.06961912694030156</v>
       </c>
       <c r="AY80" s="502" t="n">
         <v>0.06556043203288629</v>
@@ -18692,7 +18692,7 @@
         </is>
       </c>
       <c r="BB80" s="221" t="n">
-        <v>56.95743939234</v>
+        <v>56.95743939234001</v>
       </c>
       <c r="BC80" s="222" t="n">
         <v>125.43400213578</v>
@@ -18719,19 +18719,19 @@
         <v>0.07460714012500795</v>
       </c>
       <c r="BK80" s="505" t="n">
-        <v>0.07154779663147842</v>
+        <v>0.07154779663147844</v>
       </c>
       <c r="BL80" s="504" t="n">
-        <v>0.04519174575233703</v>
+        <v>0.04519174575233705</v>
       </c>
       <c r="BM80" s="504" t="n">
-        <v>0.052005912506419</v>
+        <v>0.05200591250641899</v>
       </c>
       <c r="BN80" s="504" t="n">
         <v>0.07024743746163575</v>
       </c>
       <c r="BO80" s="504" t="n">
-        <v>0.06961912694030155</v>
+        <v>0.06961912694030156</v>
       </c>
       <c r="BP80" s="505" t="n">
         <v>0.06556043203288629</v>
@@ -18766,7 +18766,7 @@
         <v>0.07026534493983633</v>
       </c>
       <c r="CA80" s="504" t="n">
-        <v>0.06963425328642329</v>
+        <v>0.06963425328642332</v>
       </c>
       <c r="CB80" s="505" t="n">
         <v>0.0655721710134055</v>
@@ -20211,7 +20211,7 @@
         </is>
       </c>
       <c r="AK91" s="435" t="n">
-        <v>80794.97273624</v>
+        <v>80794.97273623999</v>
       </c>
       <c r="AL91" s="408" t="n">
         <v>174399.72519538</v>
@@ -20246,7 +20246,7 @@
         </is>
       </c>
       <c r="BB91" s="439" t="n">
-        <v>80794.97273624</v>
+        <v>80794.97273623999</v>
       </c>
       <c r="BC91" s="440" t="n">
         <v>174399.72519538</v>
@@ -20293,7 +20293,7 @@
         <v>296783.1091025257</v>
       </c>
       <c r="BW91" s="441" t="n">
-        <v>341201.7996301624</v>
+        <v>341201.7996301625</v>
       </c>
       <c r="BX91" s="442" t="n">
         <v>1380.495149088613</v>
@@ -20993,10 +20993,10 @@
         <v>57819.84417732574</v>
       </c>
       <c r="AW96" s="375" t="n">
-        <v>60662.44851795744</v>
+        <v>60662.44851795745</v>
       </c>
       <c r="AX96" s="375" t="n">
-        <v>60011.32023524767</v>
+        <v>60011.32023524766</v>
       </c>
       <c r="AY96" s="456" t="n">
         <v>59334.37238636029</v>
@@ -21087,19 +21087,19 @@
         <v>0</v>
       </c>
       <c r="DC96" s="391" t="n">
-        <v>242214.1477819244</v>
+        <v>242214.1477819243</v>
       </c>
       <c r="DD96" s="375" t="n">
-        <v>45650.81714687881</v>
+        <v>45650.81714687879</v>
       </c>
       <c r="DE96" s="375" t="n">
-        <v>48240.88012252496</v>
+        <v>48240.88012252494</v>
       </c>
       <c r="DF96" s="375" t="n">
-        <v>47894.66624533238</v>
+        <v>47894.66624533237</v>
       </c>
       <c r="DG96" s="392" t="n">
-        <v>47466.23510528405</v>
+        <v>47466.23510528402</v>
       </c>
       <c r="DI96" s="368" t="n"/>
       <c r="DJ96" s="368" t="n"/>
@@ -21314,7 +21314,7 @@
         <v>0</v>
       </c>
       <c r="DC97" s="391" t="n">
-        <v>63581.39137306156</v>
+        <v>63581.39137306155</v>
       </c>
       <c r="DD97" s="375" t="n">
         <v>36840.47335043464</v>
@@ -21323,10 +21323,10 @@
         <v>41783.40242300271</v>
       </c>
       <c r="DF97" s="375" t="n">
-        <v>47538.68160722342</v>
+        <v>47538.68160722341</v>
       </c>
       <c r="DG97" s="392" t="n">
-        <v>52637.13038052491</v>
+        <v>52637.1303805249</v>
       </c>
       <c r="DI97" s="368" t="n"/>
       <c r="DJ97" s="368" t="n"/>
@@ -21444,16 +21444,16 @@
         <v>209859.9122092853</v>
       </c>
       <c r="AV98" s="375" t="n">
-        <v>109522.0380868603</v>
+        <v>109522.0380868604</v>
       </c>
       <c r="AW98" s="375" t="n">
         <v>126384.8968960265</v>
       </c>
       <c r="AX98" s="375" t="n">
-        <v>147026.8981883551</v>
+        <v>147026.8981883552</v>
       </c>
       <c r="AY98" s="456" t="n">
-        <v>161259.4019061703</v>
+        <v>161259.4019061702</v>
       </c>
       <c r="BA98" s="111" t="inlineStr">
         <is>
@@ -21768,19 +21768,19 @@
         <v>0</v>
       </c>
       <c r="DC99" s="419" t="n">
-        <v>4415.54584678577</v>
+        <v>4415.545846785769</v>
       </c>
       <c r="DD99" s="420" t="n">
-        <v>4762.243435349772</v>
+        <v>4762.243435349771</v>
       </c>
       <c r="DE99" s="420" t="n">
         <v>5162.60207409034</v>
       </c>
       <c r="DF99" s="420" t="n">
-        <v>5542.300576123017</v>
+        <v>5542.300576123015</v>
       </c>
       <c r="DG99" s="421" t="n">
-        <v>5946.33072039547</v>
+        <v>5946.330720395468</v>
       </c>
       <c r="DI99" s="368" t="n"/>
       <c r="DJ99" s="368" t="n"/>
@@ -21877,7 +21877,7 @@
         <v>4904903.359693</v>
       </c>
       <c r="AO100" s="409" t="n">
-        <v>5759810.437133</v>
+        <v>5759810.437132999</v>
       </c>
       <c r="AP100" s="436" t="n">
         <v>1712.566137457642</v>
@@ -21904,7 +21904,7 @@
         <v>242827.0115175217</v>
       </c>
       <c r="AX100" s="408" t="n">
-        <v>270024.4103171414</v>
+        <v>270024.4103171416</v>
       </c>
       <c r="AY100" s="409" t="n">
         <v>290024.5766233449</v>
@@ -21927,7 +21927,7 @@
         <v>4904903.359693</v>
       </c>
       <c r="BF100" s="441" t="n">
-        <v>5759810.437133</v>
+        <v>5759810.437132999</v>
       </c>
       <c r="BG100" s="442" t="n">
         <v>1712.566137457642</v>
@@ -21965,7 +21965,7 @@
         <v>5795026.489558407</v>
       </c>
       <c r="BX100" s="442" t="n">
-        <v>1714.363444216887</v>
+        <v>1714.363444216886</v>
       </c>
       <c r="BY100" s="443" t="n">
         <v>1594.095643271079</v>
@@ -21997,7 +21997,7 @@
         <v>0</v>
       </c>
       <c r="DC100" s="439" t="n">
-        <v>414274.0719449044</v>
+        <v>414274.0719449043</v>
       </c>
       <c r="DD100" s="440" t="n">
         <v>185369.1882893765</v>
@@ -22006,10 +22006,10 @@
         <v>213077.5907853029</v>
       </c>
       <c r="DF100" s="440" t="n">
-        <v>244468.1330571697</v>
+        <v>244468.1330571696</v>
       </c>
       <c r="DG100" s="441" t="n">
-        <v>273588.5049591262</v>
+        <v>273588.5049591261</v>
       </c>
       <c r="DI100" s="368" t="n"/>
       <c r="DJ100" s="368" t="n"/>
@@ -23081,13 +23081,13 @@
         <v>0</v>
       </c>
       <c r="BX108" s="197" t="n">
-        <v>23.94490471180372</v>
+        <v>23.94490471180375</v>
       </c>
       <c r="BY108" s="190" t="n">
         <v>17.77149025158941</v>
       </c>
       <c r="BZ108" s="190" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="CA108" s="190" t="n">
         <v>17.291081220829</v>
@@ -23096,13 +23096,13 @@
         <v>17.05692206673462</v>
       </c>
       <c r="CC108" s="199" t="n">
-        <v>23.94490471180372</v>
+        <v>23.94490471180375</v>
       </c>
       <c r="CD108" s="200" t="n">
         <v>17.77149025158941</v>
       </c>
       <c r="CE108" s="200" t="n">
-        <v>17.53795164492137</v>
+        <v>17.53795164492138</v>
       </c>
       <c r="CF108" s="200" t="n">
         <v>17.291081220829</v>
@@ -23138,19 +23138,19 @@
         <v>500</v>
       </c>
       <c r="CW108" s="199" t="n">
-        <v>6.49266376239819</v>
+        <v>6.492663762398219</v>
       </c>
       <c r="CX108" s="200" t="n">
-        <v>0.5582212223740186</v>
+        <v>0.5582212223740207</v>
       </c>
       <c r="CY108" s="200" t="n">
-        <v>0.5560499977934452</v>
+        <v>0.5560499977934472</v>
       </c>
       <c r="CZ108" s="200" t="n">
-        <v>0.5496802400906832</v>
+        <v>0.5496802400906852</v>
       </c>
       <c r="DA108" s="201" t="n">
-        <v>0.5365263753544579</v>
+        <v>0.5365263753544597</v>
       </c>
     </row>
     <row r="109">
@@ -23433,19 +23433,19 @@
         <v>1332</v>
       </c>
       <c r="CW109" s="197" t="n">
-        <v>0.4056209815029401</v>
+        <v>0.4056209815029412</v>
       </c>
       <c r="CX109" s="190" t="n">
-        <v>0.08078411315882889</v>
+        <v>0.08078411315882925</v>
       </c>
       <c r="CY109" s="190" t="n">
-        <v>0.08279381105870622</v>
+        <v>0.08279381105870662</v>
       </c>
       <c r="CZ109" s="190" t="n">
-        <v>0.08509236834521014</v>
+        <v>0.08509236834521057</v>
       </c>
       <c r="DA109" s="198" t="n">
-        <v>0.07410678027569523</v>
+        <v>0.07410678027569567</v>
       </c>
     </row>
     <row r="110">
@@ -23671,7 +23671,7 @@
         <v>0</v>
       </c>
       <c r="BX110" s="197" t="n">
-        <v>81.16527501751193</v>
+        <v>81.16527501751195</v>
       </c>
       <c r="BY110" s="190" t="n">
         <v>80.4491340264793</v>
@@ -23683,10 +23683,10 @@
         <v>81.28160965353055</v>
       </c>
       <c r="CB110" s="198" t="n">
-        <v>83.42484193069403</v>
+        <v>83.42484193069404</v>
       </c>
       <c r="CC110" s="197" t="n">
-        <v>81.16527501751193</v>
+        <v>81.16527501751195</v>
       </c>
       <c r="CD110" s="190" t="n">
         <v>80.4491340264793</v>
@@ -23698,7 +23698,7 @@
         <v>81.28160965353055</v>
       </c>
       <c r="CG110" s="198" t="n">
-        <v>83.42484193069403</v>
+        <v>83.42484193069404</v>
       </c>
       <c r="CI110" s="197" t="n">
         <v>0</v>
@@ -23728,19 +23728,19 @@
         <v>7464</v>
       </c>
       <c r="CW110" s="197" t="n">
-        <v>0.2641001573489117</v>
+        <v>0.2641001573489154</v>
       </c>
       <c r="CX110" s="190" t="n">
-        <v>0.07572616131653595</v>
+        <v>0.07572616131653802</v>
       </c>
       <c r="CY110" s="190" t="n">
-        <v>0.07524928641776088</v>
+        <v>0.07524928641776313</v>
       </c>
       <c r="CZ110" s="190" t="n">
-        <v>0.07523867193467433</v>
+        <v>0.0752386719346768</v>
       </c>
       <c r="DA110" s="198" t="n">
-        <v>0.074729758622644</v>
+        <v>0.07472975862264647</v>
       </c>
     </row>
     <row r="111" ht="15.75" customHeight="1" thickBot="1">
@@ -24023,19 +24023,19 @@
         <v>1590</v>
       </c>
       <c r="CW111" s="211" t="n">
-        <v>0.006234181061802669</v>
+        <v>0.006234181061802624</v>
       </c>
       <c r="CX111" s="212" t="n">
-        <v>0.006396145085788303</v>
+        <v>0.006396145085788257</v>
       </c>
       <c r="CY111" s="212" t="n">
-        <v>0.006590523934945409</v>
+        <v>0.00659052393494536</v>
       </c>
       <c r="CZ111" s="212" t="n">
-        <v>0.006724179760346102</v>
+        <v>0.006724179760346054</v>
       </c>
       <c r="DA111" s="213" t="n">
-        <v>0.006860546125885921</v>
+        <v>0.006860546125885872</v>
       </c>
     </row>
     <row r="112" ht="15.75" customHeight="1" thickBot="1">
@@ -24176,7 +24176,7 @@
         <v>126.0462685012848</v>
       </c>
       <c r="AU112" s="207" t="n">
-        <v>139.8581946663783</v>
+        <v>139.8581946663784</v>
       </c>
       <c r="AV112" s="207" t="n">
         <v>140.5583731904682</v>
@@ -24226,7 +24226,7 @@
         <v>126.0462685012848</v>
       </c>
       <c r="BL112" s="222" t="n">
-        <v>139.8581946663783</v>
+        <v>139.8581946663784</v>
       </c>
       <c r="BM112" s="222" t="n">
         <v>140.5583731904682</v>
@@ -24261,7 +24261,7 @@
         <v>17.670807431792</v>
       </c>
       <c r="BX112" s="221" t="n">
-        <v>141.6347756783579</v>
+        <v>141.634775678358</v>
       </c>
       <c r="BY112" s="222" t="n">
         <v>134.353273158068</v>
@@ -24318,19 +24318,19 @@
         <v>10886</v>
       </c>
       <c r="CW112" s="211" t="n">
-        <v>7.168619082311845</v>
+        <v>7.168619082311878</v>
       </c>
       <c r="CX112" s="212" t="n">
-        <v>0.7211276419351718</v>
+        <v>0.7211276419351762</v>
       </c>
       <c r="CY112" s="212" t="n">
-        <v>0.7206836192048578</v>
+        <v>0.7206836192048623</v>
       </c>
       <c r="CZ112" s="212" t="n">
-        <v>0.7167354601309137</v>
+        <v>0.7167354601309186</v>
       </c>
       <c r="DA112" s="213" t="n">
-        <v>0.692223460378683</v>
+        <v>0.6922234603786876</v>
       </c>
     </row>
     <row r="113" ht="15.75" customHeight="1" thickBot="1">
@@ -25701,28 +25701,28 @@
         <v>15.05560425447307</v>
       </c>
       <c r="BX119" s="515" t="n">
-        <v>0.04532650984064428</v>
+        <v>0.04532650984064425</v>
       </c>
       <c r="BY119" s="461" t="n">
-        <v>0.06738687802945346</v>
+        <v>0.06738687802945344</v>
       </c>
       <c r="BZ119" s="461" t="n">
-        <v>0.09468260417601468</v>
+        <v>0.09468260417601465</v>
       </c>
       <c r="CA119" s="461" t="n">
-        <v>0.1316235095328877</v>
+        <v>0.1316235095328876</v>
       </c>
       <c r="CB119" s="516" t="n">
         <v>0.1798955953329979</v>
       </c>
       <c r="CC119" s="197" t="n">
-        <v>3.678938636799854</v>
+        <v>3.678938636799852</v>
       </c>
       <c r="CD119" s="190" t="n">
-        <v>5.421215982217515</v>
+        <v>5.421215982217513</v>
       </c>
       <c r="CE119" s="190" t="n">
-        <v>7.620431052461177</v>
+        <v>7.620431052461175</v>
       </c>
       <c r="CF119" s="190" t="n">
         <v>10.69857072307993</v>
@@ -26205,28 +26205,28 @@
         <v>15.05560425447307</v>
       </c>
       <c r="BX121" s="466" t="n">
-        <v>0.02597482588001164</v>
+        <v>0.02597482588001162</v>
       </c>
       <c r="BY121" s="467" t="n">
-        <v>0.0403504570807099</v>
+        <v>0.04035045708070988</v>
       </c>
       <c r="BZ121" s="467" t="n">
-        <v>0.05948772547001616</v>
+        <v>0.05948772547001615</v>
       </c>
       <c r="CA121" s="467" t="n">
-        <v>0.08530987132632697</v>
+        <v>0.08530987132632693</v>
       </c>
       <c r="CB121" s="468" t="n">
         <v>0.1182337294927281</v>
       </c>
       <c r="CC121" s="212" t="n">
-        <v>3.678938636799854</v>
+        <v>3.678938636799852</v>
       </c>
       <c r="CD121" s="212" t="n">
-        <v>5.421215982217515</v>
+        <v>5.421215982217513</v>
       </c>
       <c r="CE121" s="212" t="n">
-        <v>7.620431052461177</v>
+        <v>7.620431052461175</v>
       </c>
       <c r="CF121" s="212" t="n">
         <v>10.69857072307993</v>
@@ -27923,7 +27923,7 @@
         <v>0.1241408936973136</v>
       </c>
       <c r="M130" s="495" t="n">
-        <v>0.03855360841168162</v>
+        <v>0.03855360841168161</v>
       </c>
       <c r="N130" s="495" t="n">
         <v>0.04927652132790298</v>
@@ -27973,7 +27973,7 @@
         <v>0.1241408936973136</v>
       </c>
       <c r="AD130" s="498" t="n">
-        <v>0.03855360841168162</v>
+        <v>0.03855360841168161</v>
       </c>
       <c r="AE130" s="498" t="n">
         <v>0.04927652132790298</v>
@@ -28023,7 +28023,7 @@
         <v>0.1241408936973136</v>
       </c>
       <c r="AU130" s="501" t="n">
-        <v>0.03855360841168162</v>
+        <v>0.03855360841168161</v>
       </c>
       <c r="AV130" s="501" t="n">
         <v>0.04927652132790297</v>
@@ -28073,7 +28073,7 @@
         <v>0.1241408936973136</v>
       </c>
       <c r="BL130" s="504" t="n">
-        <v>0.03855360841168162</v>
+        <v>0.03855360841168161</v>
       </c>
       <c r="BM130" s="504" t="n">
         <v>0.04927652132790297</v>
@@ -28108,7 +28108,7 @@
         <v>0</v>
       </c>
       <c r="BX130" s="503" t="n">
-        <v>0.03667384154531693</v>
+        <v>0.03667384154531692</v>
       </c>
       <c r="BY130" s="504" t="n">
         <v>0.04902500103360271</v>
@@ -30296,49 +30296,49 @@
         </is>
       </c>
       <c r="BS146" s="391" t="n">
-        <v>11005.84284113696</v>
+        <v>11005.84284113699</v>
       </c>
       <c r="BT146" s="375" t="n">
-        <v>3971.299184686872</v>
+        <v>3971.299184686875</v>
       </c>
       <c r="BU146" s="375" t="n">
-        <v>4027.733979729947</v>
+        <v>4027.73397972995</v>
       </c>
       <c r="BV146" s="375" t="n">
-        <v>4067.985565483056</v>
+        <v>4067.985565483059</v>
       </c>
       <c r="BW146" s="392" t="n">
-        <v>4100.881810581043</v>
+        <v>4100.881810581046</v>
       </c>
       <c r="BX146" s="386" t="n">
-        <v>459.6319331231913</v>
+        <v>459.6319331231922</v>
       </c>
       <c r="BY146" s="372" t="n">
-        <v>223.4646126163615</v>
+        <v>223.4646126163617</v>
       </c>
       <c r="BZ146" s="372" t="n">
-        <v>229.6581756682112</v>
+        <v>229.6581756682114</v>
       </c>
       <c r="CA146" s="372" t="n">
-        <v>235.2649619494426</v>
+        <v>235.2649619494427</v>
       </c>
       <c r="CB146" s="387" t="n">
-        <v>240.4233187286947</v>
+        <v>240.4233187286949</v>
       </c>
       <c r="CW146" s="511" t="n">
-        <v>7800.981532165267</v>
+        <v>7800.981532165301</v>
       </c>
       <c r="CX146" s="512" t="n">
-        <v>716.9772907122674</v>
+        <v>716.9772907122701</v>
       </c>
       <c r="CY146" s="512" t="n">
-        <v>726.0615485215986</v>
+        <v>726.0615485216013</v>
       </c>
       <c r="CZ146" s="512" t="n">
-        <v>722.975259170675</v>
+        <v>722.9752591706776</v>
       </c>
       <c r="DA146" s="513" t="n">
-        <v>709.5005900935212</v>
+        <v>709.5005900935236</v>
       </c>
     </row>
     <row r="147">
@@ -30488,49 +30488,49 @@
         </is>
       </c>
       <c r="BS147" s="391" t="n">
-        <v>3060.302267449386</v>
+        <v>3060.302267449389</v>
       </c>
       <c r="BT147" s="375" t="n">
-        <v>2343.584759766819</v>
+        <v>2343.58475976682</v>
       </c>
       <c r="BU147" s="375" t="n">
-        <v>2390.968356973722</v>
+        <v>2390.968356973723</v>
       </c>
       <c r="BV147" s="375" t="n">
-        <v>2420.337708389658</v>
+        <v>2420.33770838966</v>
       </c>
       <c r="BW147" s="392" t="n">
-        <v>2405.099486598686</v>
+        <v>2405.099486598688</v>
       </c>
       <c r="BX147" s="386" t="n">
-        <v>214.6376066608078</v>
+        <v>214.637606660808</v>
       </c>
       <c r="BY147" s="372" t="n">
-        <v>175.2143618379644</v>
+        <v>175.2143618379645</v>
       </c>
       <c r="BZ147" s="372" t="n">
-        <v>186.5078153278422</v>
+        <v>186.5078153278423</v>
       </c>
       <c r="CA147" s="372" t="n">
-        <v>197.5546038722474</v>
+        <v>197.5546038722475</v>
       </c>
       <c r="CB147" s="387" t="n">
-        <v>205.6042943544613</v>
+        <v>205.6042943544614</v>
       </c>
       <c r="CW147" s="391" t="n">
-        <v>986.2700604515633</v>
+        <v>986.2700604515661</v>
       </c>
       <c r="CX147" s="375" t="n">
-        <v>231.7148123981044</v>
+        <v>231.7148123981054</v>
       </c>
       <c r="CY147" s="375" t="n">
-        <v>252.7880523368112</v>
+        <v>252.7880523368124</v>
       </c>
       <c r="CZ147" s="375" t="n">
-        <v>270.8465969963156</v>
+        <v>270.846596996317</v>
       </c>
       <c r="DA147" s="392" t="n">
-        <v>244.2168439960109</v>
+        <v>244.2168439960124</v>
       </c>
     </row>
     <row r="148">
@@ -30683,46 +30683,46 @@
         <v>31194.64853336072</v>
       </c>
       <c r="BT148" s="375" t="n">
-        <v>35577.50339981192</v>
+        <v>35577.50339981193</v>
       </c>
       <c r="BU148" s="375" t="n">
-        <v>42320.33539830259</v>
+        <v>42320.3353983026</v>
       </c>
       <c r="BV148" s="375" t="n">
-        <v>52001.74829620278</v>
+        <v>52001.74829620279</v>
       </c>
       <c r="BW148" s="392" t="n">
-        <v>66182.01770706019</v>
+        <v>66182.01770706021</v>
       </c>
       <c r="BX148" s="386" t="n">
         <v>384.3349083290886</v>
       </c>
       <c r="BY148" s="372" t="n">
-        <v>442.2360020444946</v>
+        <v>442.2360020444947</v>
       </c>
       <c r="BZ148" s="372" t="n">
-        <v>525.8232162365044</v>
+        <v>525.8232162365045</v>
       </c>
       <c r="CA148" s="372" t="n">
-        <v>639.7726191430564</v>
+        <v>639.7726191430565</v>
       </c>
       <c r="CB148" s="387" t="n">
-        <v>793.3130728859099</v>
+        <v>793.3130728859101</v>
       </c>
       <c r="CW148" s="391" t="n">
-        <v>578.8040710369563</v>
+        <v>578.8040710369645</v>
       </c>
       <c r="CX148" s="375" t="n">
-        <v>182.6507673135264</v>
+        <v>182.6507673135314</v>
       </c>
       <c r="CY148" s="375" t="n">
-        <v>191.8857199078146</v>
+        <v>191.8857199078203</v>
       </c>
       <c r="CZ148" s="375" t="n">
-        <v>203.6417291438435</v>
+        <v>203.6417291438502</v>
       </c>
       <c r="DA148" s="392" t="n">
-        <v>207.8945490444323</v>
+        <v>207.8945490444392</v>
       </c>
     </row>
     <row r="149" ht="15.75" customHeight="1" thickBot="1">
@@ -30902,19 +30902,19 @@
         <v>18302.44144493353</v>
       </c>
       <c r="CW149" s="419" t="n">
-        <v>219.8088544235453</v>
+        <v>219.8088544235437</v>
       </c>
       <c r="CX149" s="420" t="n">
-        <v>202.9991592293412</v>
+        <v>202.9991592293397</v>
       </c>
       <c r="CY149" s="420" t="n">
-        <v>212.5341257203996</v>
+        <v>212.534125720398</v>
       </c>
       <c r="CZ149" s="420" t="n">
-        <v>223.7561512059142</v>
+        <v>223.7561512059126</v>
       </c>
       <c r="DA149" s="421" t="n">
-        <v>236.3659703246933</v>
+        <v>236.3659703246916</v>
       </c>
     </row>
     <row r="150" ht="15.75" customHeight="1" thickBot="1">
@@ -31079,7 +31079,7 @@
         <v>342713.4789830479</v>
       </c>
       <c r="BX150" s="442" t="n">
-        <v>3093.388983960046</v>
+        <v>3093.388983960045</v>
       </c>
       <c r="BY150" s="443" t="n">
         <v>3426.414946400491</v>
@@ -31094,19 +31094,19 @@
         <v>2699.955785208391</v>
       </c>
       <c r="CW150" s="419" t="n">
-        <v>9585.864518077331</v>
+        <v>9585.864518077375</v>
       </c>
       <c r="CX150" s="420" t="n">
-        <v>1334.342029653239</v>
+        <v>1334.342029653247</v>
       </c>
       <c r="CY150" s="420" t="n">
-        <v>1383.269446486624</v>
+        <v>1383.269446486632</v>
       </c>
       <c r="CZ150" s="420" t="n">
-        <v>1421.219736516748</v>
+        <v>1421.219736516757</v>
       </c>
       <c r="DA150" s="421" t="n">
-        <v>1397.977953458658</v>
+        <v>1397.977953458667</v>
       </c>
     </row>
     <row r="151">
@@ -34853,7 +34853,7 @@
         <v>176.1454362373095</v>
       </c>
       <c r="BZ174" s="190" t="n">
-        <v>184.3095229423782</v>
+        <v>184.3095229423781</v>
       </c>
       <c r="CA174" s="190" t="n">
         <v>198.6343284113347</v>
@@ -34868,7 +34868,7 @@
         <v>204.1389513803095</v>
       </c>
       <c r="CE174" s="190" t="n">
-        <v>227.7167529123782</v>
+        <v>227.7167529123781</v>
       </c>
       <c r="CF174" s="190" t="n">
         <v>254.4273779823347</v>
@@ -35411,7 +35411,7 @@
         <v>2285.762979922697</v>
       </c>
       <c r="BZ176" s="222" t="n">
-        <v>2628.450032106747</v>
+        <v>2628.450032106746</v>
       </c>
       <c r="CA176" s="222" t="n">
         <v>3069.072466969569</v>
@@ -38461,13 +38461,13 @@
         <v>128.501482714</v>
       </c>
       <c r="AP190" s="194" t="n">
-        <v>906.0765657566792</v>
+        <v>906.0765657566795</v>
       </c>
       <c r="AQ190" s="179" t="n">
-        <v>1920.607781175105</v>
+        <v>1920.607781175106</v>
       </c>
       <c r="AR190" s="179" t="n">
-        <v>2249.192672065882</v>
+        <v>2249.192672065881</v>
       </c>
       <c r="AS190" s="179" t="n">
         <v>2654.460653987203</v>
@@ -38476,13 +38476,13 @@
         <v>3148.734546452979</v>
       </c>
       <c r="AU190" s="190" t="n">
-        <v>921.8835847439334</v>
+        <v>921.8835847439337</v>
       </c>
       <c r="AV190" s="190" t="n">
         <v>1975.066111716585</v>
       </c>
       <c r="AW190" s="190" t="n">
-        <v>2346.968258259808</v>
+        <v>2346.968258259807</v>
       </c>
       <c r="AX190" s="190" t="n">
         <v>2769.0896092362</v>
@@ -38511,13 +38511,13 @@
         <v>128.501482714</v>
       </c>
       <c r="BG190" s="197" t="n">
-        <v>906.0765657566792</v>
+        <v>906.0765657566795</v>
       </c>
       <c r="BH190" s="190" t="n">
-        <v>1920.607781175105</v>
+        <v>1920.607781175106</v>
       </c>
       <c r="BI190" s="190" t="n">
-        <v>2249.192672065882</v>
+        <v>2249.192672065881</v>
       </c>
       <c r="BJ190" s="190" t="n">
         <v>2654.460653987203</v>
@@ -38526,13 +38526,13 @@
         <v>3148.734546452979</v>
       </c>
       <c r="BL190" s="199" t="n">
-        <v>921.8835847436792</v>
+        <v>921.8835847436795</v>
       </c>
       <c r="BM190" s="200" t="n">
-        <v>1975.066111716105</v>
+        <v>1975.066111716106</v>
       </c>
       <c r="BN190" s="200" t="n">
-        <v>2346.968258259882</v>
+        <v>2346.968258259881</v>
       </c>
       <c r="BO190" s="200" t="n">
         <v>2769.089609236203</v>
@@ -38561,13 +38561,13 @@
         <v>108.838066539</v>
       </c>
       <c r="BX190" s="197" t="n">
-        <v>901.4276691637683</v>
+        <v>901.4276691637687</v>
       </c>
       <c r="BY190" s="190" t="n">
-        <v>1925.974758287879</v>
+        <v>1925.97475828788</v>
       </c>
       <c r="BZ190" s="190" t="n">
-        <v>2258.024495101128</v>
+        <v>2258.024495101127</v>
       </c>
       <c r="CA190" s="190" t="n">
         <v>2667.756421793293</v>
@@ -38576,13 +38576,13 @@
         <v>3167.861436252626</v>
       </c>
       <c r="CC190" s="199" t="n">
-        <v>915.3909209817683</v>
+        <v>915.3909209817687</v>
       </c>
       <c r="CD190" s="200" t="n">
         <v>1974.50789049388</v>
       </c>
       <c r="CE190" s="200" t="n">
-        <v>2346.412208262128</v>
+        <v>2346.412208262127</v>
       </c>
       <c r="CF190" s="200" t="n">
         <v>2768.539928996293</v>
@@ -38618,22 +38618,22 @@
         <v>6817</v>
       </c>
       <c r="CW190" s="91" t="n">
-        <v>6.492663762398208</v>
+        <v>6.492663762398237</v>
       </c>
       <c r="CX190" s="92" t="n">
-        <v>0.5582212223740151</v>
+        <v>0.5582212223740172</v>
       </c>
       <c r="CY190" s="92" t="n">
-        <v>0.5560499977934462</v>
+        <v>0.5560499977934482</v>
       </c>
       <c r="CZ190" s="92" t="n">
-        <v>0.5496802400906827</v>
+        <v>0.5496802400906847</v>
       </c>
       <c r="DA190" s="93" t="n">
-        <v>0.5365263753544431</v>
+        <v>0.5365263753544449</v>
       </c>
       <c r="DC190" s="393" t="n">
-        <v>0.006431830912802234</v>
+        <v>0.006431830912802232</v>
       </c>
       <c r="DD190" s="394" t="n">
         <v>0.000264445797431248</v>
@@ -38785,7 +38785,7 @@
         <v>215.0875607908827</v>
       </c>
       <c r="AU191" s="190" t="n">
-        <v>177.9562690168208</v>
+        <v>177.9562690168209</v>
       </c>
       <c r="AV191" s="190" t="n">
         <v>225.0657462855991</v>
@@ -38879,7 +38879,7 @@
         <v>178.4113148934441</v>
       </c>
       <c r="CA191" s="190" t="n">
-        <v>194.7783481238815</v>
+        <v>194.7783481238814</v>
       </c>
       <c r="CB191" s="198" t="n">
         <v>216.7829927773281</v>
@@ -38927,22 +38927,22 @@
         <v>12808</v>
       </c>
       <c r="CW191" s="102" t="n">
-        <v>0.4056209815029398</v>
+        <v>0.4056209815029409</v>
       </c>
       <c r="CX191" s="103" t="n">
-        <v>0.08078411315871847</v>
+        <v>0.08078411315871883</v>
       </c>
       <c r="CY191" s="103" t="n">
-        <v>0.08279381105852547</v>
+        <v>0.08279381105852586</v>
       </c>
       <c r="CZ191" s="103" t="n">
-        <v>0.08509236834482972</v>
+        <v>0.08509236834483014</v>
       </c>
       <c r="DA191" s="104" t="n">
-        <v>0.07410678027584618</v>
+        <v>0.07410678027584662</v>
       </c>
       <c r="DC191" s="396" t="n">
-        <v>0.002257409169410834</v>
+        <v>0.002257409169410833</v>
       </c>
       <c r="DD191" s="397" t="n">
         <v>0.000343546109341654</v>
@@ -39085,13 +39085,13 @@
         <v>175.6085183659755</v>
       </c>
       <c r="AR192" s="179" t="n">
-        <v>183.4736042204119</v>
+        <v>183.473604220412</v>
       </c>
       <c r="AS192" s="179" t="n">
         <v>197.4370540006157</v>
       </c>
       <c r="AT192" s="195" t="n">
-        <v>218.040042079689</v>
+        <v>218.0400420796891</v>
       </c>
       <c r="AU192" s="190" t="n">
         <v>151.8723645526329</v>
@@ -39100,13 +39100,13 @@
         <v>204.2146775417666</v>
       </c>
       <c r="AW192" s="190" t="n">
-        <v>227.7920021994057</v>
+        <v>227.7920021994058</v>
       </c>
       <c r="AX192" s="190" t="n">
         <v>254.5026166542022</v>
       </c>
       <c r="AY192" s="196" t="n">
-        <v>286.353683077626</v>
+        <v>286.3536830776262</v>
       </c>
       <c r="BA192" s="111" t="inlineStr">
         <is>
@@ -39135,13 +39135,13 @@
         <v>175.6085183659755</v>
       </c>
       <c r="BI192" s="190" t="n">
-        <v>183.4736042204119</v>
+        <v>183.473604220412</v>
       </c>
       <c r="BJ192" s="190" t="n">
         <v>197.4370540006157</v>
       </c>
       <c r="BK192" s="198" t="n">
-        <v>218.040042079689</v>
+        <v>218.0400420796891</v>
       </c>
       <c r="BL192" s="197" t="n">
         <v>151.8723645531072</v>
@@ -39150,13 +39150,13 @@
         <v>204.2146775419755</v>
       </c>
       <c r="BN192" s="190" t="n">
-        <v>227.7920021994119</v>
+        <v>227.792002199412</v>
       </c>
       <c r="BO192" s="190" t="n">
         <v>254.5026166546157</v>
       </c>
       <c r="BP192" s="198" t="n">
-        <v>286.353683077689</v>
+        <v>286.3536830776891</v>
       </c>
       <c r="BR192" s="111" t="inlineStr">
         <is>
@@ -39185,13 +39185,13 @@
         <v>176.145436237285</v>
       </c>
       <c r="BZ192" s="190" t="n">
-        <v>184.3095229427919</v>
+        <v>184.309522942792</v>
       </c>
       <c r="CA192" s="190" t="n">
         <v>198.6343284119542</v>
       </c>
       <c r="CB192" s="198" t="n">
-        <v>219.6834344195325</v>
+        <v>219.6834344195327</v>
       </c>
       <c r="CC192" s="197" t="n">
         <v>151.6082643958643</v>
@@ -39200,13 +39200,13 @@
         <v>204.138951380285</v>
       </c>
       <c r="CE192" s="190" t="n">
-        <v>227.7167529127919</v>
+        <v>227.716752912792</v>
       </c>
       <c r="CF192" s="190" t="n">
         <v>254.4273779829542</v>
       </c>
       <c r="CG192" s="198" t="n">
-        <v>286.2789533195325</v>
+        <v>286.2789533195327</v>
       </c>
       <c r="CI192" s="197" t="n">
         <v>0</v>
@@ -39236,19 +39236,19 @@
         <v>8351</v>
       </c>
       <c r="CW192" s="102" t="n">
-        <v>0.2641001573490654</v>
+        <v>0.2641001573490691</v>
       </c>
       <c r="CX192" s="103" t="n">
-        <v>0.07572616131645396</v>
+        <v>0.07572616131645603</v>
       </c>
       <c r="CY192" s="103" t="n">
-        <v>0.07524928641767235</v>
+        <v>0.07524928641767459</v>
       </c>
       <c r="CZ192" s="103" t="n">
-        <v>0.07523867193468156</v>
+        <v>0.07523867193468403</v>
       </c>
       <c r="DA192" s="104" t="n">
-        <v>0.07472975862258897</v>
+        <v>0.07472975862259144</v>
       </c>
       <c r="DC192" s="396" t="n">
         <v>0.001826142066693257</v>
@@ -39388,34 +39388,34 @@
         <v>0</v>
       </c>
       <c r="AP193" s="206" t="n">
-        <v>8.638281980360063</v>
+        <v>8.638281980360059</v>
       </c>
       <c r="AQ193" s="207" t="n">
-        <v>7.571574146618566</v>
+        <v>7.57157414661857</v>
       </c>
       <c r="AR193" s="207" t="n">
-        <v>7.711289693800257</v>
+        <v>7.711289693800254</v>
       </c>
       <c r="AS193" s="207" t="n">
-        <v>7.910092821495519</v>
+        <v>7.910092821495514</v>
       </c>
       <c r="AT193" s="208" t="n">
-        <v>8.142790620811347</v>
+        <v>8.142790620811343</v>
       </c>
       <c r="AU193" s="209" t="n">
-        <v>8.638281980360063</v>
+        <v>8.638281980360059</v>
       </c>
       <c r="AV193" s="209" t="n">
-        <v>7.571574146618566</v>
+        <v>7.57157414661857</v>
       </c>
       <c r="AW193" s="209" t="n">
-        <v>7.711289693800257</v>
+        <v>7.711289693800254</v>
       </c>
       <c r="AX193" s="209" t="n">
-        <v>7.910092821495519</v>
+        <v>7.910092821495514</v>
       </c>
       <c r="AY193" s="210" t="n">
-        <v>8.142790620811347</v>
+        <v>8.142790620811343</v>
       </c>
       <c r="BA193" s="111" t="inlineStr">
         <is>
@@ -39438,34 +39438,34 @@
         <v>0</v>
       </c>
       <c r="BG193" s="211" t="n">
-        <v>8.638281980360063</v>
+        <v>8.638281980360059</v>
       </c>
       <c r="BH193" s="212" t="n">
-        <v>7.571574146618566</v>
+        <v>7.57157414661857</v>
       </c>
       <c r="BI193" s="212" t="n">
-        <v>7.711289693800257</v>
+        <v>7.711289693800254</v>
       </c>
       <c r="BJ193" s="212" t="n">
-        <v>7.910092821495519</v>
+        <v>7.910092821495514</v>
       </c>
       <c r="BK193" s="213" t="n">
-        <v>8.142790620811347</v>
+        <v>8.142790620811343</v>
       </c>
       <c r="BL193" s="212" t="n">
-        <v>8.638281980360063</v>
+        <v>8.638281980360059</v>
       </c>
       <c r="BM193" s="212" t="n">
-        <v>7.571574146618566</v>
+        <v>7.57157414661857</v>
       </c>
       <c r="BN193" s="212" t="n">
-        <v>7.711289693800257</v>
+        <v>7.711289693800254</v>
       </c>
       <c r="BO193" s="212" t="n">
-        <v>7.910092821495519</v>
+        <v>7.910092821495514</v>
       </c>
       <c r="BP193" s="213" t="n">
-        <v>8.142790620811347</v>
+        <v>8.142790620811343</v>
       </c>
       <c r="BR193" s="111" t="inlineStr">
         <is>
@@ -39488,34 +39488,34 @@
         <v>0</v>
       </c>
       <c r="BX193" s="211" t="n">
-        <v>8.63204779929826</v>
+        <v>8.632047799298256</v>
       </c>
       <c r="BY193" s="212" t="n">
-        <v>7.565178001532778</v>
+        <v>7.565178001532781</v>
       </c>
       <c r="BZ193" s="212" t="n">
-        <v>7.704699169865312</v>
+        <v>7.704699169865308</v>
       </c>
       <c r="CA193" s="212" t="n">
-        <v>7.903368641735173</v>
+        <v>7.903368641735168</v>
       </c>
       <c r="CB193" s="213" t="n">
-        <v>8.135930074685461</v>
+        <v>8.135930074685458</v>
       </c>
       <c r="CC193" s="212" t="n">
-        <v>8.63204779929826</v>
+        <v>8.632047799298256</v>
       </c>
       <c r="CD193" s="212" t="n">
-        <v>7.565178001532778</v>
+        <v>7.565178001532781</v>
       </c>
       <c r="CE193" s="212" t="n">
-        <v>7.704699169865312</v>
+        <v>7.704699169865308</v>
       </c>
       <c r="CF193" s="212" t="n">
-        <v>7.903368641735173</v>
+        <v>7.903368641735168</v>
       </c>
       <c r="CG193" s="213" t="n">
-        <v>8.135930074685461</v>
+        <v>8.135930074685458</v>
       </c>
       <c r="CI193" s="211" t="n">
         <v>0</v>
@@ -39545,19 +39545,19 @@
         <v>948</v>
       </c>
       <c r="CW193" s="132" t="n">
-        <v>0.00623418106180267</v>
+        <v>0.006234181061802625</v>
       </c>
       <c r="CX193" s="133" t="n">
-        <v>0.006396145085788303</v>
+        <v>0.006396145085788256</v>
       </c>
       <c r="CY193" s="133" t="n">
-        <v>0.006590523934945408</v>
+        <v>0.006590523934945361</v>
       </c>
       <c r="CZ193" s="133" t="n">
-        <v>0.006724179760346102</v>
+        <v>0.006724179760346054</v>
       </c>
       <c r="DA193" s="134" t="n">
-        <v>0.006860546125885922</v>
+        <v>0.006860546125885872</v>
       </c>
       <c r="DC193" s="422" t="n">
         <v>0</v>
@@ -39697,13 +39697,13 @@
         <v>276.650690708</v>
       </c>
       <c r="AP194" s="206" t="n">
-        <v>1200.88963646106</v>
+        <v>1200.889636461061</v>
       </c>
       <c r="AQ194" s="207" t="n">
-        <v>2279.27106795756</v>
+        <v>2279.271067957561</v>
       </c>
       <c r="AR194" s="207" t="n">
-        <v>2617.890290245479</v>
+        <v>2617.890290245478</v>
       </c>
       <c r="AS194" s="207" t="n">
         <v>3053.331266267291</v>
@@ -39712,10 +39712,10 @@
         <v>3590.004939944361</v>
       </c>
       <c r="AU194" s="207" t="n">
-        <v>1260.350500293747</v>
+        <v>1260.350500293748</v>
       </c>
       <c r="AV194" s="207" t="n">
-        <v>2411.918109690569</v>
+        <v>2411.91810969057</v>
       </c>
       <c r="AW194" s="207" t="n">
         <v>2827.817659932744</v>
@@ -39747,13 +39747,13 @@
         <v>276.650690708</v>
       </c>
       <c r="BG194" s="221" t="n">
-        <v>1200.88963646106</v>
+        <v>1200.889636461061</v>
       </c>
       <c r="BH194" s="222" t="n">
-        <v>2279.27106795756</v>
+        <v>2279.271067957561</v>
       </c>
       <c r="BI194" s="222" t="n">
-        <v>2617.890290245479</v>
+        <v>2617.890290245478</v>
       </c>
       <c r="BJ194" s="222" t="n">
         <v>3053.331266267291</v>
@@ -39765,10 +39765,10 @@
         <v>1260.350500294061</v>
       </c>
       <c r="BM194" s="222" t="n">
-        <v>2411.91810969056</v>
+        <v>2411.918109690561</v>
       </c>
       <c r="BN194" s="222" t="n">
-        <v>2827.817659932479</v>
+        <v>2827.817659932478</v>
       </c>
       <c r="BO194" s="222" t="n">
         <v>3299.49732556229</v>
@@ -39800,10 +39800,10 @@
         <v>1196.224441815376</v>
       </c>
       <c r="BY194" s="222" t="n">
-        <v>2285.762979922257</v>
+        <v>2285.762979922258</v>
       </c>
       <c r="BZ194" s="222" t="n">
-        <v>2628.450032107229</v>
+        <v>2628.450032107228</v>
       </c>
       <c r="CA194" s="222" t="n">
         <v>3069.072466970864</v>
@@ -39812,13 +39812,13 @@
         <v>3612.463793524172</v>
       </c>
       <c r="CC194" s="222" t="n">
-        <v>1253.181881212376</v>
+        <v>1253.181881212377</v>
       </c>
       <c r="CD194" s="222" t="n">
-        <v>2411.196982048257</v>
+        <v>2411.196982048258</v>
       </c>
       <c r="CE194" s="222" t="n">
-        <v>2827.096976313229</v>
+        <v>2827.096976313228</v>
       </c>
       <c r="CF194" s="222" t="n">
         <v>3298.780590102864</v>
@@ -39854,19 +39854,19 @@
         <v>28924</v>
       </c>
       <c r="CW194" s="132" t="n">
-        <v>7.168619082312016</v>
+        <v>7.16861908231205</v>
       </c>
       <c r="CX194" s="133" t="n">
-        <v>0.7211276419349758</v>
+        <v>0.7211276419349804</v>
       </c>
       <c r="CY194" s="133" t="n">
-        <v>0.7206836192045895</v>
+        <v>0.720683619204594</v>
       </c>
       <c r="CZ194" s="133" t="n">
-        <v>0.7167354601305401</v>
+        <v>0.7167354601305449</v>
       </c>
       <c r="DA194" s="134" t="n">
-        <v>0.6922234603787643</v>
+        <v>0.6922234603787689</v>
       </c>
     </row>
     <row r="195" ht="15.75" customHeight="1" thickBot="1">
@@ -40825,10 +40825,10 @@
         <v>1.843767169487867</v>
       </c>
       <c r="AQ199" s="190" t="n">
-        <v>5.925198335149754</v>
+        <v>5.925198335149756</v>
       </c>
       <c r="AR199" s="190" t="n">
-        <v>9.387873033039234</v>
+        <v>9.387873033039231</v>
       </c>
       <c r="AS199" s="190" t="n">
         <v>13.845448046181</v>
@@ -40837,13 +40837,13 @@
         <v>19.66341617499921</v>
       </c>
       <c r="AU199" s="190" t="n">
-        <v>907.920332926167</v>
+        <v>907.9203329261674</v>
       </c>
       <c r="AV199" s="190" t="n">
-        <v>1926.532979510255</v>
+        <v>1926.532979510256</v>
       </c>
       <c r="AW199" s="190" t="n">
-        <v>2258.580545098921</v>
+        <v>2258.58054509892</v>
       </c>
       <c r="AX199" s="190" t="n">
         <v>2668.306102033384</v>
@@ -40875,10 +40875,10 @@
         <v>1.843767169487359</v>
       </c>
       <c r="BH199" s="190" t="n">
-        <v>5.925198335148315</v>
+        <v>5.925198335148317</v>
       </c>
       <c r="BI199" s="190" t="n">
-        <v>9.387873033039527</v>
+        <v>9.387873033039524</v>
       </c>
       <c r="BJ199" s="190" t="n">
         <v>13.84544804618101</v>
@@ -40887,13 +40887,13 @@
         <v>19.66341617500187</v>
       </c>
       <c r="BL199" s="199" t="n">
-        <v>907.9203329261666</v>
+        <v>907.9203329261669</v>
       </c>
       <c r="BM199" s="200" t="n">
-        <v>1926.532979510253</v>
+        <v>1926.532979510254</v>
       </c>
       <c r="BN199" s="200" t="n">
-        <v>2258.580545098921</v>
+        <v>2258.58054509892</v>
       </c>
       <c r="BO199" s="200" t="n">
         <v>2668.306102033384</v>
@@ -40907,28 +40907,28 @@
         </is>
       </c>
       <c r="BS199" s="335" t="n">
-        <v>755.3202508115063</v>
+        <v>755.3202508115062</v>
       </c>
       <c r="BT199" s="336" t="n">
         <v>56.33223463137914</v>
       </c>
       <c r="BU199" s="336" t="n">
-        <v>55.65626850157529</v>
+        <v>55.6562685015753</v>
       </c>
       <c r="BV199" s="336" t="n">
-        <v>51.23859989215605</v>
+        <v>51.23859989215606</v>
       </c>
       <c r="BW199" s="337" t="n">
         <v>45.51792185462426</v>
       </c>
       <c r="BX199" s="462" t="n">
-        <v>0.8324179600856522</v>
+        <v>0.8324179600856517</v>
       </c>
       <c r="BY199" s="463" t="n">
-        <v>0.02904908370653093</v>
+        <v>0.02904908370653091</v>
       </c>
       <c r="BZ199" s="463" t="n">
-        <v>0.02450483665019171</v>
+        <v>0.02450483665019172</v>
       </c>
       <c r="CA199" s="463" t="n">
         <v>0.01910076030585956</v>
@@ -40937,13 +40937,13 @@
         <v>0.01428902418260767</v>
       </c>
       <c r="CC199" s="199" t="n">
-        <v>750.3645815300681</v>
+        <v>750.364581530068</v>
       </c>
       <c r="CD199" s="200" t="n">
-        <v>55.94780197017028</v>
+        <v>55.94780197017027</v>
       </c>
       <c r="CE199" s="200" t="n">
-        <v>55.33252140458474</v>
+        <v>55.33252140458475</v>
       </c>
       <c r="CF199" s="200" t="n">
         <v>50.95617596709128</v>
@@ -41135,7 +41135,7 @@
         <v>0.006</v>
       </c>
       <c r="AP200" s="233" t="n">
-        <v>0.3559125380336416</v>
+        <v>0.3559125380336418</v>
       </c>
       <c r="AQ200" s="190" t="n">
         <v>0.6751972388567973</v>
@@ -41150,7 +41150,7 @@
         <v>1.769538766722183</v>
       </c>
       <c r="AU200" s="190" t="n">
-        <v>151.2042825439478</v>
+        <v>151.2042825439479</v>
       </c>
       <c r="AV200" s="190" t="n">
         <v>176.1583915087177</v>
@@ -41185,7 +41185,7 @@
         <v>0.006</v>
       </c>
       <c r="BG200" s="197" t="n">
-        <v>0.3559125380338284</v>
+        <v>0.3559125380338285</v>
       </c>
       <c r="BH200" s="190" t="n">
         <v>0.6751972388575826</v>
@@ -41200,7 +41200,7 @@
         <v>1.769538766721296</v>
       </c>
       <c r="BL200" s="197" t="n">
-        <v>151.204282543948</v>
+        <v>151.2042825439481</v>
       </c>
       <c r="BM200" s="190" t="n">
         <v>176.1583915087185</v>
@@ -41220,7 +41220,7 @@
         </is>
       </c>
       <c r="BS200" s="335" t="n">
-        <v>51.13856851003995</v>
+        <v>51.13856851003994</v>
       </c>
       <c r="BT200" s="336" t="n">
         <v>16.0958098959233</v>
@@ -41235,7 +41235,7 @@
         <v>19.75993719002158</v>
       </c>
       <c r="BX200" s="462" t="n">
-        <v>0.3372284849427493</v>
+        <v>0.3372284849427491</v>
       </c>
       <c r="BY200" s="463" t="n">
         <v>0.09130608373051914</v>
@@ -41244,13 +41244,13 @@
         <v>0.0976694843542965</v>
       </c>
       <c r="CA200" s="463" t="n">
-        <v>0.09748899055852775</v>
+        <v>0.09748899055852776</v>
       </c>
       <c r="CB200" s="464" t="n">
-        <v>0.09155882751752581</v>
+        <v>0.09155882751752585</v>
       </c>
       <c r="CC200" s="197" t="n">
-        <v>50.85360417009775</v>
+        <v>50.85360417009774</v>
       </c>
       <c r="CD200" s="190" t="n">
         <v>16.07695676392845</v>
@@ -41262,7 +41262,7 @@
         <v>18.98874454125471</v>
       </c>
       <c r="CG200" s="198" t="n">
-        <v>19.84839664443243</v>
+        <v>19.84839664443244</v>
       </c>
       <c r="CI200" s="396" t="n">
         <v>0.9999999996515252</v>
@@ -41286,7 +41286,7 @@
         <v>0.9999999979160058</v>
       </c>
       <c r="CP200" s="397" t="n">
-        <v>0.9999999988016033</v>
+        <v>0.9999999988016034</v>
       </c>
       <c r="CQ200" s="397" t="n">
         <v>0.9999999999999025</v>
@@ -41311,7 +41311,7 @@
         <v>1.000000000030032</v>
       </c>
       <c r="CY200" s="396" t="n">
-        <v>1.00000000130491</v>
+        <v>1.000000001304909</v>
       </c>
       <c r="CZ200" s="397" t="n">
         <v>0.999999998569393</v>
@@ -41323,7 +41323,7 @@
         <v>0.9999999999999307</v>
       </c>
       <c r="DC200" s="398" t="n">
-        <v>0.9999999997345222</v>
+        <v>0.9999999997345224</v>
       </c>
     </row>
     <row r="201" ht="15.75" customHeight="1" thickBot="1">
@@ -41448,19 +41448,19 @@
         <v>0.006</v>
       </c>
       <c r="AP201" s="233" t="n">
-        <v>0.3037447291052659</v>
+        <v>0.3037447291052658</v>
       </c>
       <c r="AQ201" s="190" t="n">
         <v>0.6126440326252999</v>
       </c>
       <c r="AR201" s="190" t="n">
-        <v>0.9111680087976226</v>
+        <v>0.9111680087976231</v>
       </c>
       <c r="AS201" s="190" t="n">
         <v>1.272513083271011</v>
       </c>
       <c r="AT201" s="196" t="n">
-        <v>1.718122098465756</v>
+        <v>1.718122098465757</v>
       </c>
       <c r="AU201" s="190" t="n">
         <v>135.6301634472124</v>
@@ -41469,13 +41469,13 @@
         <v>176.2211623986008</v>
       </c>
       <c r="AW201" s="190" t="n">
-        <v>184.3847722292095</v>
+        <v>184.3847722292097</v>
       </c>
       <c r="AX201" s="190" t="n">
         <v>198.7095670838868</v>
       </c>
       <c r="AY201" s="196" t="n">
-        <v>219.7581641781547</v>
+        <v>219.7581641781549</v>
       </c>
       <c r="BA201" s="111" t="inlineStr">
         <is>
@@ -41504,13 +41504,13 @@
         <v>0.6126440326259265</v>
       </c>
       <c r="BI201" s="190" t="n">
-        <v>0.9111680087976477</v>
+        <v>0.9111680087976481</v>
       </c>
       <c r="BJ201" s="190" t="n">
         <v>1.272513083273079</v>
       </c>
       <c r="BK201" s="198" t="n">
-        <v>1.718122098466134</v>
+        <v>1.718122098466135</v>
       </c>
       <c r="BL201" s="197" t="n">
         <v>135.6301634472134</v>
@@ -41519,13 +41519,13 @@
         <v>176.2211623986014</v>
       </c>
       <c r="BN201" s="190" t="n">
-        <v>184.3847722292096</v>
+        <v>184.3847722292097</v>
       </c>
       <c r="BO201" s="190" t="n">
         <v>198.7095670838888</v>
       </c>
       <c r="BP201" s="198" t="n">
-        <v>219.7581641781551</v>
+        <v>219.7581641781553</v>
       </c>
       <c r="BR201" s="111" t="inlineStr">
         <is>
@@ -41533,49 +41533,49 @@
         </is>
       </c>
       <c r="BS201" s="335" t="n">
-        <v>84.40848126919825</v>
+        <v>84.40848126919823</v>
       </c>
       <c r="BT201" s="336" t="n">
-        <v>46.47854001102072</v>
+        <v>46.47854001102073</v>
       </c>
       <c r="BU201" s="336" t="n">
-        <v>50.4514222620171</v>
+        <v>50.45142226201709</v>
       </c>
       <c r="BV201" s="336" t="n">
         <v>55.51399834326029</v>
       </c>
       <c r="BW201" s="337" t="n">
-        <v>55.46093120356361</v>
+        <v>55.4609312035636</v>
       </c>
       <c r="BX201" s="462" t="n">
-        <v>0.6230057723229331</v>
+        <v>0.623005772322933</v>
       </c>
       <c r="BY201" s="463" t="n">
         <v>0.2643552064417087</v>
       </c>
       <c r="BZ201" s="463" t="n">
-        <v>0.2746831764536097</v>
+        <v>0.2746831764536095</v>
       </c>
       <c r="CA201" s="463" t="n">
         <v>0.2809008726189627</v>
       </c>
       <c r="CB201" s="464" t="n">
-        <v>0.2541075763233429</v>
+        <v>0.2541075763233426</v>
       </c>
       <c r="CC201" s="197" t="n">
-        <v>84.33383880621696</v>
+        <v>84.33383880621695</v>
       </c>
       <c r="CD201" s="190" t="n">
-        <v>46.5649631602723</v>
+        <v>46.56496316027231</v>
       </c>
       <c r="CE201" s="190" t="n">
-        <v>50.62672521257554</v>
+        <v>50.62672521257553</v>
       </c>
       <c r="CF201" s="190" t="n">
         <v>55.79655618299955</v>
       </c>
       <c r="CG201" s="198" t="n">
-        <v>55.82322507873544</v>
+        <v>55.82322507873543</v>
       </c>
       <c r="CI201" s="422" t="n">
         <v>1</v>
@@ -41775,19 +41775,19 @@
         <v>0</v>
       </c>
       <c r="AU202" s="209" t="n">
-        <v>8.638281980360063</v>
+        <v>8.638281980360059</v>
       </c>
       <c r="AV202" s="209" t="n">
-        <v>7.571574146618566</v>
+        <v>7.57157414661857</v>
       </c>
       <c r="AW202" s="209" t="n">
-        <v>7.711289693800257</v>
+        <v>7.711289693800254</v>
       </c>
       <c r="AX202" s="209" t="n">
-        <v>7.910092821495519</v>
+        <v>7.910092821495514</v>
       </c>
       <c r="AY202" s="210" t="n">
-        <v>8.142790620811347</v>
+        <v>8.142790620811343</v>
       </c>
       <c r="BA202" s="111" t="inlineStr">
         <is>
@@ -41825,19 +41825,19 @@
         <v>0</v>
       </c>
       <c r="BL202" s="212" t="n">
-        <v>8.638281980360063</v>
+        <v>8.638281980360059</v>
       </c>
       <c r="BM202" s="212" t="n">
-        <v>7.571574146618566</v>
+        <v>7.57157414661857</v>
       </c>
       <c r="BN202" s="212" t="n">
-        <v>7.711289693800257</v>
+        <v>7.711289693800254</v>
       </c>
       <c r="BO202" s="212" t="n">
-        <v>7.910092821495519</v>
+        <v>7.910092821495514</v>
       </c>
       <c r="BP202" s="213" t="n">
-        <v>8.142790620811347</v>
+        <v>8.142790620811343</v>
       </c>
       <c r="BR202" s="111" t="inlineStr">
         <is>
@@ -41860,19 +41860,19 @@
         <v>2.388846221863131</v>
       </c>
       <c r="BX202" s="466" t="n">
-        <v>0.25075293893894</v>
+        <v>0.2507529389389401</v>
       </c>
       <c r="BY202" s="467" t="n">
-        <v>0.2935483288405812</v>
+        <v>0.2935483288405811</v>
       </c>
       <c r="BZ202" s="467" t="n">
-        <v>0.2969919734392064</v>
+        <v>0.2969919734392065</v>
       </c>
       <c r="CA202" s="467" t="n">
-        <v>0.2953979877107898</v>
+        <v>0.2953979877107901</v>
       </c>
       <c r="CB202" s="468" t="n">
-        <v>0.2927736170138278</v>
+        <v>0.2927736170138279</v>
       </c>
       <c r="CC202" s="212" t="n">
         <v>2.164511354735448</v>
@@ -42025,10 +42025,10 @@
         <v>2.503424436626775</v>
       </c>
       <c r="AQ203" s="207" t="n">
-        <v>7.213039606631851</v>
+        <v>7.213039606631853</v>
       </c>
       <c r="AR203" s="207" t="n">
-        <v>11.28042548095578</v>
+        <v>11.28042548095577</v>
       </c>
       <c r="AS203" s="207" t="n">
         <v>16.45793616370193</v>
@@ -42037,13 +42037,13 @@
         <v>23.15107704018715</v>
       </c>
       <c r="AU203" s="207" t="n">
-        <v>1203.393060897687</v>
+        <v>1203.393060897688</v>
       </c>
       <c r="AV203" s="207" t="n">
-        <v>2286.484107564192</v>
+        <v>2286.484107564193</v>
       </c>
       <c r="AW203" s="207" t="n">
-        <v>2629.170715726435</v>
+        <v>2629.170715726434</v>
       </c>
       <c r="AX203" s="207" t="n">
         <v>3069.789202430993</v>
@@ -42072,16 +42072,16 @@
         <v>0.018</v>
       </c>
       <c r="BG203" s="221" t="n">
-        <v>2.503424436627401</v>
+        <v>2.503424436627402</v>
       </c>
       <c r="BH203" s="222" t="n">
-        <v>7.213039606631824</v>
+        <v>7.213039606631826</v>
       </c>
       <c r="BI203" s="222" t="n">
-        <v>11.28042548095472</v>
+        <v>11.28042548095471</v>
       </c>
       <c r="BJ203" s="222" t="n">
-        <v>16.45793616370398</v>
+        <v>16.45793616370397</v>
       </c>
       <c r="BK203" s="214" t="n">
         <v>23.1510770401893</v>
@@ -42090,10 +42090,10 @@
         <v>1203.393060897688</v>
       </c>
       <c r="BM203" s="222" t="n">
-        <v>2286.484107564192</v>
+        <v>2286.484107564193</v>
       </c>
       <c r="BN203" s="222" t="n">
-        <v>2629.170715726434</v>
+        <v>2629.170715726433</v>
       </c>
       <c r="BO203" s="222" t="n">
         <v>3069.789202430994</v>
@@ -42107,7 +42107,7 @@
         </is>
       </c>
       <c r="BS203" s="271" t="n">
-        <v>893.0380461265416</v>
+        <v>893.0380461265415</v>
       </c>
       <c r="BT203" s="272" t="n">
         <v>121.1337260431404</v>
@@ -42122,22 +42122,22 @@
         <v>123.1276364700726</v>
       </c>
       <c r="BX203" s="466" t="n">
-        <v>0.7420986437243583</v>
+        <v>0.742098643724358</v>
       </c>
       <c r="BY203" s="467" t="n">
-        <v>0.05285345344870862</v>
+        <v>0.05285345344870861</v>
       </c>
       <c r="BZ203" s="467" t="n">
-        <v>0.04781252069541408</v>
+        <v>0.0478125206954141</v>
       </c>
       <c r="CA203" s="467" t="n">
-        <v>0.04173121269132501</v>
+        <v>0.04173121269132499</v>
       </c>
       <c r="CB203" s="468" t="n">
-        <v>0.03413716043043409</v>
+        <v>0.03413716043043408</v>
       </c>
       <c r="CC203" s="212" t="n">
-        <v>887.7165358611182</v>
+        <v>887.716535861118</v>
       </c>
       <c r="CD203" s="212" t="n">
         <v>120.8104672541025</v>
@@ -42146,7 +42146,7 @@
         <v>125.6728215569887</v>
       </c>
       <c r="CF203" s="212" t="n">
-        <v>128.0761158842507</v>
+        <v>128.0761158842506</v>
       </c>
       <c r="CG203" s="213" t="n">
         <v>123.3192560686692</v>
@@ -42925,7 +42925,7 @@
         <v>13.96325181751213</v>
       </c>
       <c r="AL208" s="190" t="n">
-        <v>48.53313220585025</v>
+        <v>48.53313220585024</v>
       </c>
       <c r="AM208" s="190" t="n">
         <v>88.38771316096077</v>
@@ -42940,25 +42940,25 @@
         <v>0.01714643719536977</v>
       </c>
       <c r="AQ208" s="463" t="n">
-        <v>0.02757291526517472</v>
+        <v>0.02757291526517471</v>
       </c>
       <c r="AR208" s="463" t="n">
-        <v>0.0416603785968642</v>
+        <v>0.04166037859686422</v>
       </c>
       <c r="AS208" s="463" t="n">
-        <v>0.0413958995283709</v>
+        <v>0.04139589952837089</v>
       </c>
       <c r="AT208" s="474" t="n">
         <v>0.03921032283605073</v>
       </c>
       <c r="AU208" s="463" t="n">
-        <v>0.01514643719509403</v>
+        <v>0.01514643719509402</v>
       </c>
       <c r="AV208" s="463" t="n">
-        <v>0.02457291526493195</v>
+        <v>0.02457291526493193</v>
       </c>
       <c r="AW208" s="463" t="n">
-        <v>0.03766037859689549</v>
+        <v>0.0376603785968955</v>
       </c>
       <c r="AX208" s="463" t="n">
         <v>0.03639589952837177</v>
@@ -42987,13 +42987,13 @@
         <v>108.838066539</v>
       </c>
       <c r="BG208" s="462" t="n">
-        <v>0.01714643719509876</v>
+        <v>0.01714643719509875</v>
       </c>
       <c r="BH208" s="463" t="n">
-        <v>0.02757291526493864</v>
+        <v>0.02757291526493863</v>
       </c>
       <c r="BI208" s="463" t="n">
-        <v>0.04166037859689418</v>
+        <v>0.04166037859689421</v>
       </c>
       <c r="BJ208" s="463" t="n">
         <v>0.04139589952837174</v>
@@ -43005,10 +43005,10 @@
         <v>0.01514643719562741</v>
       </c>
       <c r="BM208" s="476" t="n">
-        <v>0.02457291526501374</v>
+        <v>0.02457291526501373</v>
       </c>
       <c r="BN208" s="476" t="n">
-        <v>0.03766037859691102</v>
+        <v>0.03766037859691104</v>
       </c>
       <c r="BO208" s="476" t="n">
         <v>0.03639589952843711</v>
@@ -43037,13 +43037,13 @@
         <v>0</v>
       </c>
       <c r="BX208" s="462" t="n">
-        <v>0.01525386749851554</v>
+        <v>0.01525386749851553</v>
       </c>
       <c r="BY208" s="463" t="n">
-        <v>0.02457986237464998</v>
+        <v>0.02457986237464997</v>
       </c>
       <c r="BZ208" s="463" t="n">
-        <v>0.03766930330901425</v>
+        <v>0.03766930330901426</v>
       </c>
       <c r="CA208" s="463" t="n">
         <v>0.03640312575861532</v>
@@ -43192,19 +43192,19 @@
         <v>78.06602822927782</v>
       </c>
       <c r="AP209" s="473" t="n">
-        <v>0.1523289916150374</v>
+        <v>0.1523289916150373</v>
       </c>
       <c r="AQ209" s="463" t="n">
-        <v>0.2203025241913979</v>
+        <v>0.2203025241913978</v>
       </c>
       <c r="AR209" s="463" t="n">
-        <v>0.2764803793923833</v>
+        <v>0.2764803793923834</v>
       </c>
       <c r="AS209" s="463" t="n">
         <v>0.2778840630926172</v>
       </c>
       <c r="AT209" s="474" t="n">
-        <v>0.2706995805829054</v>
+        <v>0.2706995805829055</v>
       </c>
       <c r="AU209" s="463" t="n">
         <v>0.150328991615562</v>
@@ -43251,7 +43251,7 @@
         <v>0.2764803793913655</v>
       </c>
       <c r="BJ209" s="463" t="n">
-        <v>0.2778840630925977</v>
+        <v>0.2778840630925978</v>
       </c>
       <c r="BK209" s="464" t="n">
         <v>0.27069958058254</v>
@@ -43453,7 +43453,7 @@
         <v>0.1400788597574751</v>
       </c>
       <c r="AR210" s="463" t="n">
-        <v>0.1945564267010485</v>
+        <v>0.1945564267010484</v>
       </c>
       <c r="AS210" s="463" t="n">
         <v>0.224223874016677</v>
@@ -43468,13 +43468,13 @@
         <v>0.1370788597584979</v>
       </c>
       <c r="AW210" s="463" t="n">
-        <v>0.1905564267010759</v>
+        <v>0.1905564267010758</v>
       </c>
       <c r="AX210" s="463" t="n">
         <v>0.2192238740183018</v>
       </c>
       <c r="AY210" s="474" t="n">
-        <v>0.2325638636241366</v>
+        <v>0.2325638636241364</v>
       </c>
       <c r="BA210" s="111" t="inlineStr">
         <is>
@@ -43503,13 +43503,13 @@
         <v>0.1400788597583546</v>
       </c>
       <c r="BI210" s="463" t="n">
-        <v>0.1945564267010706</v>
+        <v>0.1945564267010705</v>
       </c>
       <c r="BJ210" s="463" t="n">
         <v>0.2242238740179375</v>
       </c>
       <c r="BK210" s="464" t="n">
-        <v>0.2385638636240841</v>
+        <v>0.238563863624084</v>
       </c>
       <c r="BL210" s="462" t="n">
         <v>0.1069463898438243</v>
@@ -43518,13 +43518,13 @@
         <v>0.1370788597565229</v>
       </c>
       <c r="BN210" s="463" t="n">
-        <v>0.1905564267001823</v>
+        <v>0.1905564267001822</v>
       </c>
       <c r="BO210" s="463" t="n">
         <v>0.2192238740190105</v>
       </c>
       <c r="BP210" s="464" t="n">
-        <v>0.232563863625712</v>
+        <v>0.2325638636257118</v>
       </c>
       <c r="BR210" s="111" t="inlineStr">
         <is>
@@ -43553,13 +43553,13 @@
         <v>0.1371297097086172</v>
       </c>
       <c r="BZ210" s="463" t="n">
-        <v>0.190619396310396</v>
+        <v>0.1906193963103959</v>
       </c>
       <c r="CA210" s="463" t="n">
         <v>0.219288702392468</v>
       </c>
       <c r="CB210" s="464" t="n">
-        <v>0.2326245716906366</v>
+        <v>0.2326245716906365</v>
       </c>
       <c r="CC210" s="482" t="n">
         <v>0</v>
@@ -43875,7 +43875,7 @@
         <v>0.01270752050175844</v>
       </c>
       <c r="N212" s="495" t="n">
-        <v>0.01145779712646461</v>
+        <v>0.01145779712646462</v>
       </c>
       <c r="O212" s="495" t="n">
         <v>0.01519740279998345</v>
@@ -43925,7 +43925,7 @@
         <v>0.01270752050175844</v>
       </c>
       <c r="AE212" s="498" t="n">
-        <v>0.01145779712646461</v>
+        <v>0.01145779712646462</v>
       </c>
       <c r="AF212" s="498" t="n">
         <v>0.01519740279998345</v>
@@ -43945,7 +43945,7 @@
         <v>56.95743939637322</v>
       </c>
       <c r="AL212" s="207" t="n">
-        <v>125.4340021263682</v>
+        <v>125.4340021263681</v>
       </c>
       <c r="AM212" s="207" t="n">
         <v>198.6469442060442</v>
@@ -43957,13 +43957,13 @@
         <v>253.4996136678128</v>
       </c>
       <c r="AP212" s="500" t="n">
-        <v>0.04717803802921614</v>
+        <v>0.04717803802921613</v>
       </c>
       <c r="AQ212" s="501" t="n">
         <v>0.05499649478149887</v>
       </c>
       <c r="AR212" s="501" t="n">
-        <v>0.07423652969618728</v>
+        <v>0.0742365296961873</v>
       </c>
       <c r="AS212" s="501" t="n">
         <v>0.07460714012037564</v>
@@ -43972,10 +43972,10 @@
         <v>0.07154779663203432</v>
       </c>
       <c r="AU212" s="501" t="n">
-        <v>0.04519174577476525</v>
+        <v>0.04519174577476524</v>
       </c>
       <c r="AV212" s="501" t="n">
-        <v>0.05200591248202054</v>
+        <v>0.05200591248202053</v>
       </c>
       <c r="AW212" s="501" t="n">
         <v>0.07024743745704197</v>
@@ -44007,13 +44007,13 @@
         <v>253.499613668</v>
       </c>
       <c r="BG212" s="503" t="n">
-        <v>0.04717803802920442</v>
+        <v>0.04717803802920439</v>
       </c>
       <c r="BH212" s="504" t="n">
-        <v>0.05499649478149908</v>
+        <v>0.05499649478149906</v>
       </c>
       <c r="BI212" s="504" t="n">
-        <v>0.07423652969619425</v>
+        <v>0.07423652969619428</v>
       </c>
       <c r="BJ212" s="504" t="n">
         <v>0.0746071401203664</v>
@@ -44022,13 +44022,13 @@
         <v>0.07154779663202769</v>
       </c>
       <c r="BL212" s="504" t="n">
-        <v>0.04519174577525132</v>
+        <v>0.04519174577525131</v>
       </c>
       <c r="BM212" s="504" t="n">
-        <v>0.0520059124818681</v>
+        <v>0.05200591248186808</v>
       </c>
       <c r="BN212" s="504" t="n">
-        <v>0.07024743745703292</v>
+        <v>0.07024743745703295</v>
       </c>
       <c r="BO212" s="504" t="n">
         <v>0.06961912693560188</v>
@@ -44057,13 +44057,13 @@
         <v>0</v>
       </c>
       <c r="BX212" s="503" t="n">
-        <v>0.04545025766084106</v>
+        <v>0.04545025766084104</v>
       </c>
       <c r="BY212" s="504" t="n">
-        <v>0.05202146612652388</v>
+        <v>0.05202146612652386</v>
       </c>
       <c r="BZ212" s="504" t="n">
-        <v>0.07026534493523183</v>
+        <v>0.07026534493523186</v>
       </c>
       <c r="CA212" s="504" t="n">
         <v>0.06963425328170647</v>
@@ -44737,13 +44737,13 @@
         <v>34513.2223587984</v>
       </c>
       <c r="AM219" s="368" t="n">
-        <v>62356.24033128741</v>
+        <v>62356.2403312874</v>
       </c>
       <c r="AN219" s="368" t="n">
-        <v>77145.27984093783</v>
+        <v>77145.27984093782</v>
       </c>
       <c r="AO219" s="380" t="n">
-        <v>89580.48173789638</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="AP219" s="381" t="n">
         <v>588.3746268688296</v>
@@ -44752,13 +44752,13 @@
         <v>633.7546894283594</v>
       </c>
       <c r="AR219" s="372" t="n">
-        <v>637.7485705640689</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="AS219" s="372" t="n">
-        <v>672.9999385701531</v>
+        <v>672.9999385701529</v>
       </c>
       <c r="AT219" s="382" t="n">
-        <v>697.1163277335223</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="BA219" s="83" t="inlineStr">
         <is>
@@ -44772,13 +44772,13 @@
         <v>34513.2223587984</v>
       </c>
       <c r="BD219" s="375" t="n">
-        <v>62356.24033128741</v>
+        <v>62356.2403312874</v>
       </c>
       <c r="BE219" s="375" t="n">
-        <v>77145.27984093783</v>
+        <v>77145.27984093782</v>
       </c>
       <c r="BF219" s="392" t="n">
-        <v>89580.48173789638</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="BG219" s="386" t="n">
         <v>588.3746268688296</v>
@@ -44787,13 +44787,13 @@
         <v>633.7546894283594</v>
       </c>
       <c r="BI219" s="372" t="n">
-        <v>637.7485705640689</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="BJ219" s="372" t="n">
-        <v>672.9999385701531</v>
+        <v>672.9999385701529</v>
       </c>
       <c r="BK219" s="387" t="n">
-        <v>697.1163277335223</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="BR219" s="83" t="inlineStr">
         <is>
@@ -44813,7 +44813,7 @@
         <v>67827.29415650357</v>
       </c>
       <c r="BW219" s="392" t="n">
-        <v>75872.79326328443</v>
+        <v>75872.79326328442</v>
       </c>
       <c r="BX219" s="386" t="n">
         <v>588.3746268688296</v>
@@ -44822,13 +44822,13 @@
         <v>633.7546894283594</v>
       </c>
       <c r="BZ219" s="372" t="n">
-        <v>637.7485705640689</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="CA219" s="372" t="n">
-        <v>672.9999385701531</v>
+        <v>672.9999385701529</v>
       </c>
       <c r="CB219" s="387" t="n">
-        <v>697.1163277335223</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="CI219" s="199" t="n">
         <v>0</v>
@@ -44929,13 +44929,13 @@
         <v>44335.44858341062</v>
       </c>
       <c r="AL220" s="368" t="n">
-        <v>90066.83119143533</v>
+        <v>90066.83119143534</v>
       </c>
       <c r="AM220" s="368" t="n">
         <v>128629.5373619414</v>
       </c>
       <c r="AN220" s="368" t="n">
-        <v>144792.8127813951</v>
+        <v>144792.812781395</v>
       </c>
       <c r="AO220" s="380" t="n">
         <v>159406.5384542814</v>
@@ -44950,7 +44950,7 @@
         <v>1896.257077356014</v>
       </c>
       <c r="AS220" s="372" t="n">
-        <v>1944.270389399369</v>
+        <v>1944.270389399368</v>
       </c>
       <c r="AT220" s="382" t="n">
         <v>1996.685743614348</v>
@@ -44964,13 +44964,13 @@
         <v>44335.44858341062</v>
       </c>
       <c r="BC220" s="375" t="n">
-        <v>90066.83119143533</v>
+        <v>90066.83119143534</v>
       </c>
       <c r="BD220" s="375" t="n">
         <v>128629.5373619414</v>
       </c>
       <c r="BE220" s="375" t="n">
-        <v>144792.8127813951</v>
+        <v>144792.812781395</v>
       </c>
       <c r="BF220" s="392" t="n">
         <v>159406.5384542814</v>
@@ -44985,7 +44985,7 @@
         <v>1896.257077356014</v>
       </c>
       <c r="BJ220" s="372" t="n">
-        <v>1944.270389399369</v>
+        <v>1944.270389399368</v>
       </c>
       <c r="BK220" s="387" t="n">
         <v>1996.685743614348</v>
@@ -44999,7 +44999,7 @@
         <v>43753.34732863292</v>
       </c>
       <c r="BT220" s="375" t="n">
-        <v>88840.33369839963</v>
+        <v>88840.33369839964</v>
       </c>
       <c r="BU220" s="375" t="n">
         <v>126768.5801738806</v>
@@ -45020,7 +45020,7 @@
         <v>1896.257077356014</v>
       </c>
       <c r="CA220" s="372" t="n">
-        <v>1944.270389399369</v>
+        <v>1944.270389399368</v>
       </c>
       <c r="CB220" s="387" t="n">
         <v>1996.685743614348</v>
@@ -45130,7 +45130,7 @@
         <v>74511.52994761143</v>
       </c>
       <c r="AN221" s="368" t="n">
-        <v>88747.26377651544</v>
+        <v>88747.26377651542</v>
       </c>
       <c r="AO221" s="380" t="n">
         <v>112279.5677980626</v>
@@ -45165,7 +45165,7 @@
         <v>74511.52994761143</v>
       </c>
       <c r="BE221" s="375" t="n">
-        <v>88747.26377651544</v>
+        <v>88747.26377651542</v>
       </c>
       <c r="BF221" s="392" t="n">
         <v>112279.5677980626</v>
@@ -45200,7 +45200,7 @@
         <v>72979.60358100226</v>
       </c>
       <c r="BV221" s="375" t="n">
-        <v>86768.27594245521</v>
+        <v>86768.27594245519</v>
       </c>
       <c r="BW221" s="392" t="n">
         <v>109455.6807416929</v>
@@ -45517,13 +45517,13 @@
         <v>174399.7251953768</v>
       </c>
       <c r="AM223" s="408" t="n">
-        <v>265497.3076408403</v>
+        <v>265497.3076408402</v>
       </c>
       <c r="AN223" s="408" t="n">
-        <v>310685.3563988484</v>
+        <v>310685.3563988483</v>
       </c>
       <c r="AO223" s="409" t="n">
-        <v>361266.5879902404</v>
+        <v>361266.5879902403</v>
       </c>
       <c r="AP223" s="436" t="n">
         <v>1358.792448141342</v>
@@ -45532,7 +45532,7 @@
         <v>1314.76528173481</v>
       </c>
       <c r="AR223" s="437" t="n">
-        <v>1264.71030450529</v>
+        <v>1264.710304505289</v>
       </c>
       <c r="AS223" s="437" t="n">
         <v>1262.096640327373</v>
@@ -45552,13 +45552,13 @@
         <v>174399.7251953768</v>
       </c>
       <c r="BD223" s="440" t="n">
-        <v>265497.3076408403</v>
+        <v>265497.3076408402</v>
       </c>
       <c r="BE223" s="440" t="n">
-        <v>310685.3563988484</v>
+        <v>310685.3563988483</v>
       </c>
       <c r="BF223" s="441" t="n">
-        <v>361266.5879902404</v>
+        <v>361266.5879902403</v>
       </c>
       <c r="BG223" s="442" t="n">
         <v>1358.792448141342</v>
@@ -45567,7 +45567,7 @@
         <v>1314.76528173481</v>
       </c>
       <c r="BI223" s="443" t="n">
-        <v>1264.71030450529</v>
+        <v>1264.710304505289</v>
       </c>
       <c r="BJ223" s="443" t="n">
         <v>1262.096640327373</v>
@@ -47635,13 +47635,13 @@
         <v>34513.2223587984</v>
       </c>
       <c r="AM237" s="368" t="n">
-        <v>62356.24033128741</v>
+        <v>62356.2403312874</v>
       </c>
       <c r="AN237" s="368" t="n">
-        <v>77145.27984093783</v>
+        <v>77145.27984093782</v>
       </c>
       <c r="AO237" s="380" t="n">
-        <v>89580.48173789638</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="AP237" s="381" t="n">
         <v>588.3746268688296</v>
@@ -47650,13 +47650,13 @@
         <v>633.7546894283594</v>
       </c>
       <c r="AR237" s="372" t="n">
-        <v>637.7485705640689</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="AS237" s="372" t="n">
-        <v>672.9999385701531</v>
+        <v>672.9999385701529</v>
       </c>
       <c r="AT237" s="382" t="n">
-        <v>697.1163277335223</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="BA237" s="83" t="inlineStr">
         <is>
@@ -47670,13 +47670,13 @@
         <v>34513.2223587984</v>
       </c>
       <c r="BD237" s="375" t="n">
-        <v>62356.24033128741</v>
+        <v>62356.2403312874</v>
       </c>
       <c r="BE237" s="375" t="n">
-        <v>77145.27984093783</v>
+        <v>77145.27984093782</v>
       </c>
       <c r="BF237" s="392" t="n">
-        <v>89580.48173789638</v>
+        <v>89580.48173789636</v>
       </c>
       <c r="BG237" s="386" t="n">
         <v>588.3746268688296</v>
@@ -47685,13 +47685,13 @@
         <v>633.7546894283594</v>
       </c>
       <c r="BI237" s="372" t="n">
-        <v>637.7485705640689</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="BJ237" s="372" t="n">
-        <v>672.9999385701531</v>
+        <v>672.9999385701529</v>
       </c>
       <c r="BK237" s="387" t="n">
-        <v>697.1163277335223</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="BR237" s="83" t="inlineStr">
         <is>
@@ -47711,7 +47711,7 @@
         <v>67827.29415650357</v>
       </c>
       <c r="BW237" s="392" t="n">
-        <v>75872.79326328443</v>
+        <v>75872.79326328442</v>
       </c>
       <c r="BX237" s="386" t="n">
         <v>588.3746268688296</v>
@@ -47720,13 +47720,13 @@
         <v>633.7546894283594</v>
       </c>
       <c r="BZ237" s="372" t="n">
-        <v>637.7485705640689</v>
+        <v>637.7485705640688</v>
       </c>
       <c r="CA237" s="372" t="n">
-        <v>672.9999385701531</v>
+        <v>672.9999385701529</v>
       </c>
       <c r="CB237" s="387" t="n">
-        <v>697.1163277335223</v>
+        <v>697.1163277335222</v>
       </c>
       <c r="CI237" s="199" t="n">
         <v>0</v>
@@ -47827,13 +47827,13 @@
         <v>44335.44858341062</v>
       </c>
       <c r="AL238" s="368" t="n">
-        <v>90066.83119143533</v>
+        <v>90066.83119143534</v>
       </c>
       <c r="AM238" s="368" t="n">
         <v>128629.5373619414</v>
       </c>
       <c r="AN238" s="368" t="n">
-        <v>144792.8127813951</v>
+        <v>144792.812781395</v>
       </c>
       <c r="AO238" s="380" t="n">
         <v>159406.5384542814</v>
@@ -47848,7 +47848,7 @@
         <v>1896.257077356014</v>
       </c>
       <c r="AS238" s="372" t="n">
-        <v>1944.270389399369</v>
+        <v>1944.270389399368</v>
       </c>
       <c r="AT238" s="382" t="n">
         <v>1996.685743614348</v>
@@ -47862,13 +47862,13 @@
         <v>44335.44858341062</v>
       </c>
       <c r="BC238" s="375" t="n">
-        <v>90066.83119143533</v>
+        <v>90066.83119143534</v>
       </c>
       <c r="BD238" s="375" t="n">
         <v>128629.5373619414</v>
       </c>
       <c r="BE238" s="375" t="n">
-        <v>144792.8127813951</v>
+        <v>144792.812781395</v>
       </c>
       <c r="BF238" s="392" t="n">
         <v>159406.5384542814</v>
@@ -47883,7 +47883,7 @@
         <v>1896.257077356014</v>
       </c>
       <c r="BJ238" s="372" t="n">
-        <v>1944.270389399369</v>
+        <v>1944.270389399368</v>
       </c>
       <c r="BK238" s="387" t="n">
         <v>1996.685743614348</v>
@@ -47897,7 +47897,7 @@
         <v>43753.34732863292</v>
       </c>
       <c r="BT238" s="375" t="n">
-        <v>88840.33369839963</v>
+        <v>88840.33369839964</v>
       </c>
       <c r="BU238" s="375" t="n">
         <v>126768.5801738806</v>
@@ -47918,7 +47918,7 @@
         <v>1896.257077356014</v>
       </c>
       <c r="CA238" s="372" t="n">
-        <v>1944.270389399369</v>
+        <v>1944.270389399368</v>
       </c>
       <c r="CB238" s="387" t="n">
         <v>1996.685743614348</v>
@@ -48028,7 +48028,7 @@
         <v>74511.52994761143</v>
       </c>
       <c r="AN239" s="368" t="n">
-        <v>88747.26377651544</v>
+        <v>88747.26377651542</v>
       </c>
       <c r="AO239" s="380" t="n">
         <v>112279.5677980626</v>
@@ -48063,7 +48063,7 @@
         <v>74511.52994761143</v>
       </c>
       <c r="BE239" s="375" t="n">
-        <v>88747.26377651544</v>
+        <v>88747.26377651542</v>
       </c>
       <c r="BF239" s="392" t="n">
         <v>112279.5677980626</v>
@@ -48098,7 +48098,7 @@
         <v>72979.60358100226</v>
       </c>
       <c r="BV239" s="375" t="n">
-        <v>86768.27594245521</v>
+        <v>86768.27594245519</v>
       </c>
       <c r="BW239" s="392" t="n">
         <v>109455.6807416929</v>
@@ -48415,13 +48415,13 @@
         <v>174399.7251953768</v>
       </c>
       <c r="AM241" s="408" t="n">
-        <v>265497.3076408403</v>
+        <v>265497.3076408402</v>
       </c>
       <c r="AN241" s="408" t="n">
-        <v>310685.3563988484</v>
+        <v>310685.3563988483</v>
       </c>
       <c r="AO241" s="409" t="n">
-        <v>361266.5879902404</v>
+        <v>361266.5879902403</v>
       </c>
       <c r="AP241" s="436" t="n">
         <v>1358.792448141342</v>
@@ -48430,7 +48430,7 @@
         <v>1314.76528173481</v>
       </c>
       <c r="AR241" s="437" t="n">
-        <v>1264.71030450529</v>
+        <v>1264.710304505289</v>
       </c>
       <c r="AS241" s="437" t="n">
         <v>1262.096640327373</v>
@@ -48450,13 +48450,13 @@
         <v>174399.7251953768</v>
       </c>
       <c r="BD241" s="440" t="n">
-        <v>265497.3076408403</v>
+        <v>265497.3076408402</v>
       </c>
       <c r="BE241" s="440" t="n">
-        <v>310685.3563988484</v>
+        <v>310685.3563988483</v>
       </c>
       <c r="BF241" s="441" t="n">
-        <v>361266.5879902404</v>
+        <v>361266.5879902403</v>
       </c>
       <c r="BG241" s="442" t="n">
         <v>1358.792448141342</v>
@@ -48465,7 +48465,7 @@
         <v>1314.76528173481</v>
       </c>
       <c r="BI241" s="443" t="n">
-        <v>1264.71030450529</v>
+        <v>1264.710304505289</v>
       </c>
       <c r="BJ241" s="443" t="n">
         <v>1262.096640327373</v>
@@ -49039,7 +49039,7 @@
         <v>1088657.416548779</v>
       </c>
       <c r="AL246" s="368" t="n">
-        <v>2466821.589989235</v>
+        <v>2466821.589989234</v>
       </c>
       <c r="AM246" s="368" t="n">
         <v>2936880.353989952</v>
@@ -49074,7 +49074,7 @@
         <v>1088657.416548779</v>
       </c>
       <c r="BC246" s="375" t="n">
-        <v>2466821.589989235</v>
+        <v>2466821.589989234</v>
       </c>
       <c r="BD246" s="375" t="n">
         <v>2936880.353989952</v>
@@ -49109,7 +49109,7 @@
         <v>1083071.734338342</v>
       </c>
       <c r="BT246" s="375" t="n">
-        <v>2473714.915708591</v>
+        <v>2473714.91570859</v>
       </c>
       <c r="BU246" s="375" t="n">
         <v>2948412.495226348</v>
@@ -49218,22 +49218,22 @@
         <v>366788.7949176782</v>
       </c>
       <c r="AL247" s="368" t="n">
-        <v>503342.2264200607</v>
+        <v>503342.2264200606</v>
       </c>
       <c r="AM247" s="368" t="n">
         <v>541986.1121404731</v>
       </c>
       <c r="AN247" s="368" t="n">
-        <v>615979.704802421</v>
+        <v>615979.7048024212</v>
       </c>
       <c r="AO247" s="380" t="n">
-        <v>708815.1061859919</v>
+        <v>708815.1061859918</v>
       </c>
       <c r="AP247" s="381" t="n">
-        <v>2431.506518122067</v>
+        <v>2431.506518122066</v>
       </c>
       <c r="AQ247" s="372" t="n">
-        <v>2868.321542207705</v>
+        <v>2868.321542207704</v>
       </c>
       <c r="AR247" s="372" t="n">
         <v>3053.224011881924</v>
@@ -49253,22 +49253,22 @@
         <v>366788.7949176782</v>
       </c>
       <c r="BC247" s="375" t="n">
-        <v>503342.2264200607</v>
+        <v>503342.2264200606</v>
       </c>
       <c r="BD247" s="375" t="n">
         <v>541986.1121404731</v>
       </c>
       <c r="BE247" s="375" t="n">
-        <v>615979.704802421</v>
+        <v>615979.7048024212</v>
       </c>
       <c r="BF247" s="392" t="n">
-        <v>708815.1061859919</v>
+        <v>708815.1061859918</v>
       </c>
       <c r="BG247" s="386" t="n">
-        <v>2431.506518122067</v>
+        <v>2431.506518122066</v>
       </c>
       <c r="BH247" s="372" t="n">
-        <v>2868.321542207705</v>
+        <v>2868.321542207704</v>
       </c>
       <c r="BI247" s="372" t="n">
         <v>3053.224011881924</v>
@@ -49285,25 +49285,25 @@
         </is>
       </c>
       <c r="BS247" s="391" t="n">
-        <v>366667.9285133773</v>
+        <v>366667.9285133772</v>
       </c>
       <c r="BT247" s="375" t="n">
-        <v>505047.1943934751</v>
+        <v>505047.194393475</v>
       </c>
       <c r="BU247" s="375" t="n">
         <v>544729.710622909</v>
       </c>
       <c r="BV247" s="375" t="n">
-        <v>619973.9607562228</v>
+        <v>619973.9607562231</v>
       </c>
       <c r="BW247" s="392" t="n">
-        <v>714402.3553931733</v>
+        <v>714402.3553931732</v>
       </c>
       <c r="BX247" s="386" t="n">
-        <v>2431.506518122067</v>
+        <v>2431.506518122066</v>
       </c>
       <c r="BY247" s="372" t="n">
-        <v>2868.321542207705</v>
+        <v>2868.321542207704</v>
       </c>
       <c r="BZ247" s="372" t="n">
         <v>3053.224011881924</v>
@@ -49397,13 +49397,13 @@
         <v>296582.489848911</v>
       </c>
       <c r="AL248" s="368" t="n">
-        <v>423566.0437798895</v>
+        <v>423566.0437798894</v>
       </c>
       <c r="AM248" s="368" t="n">
-        <v>467857.786612624</v>
+        <v>467857.7866126241</v>
       </c>
       <c r="AN248" s="368" t="n">
-        <v>534385.0713972369</v>
+        <v>534385.071397237</v>
       </c>
       <c r="AO248" s="380" t="n">
         <v>606576.777989015</v>
@@ -49412,13 +49412,13 @@
         <v>2191.608206723807</v>
       </c>
       <c r="AQ248" s="372" t="n">
-        <v>2411.990305032362</v>
+        <v>2411.990305032361</v>
       </c>
       <c r="AR248" s="372" t="n">
-        <v>2550.000522427323</v>
+        <v>2550.000522427324</v>
       </c>
       <c r="AS248" s="372" t="n">
-        <v>2706.609831188207</v>
+        <v>2706.609831188208</v>
       </c>
       <c r="AT248" s="382" t="n">
         <v>2781.951297580739</v>
@@ -49432,13 +49432,13 @@
         <v>296582.489848911</v>
       </c>
       <c r="BC248" s="375" t="n">
-        <v>423566.0437798895</v>
+        <v>423566.0437798894</v>
       </c>
       <c r="BD248" s="375" t="n">
-        <v>467857.786612624</v>
+        <v>467857.7866126241</v>
       </c>
       <c r="BE248" s="375" t="n">
-        <v>534385.0713972369</v>
+        <v>534385.071397237</v>
       </c>
       <c r="BF248" s="392" t="n">
         <v>606576.777989015</v>
@@ -49447,13 +49447,13 @@
         <v>2191.608206723807</v>
       </c>
       <c r="BH248" s="372" t="n">
-        <v>2411.990305032362</v>
+        <v>2411.990305032361</v>
       </c>
       <c r="BI248" s="372" t="n">
-        <v>2550.000522427323</v>
+        <v>2550.000522427324</v>
       </c>
       <c r="BJ248" s="372" t="n">
-        <v>2706.609831188207</v>
+        <v>2706.609831188208</v>
       </c>
       <c r="BK248" s="387" t="n">
         <v>2781.951297580739</v>
@@ -49470,10 +49470,10 @@
         <v>424861.0844800866</v>
       </c>
       <c r="BU248" s="375" t="n">
-        <v>469989.379791395</v>
+        <v>469989.3797913951</v>
       </c>
       <c r="BV248" s="375" t="n">
-        <v>537625.6260895854</v>
+        <v>537625.6260895856</v>
       </c>
       <c r="BW248" s="392" t="n">
         <v>611148.6154412836</v>
@@ -49482,13 +49482,13 @@
         <v>2191.608206723807</v>
       </c>
       <c r="BY248" s="372" t="n">
-        <v>2411.990305032362</v>
+        <v>2411.990305032361</v>
       </c>
       <c r="BZ248" s="372" t="n">
-        <v>2550.000522427323</v>
+        <v>2550.000522427324</v>
       </c>
       <c r="CA248" s="372" t="n">
-        <v>2706.609831188207</v>
+        <v>2706.609831188208</v>
       </c>
       <c r="CB248" s="387" t="n">
         <v>2781.951297580739</v>
@@ -49582,19 +49582,19 @@
         <v>248677.0846304711</v>
       </c>
       <c r="AN249" s="408" t="n">
-        <v>263219.0138342188</v>
+        <v>263219.0138342187</v>
       </c>
       <c r="AO249" s="409" t="n">
         <v>280543.0734739052</v>
       </c>
       <c r="AP249" s="410" t="n">
-        <v>35258.65751305073</v>
+        <v>35258.65751305072</v>
       </c>
       <c r="AQ249" s="411" t="n">
         <v>31737.73461442073</v>
       </c>
       <c r="AR249" s="411" t="n">
-        <v>32248.44280250057</v>
+        <v>32248.44280250056</v>
       </c>
       <c r="AS249" s="411" t="n">
         <v>33276.34956892231</v>
@@ -49617,19 +49617,19 @@
         <v>248677.0846304711</v>
       </c>
       <c r="BE249" s="420" t="n">
-        <v>263219.0138342188</v>
+        <v>263219.0138342187</v>
       </c>
       <c r="BF249" s="421" t="n">
         <v>280543.0734739052</v>
       </c>
       <c r="BG249" s="416" t="n">
-        <v>35258.65751305073</v>
+        <v>35258.65751305072</v>
       </c>
       <c r="BH249" s="417" t="n">
         <v>31737.73461442073</v>
       </c>
       <c r="BI249" s="417" t="n">
-        <v>32248.44280250057</v>
+        <v>32248.44280250056</v>
       </c>
       <c r="BJ249" s="417" t="n">
         <v>33276.34956892231</v>
@@ -49643,7 +49643,7 @@
         </is>
       </c>
       <c r="BS249" s="419" t="n">
-        <v>304354.4169790544</v>
+        <v>304354.4169790543</v>
       </c>
       <c r="BT249" s="420" t="n">
         <v>240101.6117355968</v>
@@ -49658,13 +49658,13 @@
         <v>280306.7074925736</v>
       </c>
       <c r="BX249" s="416" t="n">
-        <v>35258.65751305073</v>
+        <v>35258.65751305072</v>
       </c>
       <c r="BY249" s="417" t="n">
         <v>31737.73461442073</v>
       </c>
       <c r="BZ249" s="417" t="n">
-        <v>32248.44280250057</v>
+        <v>32248.44280250056</v>
       </c>
       <c r="CA249" s="417" t="n">
         <v>33276.34956892231</v>
@@ -49755,10 +49755,10 @@
         <v>2056602.927149346</v>
       </c>
       <c r="AL250" s="408" t="n">
-        <v>3634034.47108008</v>
+        <v>3634034.471080079</v>
       </c>
       <c r="AM250" s="408" t="n">
-        <v>4195401.33737352</v>
+        <v>4195401.337373521</v>
       </c>
       <c r="AN250" s="408" t="n">
         <v>4904903.359693628</v>
@@ -49770,7 +49770,7 @@
         <v>1712.566138225755</v>
       </c>
       <c r="AQ250" s="437" t="n">
-        <v>1594.384503961529</v>
+        <v>1594.384503961528</v>
       </c>
       <c r="AR250" s="437" t="n">
         <v>1602.588677228673</v>
@@ -49790,10 +49790,10 @@
         <v>2056602.927149346</v>
       </c>
       <c r="BC250" s="440" t="n">
-        <v>3634034.47108008</v>
+        <v>3634034.471080079</v>
       </c>
       <c r="BD250" s="440" t="n">
-        <v>4195401.33737352</v>
+        <v>4195401.337373521</v>
       </c>
       <c r="BE250" s="440" t="n">
         <v>4904903.359693628</v>
@@ -49805,7 +49805,7 @@
         <v>1712.566138225755</v>
       </c>
       <c r="BH250" s="443" t="n">
-        <v>1594.384503961529</v>
+        <v>1594.384503961528</v>
       </c>
       <c r="BI250" s="443" t="n">
         <v>1602.588677228673</v>
@@ -49828,7 +49828,7 @@
         <v>3643724.806317749</v>
       </c>
       <c r="BU250" s="440" t="n">
-        <v>4211596.136136963</v>
+        <v>4211596.136136964</v>
       </c>
       <c r="BV250" s="440" t="n">
         <v>4929401.874118304</v>
@@ -49840,10 +49840,10 @@
         <v>1714.36344498729</v>
       </c>
       <c r="BY250" s="443" t="n">
-        <v>1594.095642602882</v>
+        <v>1594.095642602881</v>
       </c>
       <c r="BZ250" s="443" t="n">
-        <v>1602.311660747569</v>
+        <v>1602.31166074757</v>
       </c>
       <c r="CA250" s="443" t="n">
         <v>1606.153626924828</v>
@@ -51945,7 +51945,7 @@
         <v>1088657.416548779</v>
       </c>
       <c r="AL264" s="368" t="n">
-        <v>2466821.589989235</v>
+        <v>2466821.589989234</v>
       </c>
       <c r="AM264" s="368" t="n">
         <v>2936880.353989952</v>
@@ -51957,13 +51957,13 @@
         <v>4163875.479483539</v>
       </c>
       <c r="AP264" s="381" t="n">
-        <v>1201.507088575482</v>
+        <v>1201.507088575481</v>
       </c>
       <c r="AQ264" s="372" t="n">
-        <v>1284.396332331807</v>
+        <v>1284.396332331806</v>
       </c>
       <c r="AR264" s="372" t="n">
-        <v>1305.748676164959</v>
+        <v>1305.74867616496</v>
       </c>
       <c r="AS264" s="372" t="n">
         <v>1315.265142248585</v>
@@ -51980,7 +51980,7 @@
         <v>1088657.416548779</v>
       </c>
       <c r="BC264" s="375" t="n">
-        <v>2466821.589989235</v>
+        <v>2466821.589989234</v>
       </c>
       <c r="BD264" s="375" t="n">
         <v>2936880.353989952</v>
@@ -51992,13 +51992,13 @@
         <v>4163875.479483539</v>
       </c>
       <c r="BG264" s="386" t="n">
-        <v>1201.507088575482</v>
+        <v>1201.507088575481</v>
       </c>
       <c r="BH264" s="372" t="n">
-        <v>1284.396332331807</v>
+        <v>1284.396332331806</v>
       </c>
       <c r="BI264" s="372" t="n">
-        <v>1305.748676164959</v>
+        <v>1305.74867616496</v>
       </c>
       <c r="BJ264" s="372" t="n">
         <v>1315.265142248585</v>
@@ -52015,7 +52015,7 @@
         <v>1083071.734338342</v>
       </c>
       <c r="BT264" s="375" t="n">
-        <v>2473714.915708591</v>
+        <v>2473714.91570859</v>
       </c>
       <c r="BU264" s="375" t="n">
         <v>2948412.495226348</v>
@@ -52027,13 +52027,13 @@
         <v>4189168.81122065</v>
       </c>
       <c r="BX264" s="386" t="n">
-        <v>1201.507088575482</v>
+        <v>1201.507088575481</v>
       </c>
       <c r="BY264" s="372" t="n">
-        <v>1284.396332331807</v>
+        <v>1284.396332331806</v>
       </c>
       <c r="BZ264" s="372" t="n">
-        <v>1305.748676164959</v>
+        <v>1305.74867616496</v>
       </c>
       <c r="CA264" s="372" t="n">
         <v>1315.265142248585</v>
@@ -52048,7 +52048,7 @@
         <v>1.000000000005634</v>
       </c>
       <c r="CK264" s="397" t="n">
-        <v>0.9999999999984117</v>
+        <v>0.9999999999984118</v>
       </c>
       <c r="CL264" s="397" t="n">
         <v>0.9999999999987462</v>
@@ -52060,7 +52060,7 @@
         <v>1.000000000002135</v>
       </c>
       <c r="CO264" s="103" t="n">
-        <v>0.9999999999998846</v>
+        <v>0.9999999999998848</v>
       </c>
       <c r="CP264" s="103" t="n">
         <v>1.000000000000007</v>
@@ -52078,7 +52078,7 @@
         <v>1.000000000005634</v>
       </c>
       <c r="CV264" s="397" t="n">
-        <v>0.9999999999984117</v>
+        <v>0.9999999999984118</v>
       </c>
       <c r="CW264" s="397" t="n">
         <v>0.9999999999987462</v>
@@ -52090,7 +52090,7 @@
         <v>1.0000000000002</v>
       </c>
       <c r="CZ264" s="103" t="n">
-        <v>0.9999999999999111</v>
+        <v>0.9999999999999113</v>
       </c>
       <c r="DA264" s="103" t="n">
         <v>1.000000000000014</v>
@@ -52117,19 +52117,19 @@
         <v>0</v>
       </c>
       <c r="DK264" s="391" t="n">
-        <v>242214.1477819226</v>
+        <v>242214.1477819225</v>
       </c>
       <c r="DL264" s="375" t="n">
-        <v>45650.81714687864</v>
+        <v>45650.81714687862</v>
       </c>
       <c r="DM264" s="375" t="n">
-        <v>48240.88012252509</v>
+        <v>48240.88012252508</v>
       </c>
       <c r="DN264" s="375" t="n">
-        <v>47894.66624533232</v>
+        <v>47894.66624533231</v>
       </c>
       <c r="DO264" s="392" t="n">
-        <v>47466.23510528297</v>
+        <v>47466.23510528294</v>
       </c>
     </row>
     <row r="265">
@@ -52212,28 +52212,28 @@
         <v>366788.7949176782</v>
       </c>
       <c r="AL265" s="368" t="n">
-        <v>503342.2264200607</v>
+        <v>503342.2264200606</v>
       </c>
       <c r="AM265" s="368" t="n">
         <v>541986.1121404731</v>
       </c>
       <c r="AN265" s="368" t="n">
-        <v>615979.704802421</v>
+        <v>615979.7048024212</v>
       </c>
       <c r="AO265" s="380" t="n">
-        <v>708815.1061859919</v>
+        <v>708815.1061859918</v>
       </c>
       <c r="AP265" s="381" t="n">
-        <v>2431.50651812345</v>
+        <v>2431.506518123449</v>
       </c>
       <c r="AQ265" s="372" t="n">
-        <v>2868.321542209979</v>
+        <v>2868.321542209978</v>
       </c>
       <c r="AR265" s="372" t="n">
         <v>3053.224011875301</v>
       </c>
       <c r="AS265" s="372" t="n">
-        <v>3182.97165330672</v>
+        <v>3182.971653306721</v>
       </c>
       <c r="AT265" s="382" t="n">
         <v>3295.472334986086</v>
@@ -52247,28 +52247,28 @@
         <v>366788.7949176782</v>
       </c>
       <c r="BC265" s="375" t="n">
-        <v>503342.2264200607</v>
+        <v>503342.2264200606</v>
       </c>
       <c r="BD265" s="375" t="n">
         <v>541986.1121404731</v>
       </c>
       <c r="BE265" s="375" t="n">
-        <v>615979.704802421</v>
+        <v>615979.7048024212</v>
       </c>
       <c r="BF265" s="392" t="n">
-        <v>708815.1061859919</v>
+        <v>708815.1061859918</v>
       </c>
       <c r="BG265" s="386" t="n">
-        <v>2431.50651812345</v>
+        <v>2431.506518123449</v>
       </c>
       <c r="BH265" s="372" t="n">
-        <v>2868.321542209979</v>
+        <v>2868.321542209978</v>
       </c>
       <c r="BI265" s="372" t="n">
         <v>3053.224011875301</v>
       </c>
       <c r="BJ265" s="372" t="n">
-        <v>3182.97165330672</v>
+        <v>3182.971653306721</v>
       </c>
       <c r="BK265" s="387" t="n">
         <v>3295.472334986086</v>
@@ -52282,28 +52282,28 @@
         <v>366667.9285133773</v>
       </c>
       <c r="BT265" s="375" t="n">
-        <v>505047.1943934751</v>
+        <v>505047.194393475</v>
       </c>
       <c r="BU265" s="375" t="n">
         <v>544729.7106229089</v>
       </c>
       <c r="BV265" s="375" t="n">
-        <v>619973.9607562228</v>
+        <v>619973.960756223</v>
       </c>
       <c r="BW265" s="392" t="n">
-        <v>714402.3553931734</v>
+        <v>714402.3553931733</v>
       </c>
       <c r="BX265" s="386" t="n">
-        <v>2431.50651812345</v>
+        <v>2431.506518123449</v>
       </c>
       <c r="BY265" s="372" t="n">
-        <v>2868.321542209979</v>
+        <v>2868.321542209978</v>
       </c>
       <c r="BZ265" s="372" t="n">
         <v>3053.224011875301</v>
       </c>
       <c r="CA265" s="372" t="n">
-        <v>3182.97165330672</v>
+        <v>3182.971653306721</v>
       </c>
       <c r="CB265" s="387" t="n">
         <v>3295.472334986086</v>
@@ -52336,7 +52336,7 @@
         <v>1.000000000002753</v>
       </c>
       <c r="CR265" s="104" t="n">
-        <v>0.999999999998307</v>
+        <v>0.9999999999983072</v>
       </c>
       <c r="CT265" s="396" t="n">
         <v>0.9999999999987477</v>
@@ -52354,7 +52354,7 @@
         <v>0.9999999999883175</v>
       </c>
       <c r="CY265" s="102" t="n">
-        <v>1.000000000000873</v>
+        <v>1.000000000000874</v>
       </c>
       <c r="CZ265" s="103" t="n">
         <v>1.000000000001241</v>
@@ -52363,10 +52363,10 @@
         <v>1.000000000001305</v>
       </c>
       <c r="DB265" s="103" t="n">
-        <v>1.000000000003774</v>
+        <v>1.000000000003773</v>
       </c>
       <c r="DC265" s="104" t="n">
-        <v>0.9999999999979807</v>
+        <v>0.9999999999979811</v>
       </c>
       <c r="DE265" s="391" t="n">
         <v>0</v>
@@ -52384,7 +52384,7 @@
         <v>0</v>
       </c>
       <c r="DK265" s="391" t="n">
-        <v>63581.39137306197</v>
+        <v>63581.39137306196</v>
       </c>
       <c r="DL265" s="375" t="n">
         <v>36840.47335040204</v>
@@ -52393,10 +52393,10 @@
         <v>41783.40242293903</v>
       </c>
       <c r="DN265" s="375" t="n">
-        <v>47538.68160706645</v>
+        <v>47538.68160706644</v>
       </c>
       <c r="DO265" s="392" t="n">
-        <v>52637.13038060635</v>
+        <v>52637.13038060634</v>
       </c>
     </row>
     <row r="266">
@@ -52479,13 +52479,13 @@
         <v>296582.489848911</v>
       </c>
       <c r="AL266" s="368" t="n">
-        <v>423566.0437798895</v>
+        <v>423566.0437798894</v>
       </c>
       <c r="AM266" s="368" t="n">
-        <v>467857.786612624</v>
+        <v>467857.7866126241</v>
       </c>
       <c r="AN266" s="368" t="n">
-        <v>534385.0713972369</v>
+        <v>534385.071397237</v>
       </c>
       <c r="AO266" s="380" t="n">
         <v>606576.777989015</v>
@@ -52497,13 +52497,13 @@
         <v>2411.990305032698</v>
       </c>
       <c r="AR266" s="372" t="n">
-        <v>2550.000522421599</v>
+        <v>2550.000522421598</v>
       </c>
       <c r="AS266" s="372" t="n">
         <v>2706.609831179766</v>
       </c>
       <c r="AT266" s="382" t="n">
-        <v>2781.951297584707</v>
+        <v>2781.951297584706</v>
       </c>
       <c r="BA266" s="111" t="inlineStr">
         <is>
@@ -52514,13 +52514,13 @@
         <v>296582.489848911</v>
       </c>
       <c r="BC266" s="375" t="n">
-        <v>423566.0437798895</v>
+        <v>423566.0437798894</v>
       </c>
       <c r="BD266" s="375" t="n">
-        <v>467857.786612624</v>
+        <v>467857.7866126241</v>
       </c>
       <c r="BE266" s="375" t="n">
-        <v>534385.0713972369</v>
+        <v>534385.071397237</v>
       </c>
       <c r="BF266" s="392" t="n">
         <v>606576.777989015</v>
@@ -52532,13 +52532,13 @@
         <v>2411.990305032698</v>
       </c>
       <c r="BI266" s="372" t="n">
-        <v>2550.000522421599</v>
+        <v>2550.000522421598</v>
       </c>
       <c r="BJ266" s="372" t="n">
         <v>2706.609831179766</v>
       </c>
       <c r="BK266" s="387" t="n">
-        <v>2781.951297584707</v>
+        <v>2781.951297584706</v>
       </c>
       <c r="BR266" s="111" t="inlineStr">
         <is>
@@ -52549,10 +52549,10 @@
         <v>296669.3752177259</v>
       </c>
       <c r="BT266" s="375" t="n">
-        <v>424861.0844800867</v>
+        <v>424861.0844800866</v>
       </c>
       <c r="BU266" s="375" t="n">
-        <v>469989.379791395</v>
+        <v>469989.3797913951</v>
       </c>
       <c r="BV266" s="375" t="n">
         <v>537625.6260895855</v>
@@ -52567,13 +52567,13 @@
         <v>2411.990305032698</v>
       </c>
       <c r="BZ266" s="372" t="n">
-        <v>2550.000522421599</v>
+        <v>2550.000522421598</v>
       </c>
       <c r="CA266" s="372" t="n">
         <v>2706.609831179766</v>
       </c>
       <c r="CB266" s="387" t="n">
-        <v>2781.951297584707</v>
+        <v>2781.951297584706</v>
       </c>
       <c r="CI266" s="396" t="n">
         <v>0.9999999999538677</v>
@@ -52585,7 +52585,7 @@
         <v>1.000000000025335</v>
       </c>
       <c r="CL266" s="397" t="n">
-        <v>0.999999999993972</v>
+        <v>0.9999999999939722</v>
       </c>
       <c r="CM266" s="398" t="n">
         <v>1.000000000000732</v>
@@ -52600,7 +52600,7 @@
         <v>1.000000000001489</v>
       </c>
       <c r="CQ266" s="103" t="n">
-        <v>0.9999999999994595</v>
+        <v>0.9999999999994591</v>
       </c>
       <c r="CR266" s="104" t="n">
         <v>1.000000000000587</v>
@@ -52615,7 +52615,7 @@
         <v>1.000000000025335</v>
       </c>
       <c r="CW266" s="397" t="n">
-        <v>0.999999999993972</v>
+        <v>0.9999999999939722</v>
       </c>
       <c r="CX266" s="398" t="n">
         <v>1.000000000000732</v>
@@ -52630,7 +52630,7 @@
         <v>1.000000000001817</v>
       </c>
       <c r="DB266" s="103" t="n">
-        <v>0.9999999999995079</v>
+        <v>0.9999999999995076</v>
       </c>
       <c r="DC266" s="104" t="n">
         <v>1.000000000000642</v>
@@ -52752,25 +52752,25 @@
         <v>248677.0846304711</v>
       </c>
       <c r="AN267" s="408" t="n">
-        <v>263219.0138342188</v>
+        <v>263219.0138342187</v>
       </c>
       <c r="AO267" s="409" t="n">
         <v>280543.0734739052</v>
       </c>
       <c r="AP267" s="410" t="n">
-        <v>35258.65751158106</v>
+        <v>35258.65751158107</v>
       </c>
       <c r="AQ267" s="411" t="n">
-        <v>31737.7346160196</v>
+        <v>31737.73461601958</v>
       </c>
       <c r="AR267" s="411" t="n">
-        <v>32248.44280333589</v>
+        <v>32248.4428033359</v>
       </c>
       <c r="AS267" s="411" t="n">
-        <v>33276.34956683774</v>
+        <v>33276.34956683776</v>
       </c>
       <c r="AT267" s="412" t="n">
-        <v>34452.93960486876</v>
+        <v>34452.93960486878</v>
       </c>
       <c r="BA267" s="111" t="inlineStr">
         <is>
@@ -52787,25 +52787,25 @@
         <v>248677.0846304711</v>
       </c>
       <c r="BE267" s="420" t="n">
-        <v>263219.0138342188</v>
+        <v>263219.0138342187</v>
       </c>
       <c r="BF267" s="421" t="n">
         <v>280543.0734739052</v>
       </c>
       <c r="BG267" s="416" t="n">
-        <v>35258.65751158106</v>
+        <v>35258.65751158107</v>
       </c>
       <c r="BH267" s="417" t="n">
-        <v>31737.7346160196</v>
+        <v>31737.73461601958</v>
       </c>
       <c r="BI267" s="417" t="n">
-        <v>32248.44280333589</v>
+        <v>32248.4428033359</v>
       </c>
       <c r="BJ267" s="417" t="n">
-        <v>33276.34956683774</v>
+        <v>33276.34956683776</v>
       </c>
       <c r="BK267" s="418" t="n">
-        <v>34452.93960486876</v>
+        <v>34452.93960486878</v>
       </c>
       <c r="BR267" s="111" t="inlineStr">
         <is>
@@ -52828,19 +52828,19 @@
         <v>280306.7074925736</v>
       </c>
       <c r="BX267" s="416" t="n">
-        <v>35258.65751158106</v>
+        <v>35258.65751158107</v>
       </c>
       <c r="BY267" s="417" t="n">
-        <v>31737.7346160196</v>
+        <v>31737.73461601958</v>
       </c>
       <c r="BZ267" s="417" t="n">
-        <v>32248.44280333589</v>
+        <v>32248.4428033359</v>
       </c>
       <c r="CA267" s="417" t="n">
-        <v>33276.34956683774</v>
+        <v>33276.34956683776</v>
       </c>
       <c r="CB267" s="418" t="n">
-        <v>34452.93960486876</v>
+        <v>34452.93960486878</v>
       </c>
       <c r="CI267" s="422" t="n">
         <v>1</v>
@@ -52867,7 +52867,7 @@
         <v>1.000000000032071</v>
       </c>
       <c r="CQ267" s="133" t="n">
-        <v>1.000000000018368</v>
+        <v>1.000000000018369</v>
       </c>
       <c r="CR267" s="134" t="n">
         <v>1.000000000039606</v>
@@ -52882,7 +52882,7 @@
         <v>1</v>
       </c>
       <c r="CW267" s="423" t="n">
-        <v>0.9999999999999999</v>
+        <v>1</v>
       </c>
       <c r="CX267" s="424" t="n">
         <v>1</v>
@@ -52894,10 +52894,10 @@
         <v>1.00000000000016</v>
       </c>
       <c r="DA267" s="133" t="n">
-        <v>0.999999999999166</v>
+        <v>0.9999999999991662</v>
       </c>
       <c r="DB267" s="133" t="n">
-        <v>0.9999999999995819</v>
+        <v>0.9999999999995822</v>
       </c>
       <c r="DC267" s="134" t="n">
         <v>1.000000000000172</v>
@@ -52918,19 +52918,19 @@
         <v>0</v>
       </c>
       <c r="DK267" s="419" t="n">
-        <v>4415.545846790802</v>
+        <v>4415.545846790801</v>
       </c>
       <c r="DL267" s="420" t="n">
-        <v>4762.243435281963</v>
+        <v>4762.243435281962</v>
       </c>
       <c r="DM267" s="420" t="n">
-        <v>5162.602074403597</v>
+        <v>5162.602074403596</v>
       </c>
       <c r="DN267" s="420" t="n">
-        <v>5542.300576433675</v>
+        <v>5542.300576433673</v>
       </c>
       <c r="DO267" s="421" t="n">
-        <v>5946.330721239719</v>
+        <v>5946.330721239717</v>
       </c>
     </row>
     <row r="268" ht="15.75" customHeight="1" thickBot="1">
@@ -53013,10 +53013,10 @@
         <v>2056602.927149346</v>
       </c>
       <c r="AL268" s="408" t="n">
-        <v>3634034.47108008</v>
+        <v>3634034.471080079</v>
       </c>
       <c r="AM268" s="408" t="n">
-        <v>4195401.33737352</v>
+        <v>4195401.337373521</v>
       </c>
       <c r="AN268" s="408" t="n">
         <v>4904903.359693628</v>
@@ -53025,7 +53025,7 @@
         <v>5759810.437132451</v>
       </c>
       <c r="AP268" s="436" t="n">
-        <v>1712.566138225669</v>
+        <v>1712.566138225668</v>
       </c>
       <c r="AQ268" s="437" t="n">
         <v>1594.384503961836</v>
@@ -53048,10 +53048,10 @@
         <v>2056602.927149346</v>
       </c>
       <c r="BC268" s="440" t="n">
-        <v>3634034.47108008</v>
+        <v>3634034.471080079</v>
       </c>
       <c r="BD268" s="440" t="n">
-        <v>4195401.33737352</v>
+        <v>4195401.337373521</v>
       </c>
       <c r="BE268" s="440" t="n">
         <v>4904903.359693628</v>
@@ -53060,7 +53060,7 @@
         <v>5759810.437132451</v>
       </c>
       <c r="BG268" s="442" t="n">
-        <v>1712.566138225669</v>
+        <v>1712.566138225668</v>
       </c>
       <c r="BH268" s="443" t="n">
         <v>1594.384503961836</v>
@@ -53080,7 +53080,7 @@
         </is>
       </c>
       <c r="BS268" s="439" t="n">
-        <v>2050763.4550485</v>
+        <v>2050763.455048499</v>
       </c>
       <c r="BT268" s="440" t="n">
         <v>3643724.806317749</v>
@@ -53095,13 +53095,13 @@
         <v>5795026.489547679</v>
       </c>
       <c r="BX268" s="442" t="n">
-        <v>1714.363444987201</v>
+        <v>1714.3634449872</v>
       </c>
       <c r="BY268" s="443" t="n">
-        <v>1594.095642603189</v>
+        <v>1594.095642603188</v>
       </c>
       <c r="BZ268" s="443" t="n">
-        <v>1602.311660747275</v>
+        <v>1602.311660747276</v>
       </c>
       <c r="CA268" s="443" t="n">
         <v>1606.153626924151</v>
@@ -53125,13 +53125,13 @@
         <v>0</v>
       </c>
       <c r="DK268" s="439" t="n">
-        <v>414274.0719448322</v>
+        <v>414274.071944832</v>
       </c>
       <c r="DL268" s="440" t="n">
         <v>185369.1882893562</v>
       </c>
       <c r="DM268" s="440" t="n">
-        <v>213077.5907856046</v>
+        <v>213077.5907856045</v>
       </c>
       <c r="DN268" s="440" t="n">
         <v>244468.1330573338</v>
@@ -54159,31 +54159,31 @@
         <v>0</v>
       </c>
       <c r="BX276" s="197" t="n">
-        <v>23.94490471180374</v>
+        <v>23.94490471180377</v>
       </c>
       <c r="BY276" s="190" t="n">
-        <v>17.77149025158941</v>
+        <v>17.7714902515894</v>
       </c>
       <c r="BZ276" s="190" t="n">
         <v>17.53795164492138</v>
       </c>
       <c r="CA276" s="190" t="n">
-        <v>17.291081220829</v>
+        <v>17.29108122082901</v>
       </c>
       <c r="CB276" s="198" t="n">
         <v>17.0569220667346</v>
       </c>
       <c r="CC276" s="199" t="n">
-        <v>23.94490471180374</v>
+        <v>23.94490471180377</v>
       </c>
       <c r="CD276" s="200" t="n">
-        <v>17.77149025158941</v>
+        <v>17.7714902515894</v>
       </c>
       <c r="CE276" s="200" t="n">
         <v>17.53795164492138</v>
       </c>
       <c r="CF276" s="200" t="n">
-        <v>17.291081220829</v>
+        <v>17.29108122082901</v>
       </c>
       <c r="CG276" s="201" t="n">
         <v>17.0569220667346</v>
@@ -54348,7 +54348,7 @@
         <v>12.73687464503732</v>
       </c>
       <c r="AS277" s="179" t="n">
-        <v>12.16639487087305</v>
+        <v>12.16639487087306</v>
       </c>
       <c r="AT277" s="195" t="n">
         <v>11.62360359172802</v>
@@ -54363,7 +54363,7 @@
         <v>12.73687464503732</v>
       </c>
       <c r="AX277" s="190" t="n">
-        <v>12.16639487087305</v>
+        <v>12.16639487087306</v>
       </c>
       <c r="AY277" s="196" t="n">
         <v>11.62360359172802</v>
@@ -54398,7 +54398,7 @@
         <v>12.73687464503732</v>
       </c>
       <c r="BJ277" s="190" t="n">
-        <v>12.16639487087305</v>
+        <v>12.16639487087306</v>
       </c>
       <c r="BK277" s="198" t="n">
         <v>11.62360359172802</v>
@@ -54413,7 +54413,7 @@
         <v>12.73687464503732</v>
       </c>
       <c r="BO277" s="190" t="n">
-        <v>12.16639487087305</v>
+        <v>12.16639487087306</v>
       </c>
       <c r="BP277" s="198" t="n">
         <v>11.62360359172802</v>
@@ -54619,10 +54619,10 @@
         <v>0</v>
       </c>
       <c r="AP278" s="194" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="AQ278" s="179" t="n">
-        <v>80.37340786516276</v>
+        <v>80.37340786516278</v>
       </c>
       <c r="AR278" s="179" t="n">
         <v>80.40871203656</v>
@@ -54631,13 +54631,13 @@
         <v>81.20637098159588</v>
       </c>
       <c r="AT278" s="195" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="AU278" s="190" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="AV278" s="190" t="n">
-        <v>80.37340786516276</v>
+        <v>80.37340786516278</v>
       </c>
       <c r="AW278" s="190" t="n">
         <v>80.40871203656</v>
@@ -54646,7 +54646,7 @@
         <v>81.20637098159588</v>
       </c>
       <c r="AY278" s="196" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BA278" s="111" t="inlineStr">
         <is>
@@ -54669,10 +54669,10 @@
         <v>0</v>
       </c>
       <c r="BG278" s="197" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="BH278" s="190" t="n">
-        <v>80.37340786516276</v>
+        <v>80.37340786516278</v>
       </c>
       <c r="BI278" s="190" t="n">
         <v>80.40871203656</v>
@@ -54681,13 +54681,13 @@
         <v>81.20637098159588</v>
       </c>
       <c r="BK278" s="198" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BL278" s="197" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="BM278" s="190" t="n">
-        <v>80.37340786516276</v>
+        <v>80.37340786516278</v>
       </c>
       <c r="BN278" s="190" t="n">
         <v>80.40871203656</v>
@@ -54696,7 +54696,7 @@
         <v>81.20637098159588</v>
       </c>
       <c r="BP278" s="198" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BR278" s="111" t="inlineStr">
         <is>
@@ -54719,10 +54719,10 @@
         <v>0</v>
       </c>
       <c r="BX278" s="197" t="n">
-        <v>81.16527501751209</v>
+        <v>81.1652750175121</v>
       </c>
       <c r="BY278" s="190" t="n">
-        <v>80.44913402647921</v>
+        <v>80.44913402647923</v>
       </c>
       <c r="BZ278" s="190" t="n">
         <v>80.48396132297766</v>
@@ -54731,13 +54731,13 @@
         <v>81.28160965353055</v>
       </c>
       <c r="CB278" s="198" t="n">
-        <v>83.424841930694</v>
+        <v>83.42484193069399</v>
       </c>
       <c r="CC278" s="197" t="n">
-        <v>81.16527501751209</v>
+        <v>81.1652750175121</v>
       </c>
       <c r="CD278" s="190" t="n">
-        <v>80.44913402647921</v>
+        <v>80.44913402647923</v>
       </c>
       <c r="CE278" s="190" t="n">
         <v>80.48396132297766</v>
@@ -54746,7 +54746,7 @@
         <v>81.28160965353055</v>
       </c>
       <c r="CG278" s="198" t="n">
-        <v>83.424841930694</v>
+        <v>83.42484193069399</v>
       </c>
       <c r="CI278" s="197" t="n">
         <v>0</v>
@@ -55197,7 +55197,7 @@
         <v>139.8581946663784</v>
       </c>
       <c r="AV280" s="207" t="n">
-        <v>140.5583731904682</v>
+        <v>140.5583731904683</v>
       </c>
       <c r="AW280" s="207" t="n">
         <v>140.8497154288177</v>
@@ -55206,7 +55206,7 @@
         <v>141.6497440296129</v>
       </c>
       <c r="AY280" s="208" t="n">
-        <v>143.9115807488388</v>
+        <v>143.9115807488387</v>
       </c>
       <c r="BA280" s="155" t="inlineStr">
         <is>
@@ -55247,7 +55247,7 @@
         <v>139.8581946663784</v>
       </c>
       <c r="BM280" s="222" t="n">
-        <v>140.5583731904682</v>
+        <v>140.5583731904683</v>
       </c>
       <c r="BN280" s="222" t="n">
         <v>140.8497154288177</v>
@@ -55256,7 +55256,7 @@
         <v>141.6497440296129</v>
       </c>
       <c r="BP280" s="214" t="n">
-        <v>143.9115807488388</v>
+        <v>143.9115807488387</v>
       </c>
       <c r="BR280" s="155" t="inlineStr">
         <is>
@@ -58406,31 +58406,31 @@
         <v>0</v>
       </c>
       <c r="BX294" s="197" t="n">
-        <v>23.94490471180374</v>
+        <v>23.94490471180377</v>
       </c>
       <c r="BY294" s="190" t="n">
-        <v>17.77149025158941</v>
+        <v>17.7714902515894</v>
       </c>
       <c r="BZ294" s="190" t="n">
         <v>17.53795164492138</v>
       </c>
       <c r="CA294" s="190" t="n">
-        <v>17.291081220829</v>
+        <v>17.29108122082901</v>
       </c>
       <c r="CB294" s="198" t="n">
         <v>17.0569220667346</v>
       </c>
       <c r="CC294" s="199" t="n">
-        <v>23.94490471180374</v>
+        <v>23.94490471180377</v>
       </c>
       <c r="CD294" s="200" t="n">
-        <v>17.77149025158941</v>
+        <v>17.7714902515894</v>
       </c>
       <c r="CE294" s="200" t="n">
         <v>17.53795164492138</v>
       </c>
       <c r="CF294" s="200" t="n">
-        <v>17.291081220829</v>
+        <v>17.29108122082901</v>
       </c>
       <c r="CG294" s="201" t="n">
         <v>17.0569220667346</v>
@@ -58463,19 +58463,19 @@
         <v>500</v>
       </c>
       <c r="CW294" s="199" t="n">
-        <v>6.492663762398208</v>
+        <v>6.492663762398237</v>
       </c>
       <c r="CX294" s="200" t="n">
-        <v>0.5582212223740151</v>
+        <v>0.5582212223740172</v>
       </c>
       <c r="CY294" s="200" t="n">
-        <v>0.5560499977934462</v>
+        <v>0.5560499977934482</v>
       </c>
       <c r="CZ294" s="200" t="n">
-        <v>0.5496802400906827</v>
+        <v>0.5496802400906847</v>
       </c>
       <c r="DA294" s="201" t="n">
-        <v>0.5365263753544431</v>
+        <v>0.5365263753544449</v>
       </c>
     </row>
     <row r="295">
@@ -58610,7 +58610,7 @@
         <v>12.73687464503732</v>
       </c>
       <c r="AS295" s="179" t="n">
-        <v>12.16639487087305</v>
+        <v>12.16639487087306</v>
       </c>
       <c r="AT295" s="195" t="n">
         <v>11.62360359172802</v>
@@ -58625,7 +58625,7 @@
         <v>12.73687464503732</v>
       </c>
       <c r="AX295" s="190" t="n">
-        <v>12.16639487087305</v>
+        <v>12.16639487087306</v>
       </c>
       <c r="AY295" s="196" t="n">
         <v>11.62360359172802</v>
@@ -58660,7 +58660,7 @@
         <v>12.73687464503732</v>
       </c>
       <c r="BJ295" s="190" t="n">
-        <v>12.16639487087305</v>
+        <v>12.16639487087306</v>
       </c>
       <c r="BK295" s="198" t="n">
         <v>11.62360359172802</v>
@@ -58675,7 +58675,7 @@
         <v>12.73687464503732</v>
       </c>
       <c r="BO295" s="190" t="n">
-        <v>12.16639487087305</v>
+        <v>12.16639487087306</v>
       </c>
       <c r="BP295" s="198" t="n">
         <v>11.62360359172802</v>
@@ -58710,7 +58710,7 @@
         <v>12.81966845609585</v>
       </c>
       <c r="CA295" s="190" t="n">
-        <v>12.25148723921788</v>
+        <v>12.25148723921789</v>
       </c>
       <c r="CB295" s="198" t="n">
         <v>11.69771037200386</v>
@@ -58725,7 +58725,7 @@
         <v>12.81966845609585</v>
       </c>
       <c r="CF295" s="190" t="n">
-        <v>12.25148723921788</v>
+        <v>12.25148723921789</v>
       </c>
       <c r="CG295" s="198" t="n">
         <v>11.69771037200386</v>
@@ -58758,19 +58758,19 @@
         <v>1332</v>
       </c>
       <c r="CW295" s="197" t="n">
-        <v>0.4056209815029398</v>
+        <v>0.4056209815029409</v>
       </c>
       <c r="CX295" s="190" t="n">
-        <v>0.08078411315871847</v>
+        <v>0.08078411315871883</v>
       </c>
       <c r="CY295" s="190" t="n">
-        <v>0.08279381105852547</v>
+        <v>0.08279381105852586</v>
       </c>
       <c r="CZ295" s="190" t="n">
-        <v>0.08509236834482972</v>
+        <v>0.08509236834483014</v>
       </c>
       <c r="DA295" s="198" t="n">
-        <v>0.07410678027584618</v>
+        <v>0.07410678027584662</v>
       </c>
     </row>
     <row r="296">
@@ -58896,10 +58896,10 @@
         <v>0</v>
       </c>
       <c r="AP296" s="194" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="AQ296" s="179" t="n">
-        <v>80.37340786516276</v>
+        <v>80.37340786516278</v>
       </c>
       <c r="AR296" s="179" t="n">
         <v>80.40871203656</v>
@@ -58908,13 +58908,13 @@
         <v>81.20637098159588</v>
       </c>
       <c r="AT296" s="195" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="AU296" s="190" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="AV296" s="190" t="n">
-        <v>80.37340786516276</v>
+        <v>80.37340786516278</v>
       </c>
       <c r="AW296" s="190" t="n">
         <v>80.40871203656</v>
@@ -58923,7 +58923,7 @@
         <v>81.20637098159588</v>
       </c>
       <c r="AY296" s="196" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BA296" s="111" t="inlineStr">
         <is>
@@ -58946,10 +58946,10 @@
         <v>0</v>
       </c>
       <c r="BG296" s="197" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="BH296" s="190" t="n">
-        <v>80.37340786516276</v>
+        <v>80.37340786516278</v>
       </c>
       <c r="BI296" s="190" t="n">
         <v>80.40871203656</v>
@@ -58958,13 +58958,13 @@
         <v>81.20637098159588</v>
       </c>
       <c r="BK296" s="198" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BL296" s="197" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="BM296" s="190" t="n">
-        <v>80.37340786516276</v>
+        <v>80.37340786516278</v>
       </c>
       <c r="BN296" s="190" t="n">
         <v>80.40871203656</v>
@@ -58973,7 +58973,7 @@
         <v>81.20637098159588</v>
       </c>
       <c r="BP296" s="198" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BR296" s="111" t="inlineStr">
         <is>
@@ -58996,10 +58996,10 @@
         <v>0</v>
       </c>
       <c r="BX296" s="197" t="n">
-        <v>81.16527501751209</v>
+        <v>81.1652750175121</v>
       </c>
       <c r="BY296" s="190" t="n">
-        <v>80.44913402647921</v>
+        <v>80.44913402647923</v>
       </c>
       <c r="BZ296" s="190" t="n">
         <v>80.48396132297768</v>
@@ -59008,13 +59008,13 @@
         <v>81.28160965353057</v>
       </c>
       <c r="CB296" s="198" t="n">
-        <v>83.424841930694</v>
+        <v>83.42484193069399</v>
       </c>
       <c r="CC296" s="197" t="n">
-        <v>81.16527501751209</v>
+        <v>81.1652750175121</v>
       </c>
       <c r="CD296" s="190" t="n">
-        <v>80.44913402647921</v>
+        <v>80.44913402647923</v>
       </c>
       <c r="CE296" s="190" t="n">
         <v>80.48396132297768</v>
@@ -59023,7 +59023,7 @@
         <v>81.28160965353057</v>
       </c>
       <c r="CG296" s="198" t="n">
-        <v>83.424841930694</v>
+        <v>83.42484193069399</v>
       </c>
       <c r="CI296" s="197" t="n">
         <v>0</v>
@@ -59053,19 +59053,19 @@
         <v>7464</v>
       </c>
       <c r="CW296" s="197" t="n">
-        <v>0.2641001573490654</v>
+        <v>0.2641001573490691</v>
       </c>
       <c r="CX296" s="190" t="n">
-        <v>0.07572616131645396</v>
+        <v>0.07572616131645603</v>
       </c>
       <c r="CY296" s="190" t="n">
-        <v>0.07524928641767235</v>
+        <v>0.07524928641767459</v>
       </c>
       <c r="CZ296" s="190" t="n">
-        <v>0.07523867193468156</v>
+        <v>0.07523867193468403</v>
       </c>
       <c r="DA296" s="198" t="n">
-        <v>0.07472975862258897</v>
+        <v>0.07472975862259144</v>
       </c>
     </row>
     <row r="297" ht="15.75" customHeight="1" thickBot="1">
@@ -59348,19 +59348,19 @@
         <v>1590</v>
       </c>
       <c r="CW297" s="211" t="n">
-        <v>0.00623418106180267</v>
+        <v>0.006234181061802625</v>
       </c>
       <c r="CX297" s="212" t="n">
-        <v>0.006396145085788303</v>
+        <v>0.006396145085788256</v>
       </c>
       <c r="CY297" s="212" t="n">
-        <v>0.006590523934945408</v>
+        <v>0.006590523934945361</v>
       </c>
       <c r="CZ297" s="212" t="n">
-        <v>0.006724179760346102</v>
+        <v>0.006724179760346054</v>
       </c>
       <c r="DA297" s="213" t="n">
-        <v>0.006860546125885922</v>
+        <v>0.006860546125885872</v>
       </c>
     </row>
     <row r="298" ht="15.75" customHeight="1" thickBot="1">
@@ -59504,7 +59504,7 @@
         <v>139.8581946663784</v>
       </c>
       <c r="AV298" s="207" t="n">
-        <v>140.5583731904682</v>
+        <v>140.5583731904683</v>
       </c>
       <c r="AW298" s="207" t="n">
         <v>140.8497154288177</v>
@@ -59513,7 +59513,7 @@
         <v>141.6497440296129</v>
       </c>
       <c r="AY298" s="208" t="n">
-        <v>143.9115807488388</v>
+        <v>143.9115807488387</v>
       </c>
       <c r="BA298" s="155" t="inlineStr">
         <is>
@@ -59554,7 +59554,7 @@
         <v>139.8581946663784</v>
       </c>
       <c r="BM298" s="222" t="n">
-        <v>140.5583731904682</v>
+        <v>140.5583731904683</v>
       </c>
       <c r="BN298" s="222" t="n">
         <v>140.8497154288177</v>
@@ -59563,7 +59563,7 @@
         <v>141.6497440296129</v>
       </c>
       <c r="BP298" s="214" t="n">
-        <v>143.9115807488388</v>
+        <v>143.9115807488387</v>
       </c>
       <c r="BR298" s="155" t="inlineStr">
         <is>
@@ -59643,19 +59643,19 @@
         <v>10886</v>
       </c>
       <c r="CW298" s="211" t="n">
-        <v>7.168619082312016</v>
+        <v>7.16861908231205</v>
       </c>
       <c r="CX298" s="212" t="n">
-        <v>0.7211276419349758</v>
+        <v>0.7211276419349804</v>
       </c>
       <c r="CY298" s="212" t="n">
-        <v>0.7206836192045895</v>
+        <v>0.720683619204594</v>
       </c>
       <c r="CZ298" s="212" t="n">
-        <v>0.7167354601305401</v>
+        <v>0.7167354601305449</v>
       </c>
       <c r="DA298" s="213" t="n">
-        <v>0.6922234603787643</v>
+        <v>0.6922234603787689</v>
       </c>
     </row>
     <row r="299" ht="15.75" customHeight="1" thickBot="1">
@@ -60522,34 +60522,34 @@
         <v>0</v>
       </c>
       <c r="BX303" s="462" t="n">
-        <v>-0.592419182931192</v>
+        <v>-0.5924191829311962</v>
       </c>
       <c r="BY303" s="463" t="n">
-        <v>-0.0335166388501578</v>
+        <v>-0.03351663885015793</v>
       </c>
       <c r="BZ303" s="463" t="n">
-        <v>-0.03385212588450325</v>
+        <v>-0.03385212588450337</v>
       </c>
       <c r="CA303" s="463" t="n">
-        <v>-0.03394822878279808</v>
+        <v>-0.0339482287827982</v>
       </c>
       <c r="CB303" s="464" t="n">
-        <v>-0.03356673936369789</v>
+        <v>-0.03356673936369799</v>
       </c>
       <c r="CC303" s="199" t="n">
-        <v>-14.18542088473202</v>
+        <v>-14.18542088473214</v>
       </c>
       <c r="CD303" s="200" t="n">
-        <v>-0.595640620591622</v>
+        <v>-0.5956406205916243</v>
       </c>
       <c r="CE303" s="200" t="n">
-        <v>-0.5936969468402092</v>
+        <v>-0.5936969468402115</v>
       </c>
       <c r="CF303" s="200" t="n">
-        <v>-0.5870015811866466</v>
+        <v>-0.5870015811866487</v>
       </c>
       <c r="CG303" s="201" t="n">
-        <v>-0.5725452573609875</v>
+        <v>-0.5725452573609894</v>
       </c>
     </row>
     <row r="304">
@@ -60698,7 +60698,7 @@
         <v>12.73687464503732</v>
       </c>
       <c r="AX304" s="190" t="n">
-        <v>12.16639487087305</v>
+        <v>12.16639487087306</v>
       </c>
       <c r="AY304" s="196" t="n">
         <v>11.62360359172802</v>
@@ -60748,7 +60748,7 @@
         <v>12.73687464503732</v>
       </c>
       <c r="BO304" s="190" t="n">
-        <v>12.16639487087305</v>
+        <v>12.16639487087306</v>
       </c>
       <c r="BP304" s="198" t="n">
         <v>11.62360359172802</v>
@@ -60774,34 +60774,34 @@
         <v>0</v>
       </c>
       <c r="BX304" s="462" t="n">
-        <v>-0.03016497231113222</v>
+        <v>-0.0301649723111323</v>
       </c>
       <c r="BY304" s="463" t="n">
-        <v>-0.006113542727863165</v>
+        <v>-0.006113542727863194</v>
       </c>
       <c r="BZ304" s="463" t="n">
-        <v>-0.006542854605148969</v>
+        <v>-0.006542854605148999</v>
       </c>
       <c r="CA304" s="463" t="n">
-        <v>-0.007043310795919782</v>
+        <v>-0.007043310795919816</v>
       </c>
       <c r="CB304" s="464" t="n">
-        <v>-0.006416450992251358</v>
+        <v>-0.006416450992251396</v>
       </c>
       <c r="CC304" s="197" t="n">
-        <v>-0.4300920728546407</v>
+        <v>-0.4300920728546419</v>
       </c>
       <c r="CD304" s="190" t="n">
-        <v>-0.08177186741377519</v>
+        <v>-0.08177186741377557</v>
       </c>
       <c r="CE304" s="190" t="n">
-        <v>-0.08387722679444969</v>
+        <v>-0.08387722679445007</v>
       </c>
       <c r="CF304" s="190" t="n">
-        <v>-0.08629103233805677</v>
+        <v>-0.0862910323380572</v>
       </c>
       <c r="CG304" s="198" t="n">
-        <v>-0.07505778532351319</v>
+        <v>-0.07505778532351363</v>
       </c>
     </row>
     <row r="305">
@@ -60941,10 +60941,10 @@
         <v>0</v>
       </c>
       <c r="AU305" s="190" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="AV305" s="190" t="n">
-        <v>80.37340786516276</v>
+        <v>80.37340786516278</v>
       </c>
       <c r="AW305" s="190" t="n">
         <v>80.40871203656</v>
@@ -60953,7 +60953,7 @@
         <v>81.20637098159588</v>
       </c>
       <c r="AY305" s="196" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BA305" s="111" t="inlineStr">
         <is>
@@ -60991,10 +60991,10 @@
         <v>0</v>
       </c>
       <c r="BL305" s="197" t="n">
-        <v>80.90117486016302</v>
+        <v>80.90117486016304</v>
       </c>
       <c r="BM305" s="190" t="n">
-        <v>80.37340786516276</v>
+        <v>80.37340786516278</v>
       </c>
       <c r="BN305" s="190" t="n">
         <v>80.40871203656</v>
@@ -61003,7 +61003,7 @@
         <v>81.20637098159588</v>
       </c>
       <c r="BP305" s="198" t="n">
-        <v>83.35011217207141</v>
+        <v>83.35011217207139</v>
       </c>
       <c r="BR305" s="111" t="inlineStr">
         <is>
@@ -61026,13 +61026,13 @@
         <v>15.05560425447307</v>
       </c>
       <c r="BX305" s="462" t="n">
-        <v>0.04532650984064247</v>
+        <v>0.04532650984064242</v>
       </c>
       <c r="BY305" s="463" t="n">
-        <v>0.06738687802945442</v>
+        <v>0.06738687802945438</v>
       </c>
       <c r="BZ305" s="463" t="n">
-        <v>0.09468260417601566</v>
+        <v>0.09468260417601564</v>
       </c>
       <c r="CA305" s="463" t="n">
         <v>0.1316235095328876</v>
@@ -61041,13 +61041,13 @@
         <v>0.1798955953329985</v>
       </c>
       <c r="CC305" s="197" t="n">
-        <v>3.678938636799714</v>
+        <v>3.67893863679971</v>
       </c>
       <c r="CD305" s="190" t="n">
-        <v>5.421215982217586</v>
+        <v>5.421215982217584</v>
       </c>
       <c r="CE305" s="190" t="n">
-        <v>7.62043105246125</v>
+        <v>7.620431052461247</v>
       </c>
       <c r="CF305" s="190" t="n">
         <v>10.69857072307993</v>
@@ -61202,7 +61202,7 @@
         <v>17.25272604828146</v>
       </c>
       <c r="AX306" s="209" t="n">
-        <v>14.57745381771261</v>
+        <v>14.57745381771262</v>
       </c>
       <c r="AY306" s="210" t="n">
         <v>14.74666186186718</v>
@@ -61252,7 +61252,7 @@
         <v>17.25272604828146</v>
       </c>
       <c r="BO306" s="212" t="n">
-        <v>14.57745381771261</v>
+        <v>14.57745381771262</v>
       </c>
       <c r="BP306" s="213" t="n">
         <v>14.74666186186718</v>
@@ -61278,34 +61278,34 @@
         <v>0</v>
       </c>
       <c r="BX306" s="466" t="n">
-        <v>-0.0002801359022896189</v>
+        <v>-0.0002801359022896169</v>
       </c>
       <c r="BY306" s="467" t="n">
-        <v>-0.0002812193515633527</v>
+        <v>-0.0002812193515633506</v>
       </c>
       <c r="BZ306" s="467" t="n">
-        <v>-0.0003821449695580503</v>
+        <v>-0.0003821449695580476</v>
       </c>
       <c r="CA306" s="467" t="n">
-        <v>-0.0004614854525082726</v>
+        <v>-0.0004614854525082692</v>
       </c>
       <c r="CB306" s="468" t="n">
-        <v>-0.0004654435958074439</v>
+        <v>-0.0004654435958074405</v>
       </c>
       <c r="CC306" s="212" t="n">
-        <v>-0.00623767389767624</v>
+        <v>-0.006237673897676195</v>
       </c>
       <c r="CD306" s="212" t="n">
-        <v>-0.006399742525335365</v>
+        <v>-0.006399742525335316</v>
       </c>
       <c r="CE306" s="212" t="n">
-        <v>-0.006595561006082391</v>
+        <v>-0.006595561006082344</v>
       </c>
       <c r="CF306" s="212" t="n">
-        <v>-0.006730385982625002</v>
+        <v>-0.006730385982624953</v>
       </c>
       <c r="CG306" s="213" t="n">
-        <v>-0.006866932520401992</v>
+        <v>-0.006866932520401942</v>
       </c>
     </row>
     <row r="307" ht="15.75" customHeight="1" thickBot="1">
@@ -61457,7 +61457,7 @@
         <v>124.6916206509199</v>
       </c>
       <c r="AY307" s="208" t="n">
-        <v>126.2407733170468</v>
+        <v>126.2407733170467</v>
       </c>
       <c r="BA307" s="155" t="inlineStr">
         <is>
@@ -61507,7 +61507,7 @@
         <v>124.6916206509199</v>
       </c>
       <c r="BP307" s="214" t="n">
-        <v>126.2407733170468</v>
+        <v>126.2407733170467</v>
       </c>
       <c r="BR307" s="155" t="inlineStr">
         <is>
@@ -61530,34 +61530,34 @@
         <v>15.05560425447307</v>
       </c>
       <c r="BX307" s="466" t="n">
-        <v>-0.07726077117907064</v>
+        <v>-0.07726077117907147</v>
       </c>
       <c r="BY307" s="467" t="n">
-        <v>0.03526079893947398</v>
+        <v>0.03526079893947395</v>
       </c>
       <c r="BZ307" s="467" t="n">
-        <v>0.05414685943907789</v>
+        <v>0.05414685943907786</v>
       </c>
       <c r="CA307" s="467" t="n">
-        <v>0.07988740171907742</v>
+        <v>0.07988740171907738</v>
       </c>
       <c r="CB307" s="468" t="n">
         <v>0.1130777023617176</v>
       </c>
       <c r="CC307" s="212" t="n">
-        <v>-10.94281199468462</v>
+        <v>-10.94281199468474</v>
       </c>
       <c r="CD307" s="212" t="n">
-        <v>4.737403751686854</v>
+        <v>4.737403751686849</v>
       </c>
       <c r="CE307" s="212" t="n">
-        <v>6.936261317820508</v>
+        <v>6.936261317820503</v>
       </c>
       <c r="CF307" s="212" t="n">
         <v>10.0185477235726</v>
       </c>
       <c r="CG307" s="213" t="n">
-        <v>14.35329162947859</v>
+        <v>14.35329162947858</v>
       </c>
     </row>
     <row r="308" ht="15.75" customHeight="1" thickBot="1">
@@ -63087,7 +63087,7 @@
         <v>0.442428536053965</v>
       </c>
       <c r="AS315" s="490" t="n">
-        <v>0.5427457743385103</v>
+        <v>0.5427457743385102</v>
       </c>
       <c r="AT315" s="491" t="n">
         <v>0.5511013856670294</v>
@@ -63137,7 +63137,7 @@
         <v>0.442428536053965</v>
       </c>
       <c r="BJ315" s="467" t="n">
-        <v>0.5427457743385103</v>
+        <v>0.5427457743385102</v>
       </c>
       <c r="BK315" s="468" t="n">
         <v>0.5511013856670294</v>
@@ -63248,7 +63248,7 @@
         <v>0.1241408936973136</v>
       </c>
       <c r="M316" s="495" t="n">
-        <v>0.03855360841168162</v>
+        <v>0.03855360841168161</v>
       </c>
       <c r="N316" s="495" t="n">
         <v>0.04927652132790298</v>
@@ -63298,7 +63298,7 @@
         <v>0.1241408936973136</v>
       </c>
       <c r="AD316" s="498" t="n">
-        <v>0.03855360841168162</v>
+        <v>0.03855360841168161</v>
       </c>
       <c r="AE316" s="498" t="n">
         <v>0.04927652132790298</v>
@@ -63336,7 +63336,7 @@
         <v>0.03894904327765471</v>
       </c>
       <c r="AQ316" s="501" t="n">
-        <v>0.04990992972982684</v>
+        <v>0.04990992972982683</v>
       </c>
       <c r="AR316" s="501" t="n">
         <v>0.09650278609956181</v>
@@ -63351,7 +63351,7 @@
         <v>0.03855360841168162</v>
       </c>
       <c r="AV316" s="501" t="n">
-        <v>0.04927652132790297</v>
+        <v>0.04927652132790296</v>
       </c>
       <c r="AW316" s="501" t="n">
         <v>0.0956303036239939</v>
@@ -63386,7 +63386,7 @@
         <v>0.03894904327765471</v>
       </c>
       <c r="BH316" s="504" t="n">
-        <v>0.04990992972982684</v>
+        <v>0.04990992972982683</v>
       </c>
       <c r="BI316" s="504" t="n">
         <v>0.09650278609956181</v>
@@ -63401,7 +63401,7 @@
         <v>0.03855360841168162</v>
       </c>
       <c r="BM316" s="504" t="n">
-        <v>0.04927652132790297</v>
+        <v>0.04927652132790296</v>
       </c>
       <c r="BN316" s="504" t="n">
         <v>0.0956303036239939</v>
@@ -63433,7 +63433,7 @@
         <v>0</v>
       </c>
       <c r="BX316" s="503" t="n">
-        <v>0.03667384154531689</v>
+        <v>0.03667384154531688</v>
       </c>
       <c r="BY316" s="504" t="n">
         <v>0.04902500103360277</v>
@@ -63445,7 +63445,7 @@
         <v>0.1191159846016613</v>
       </c>
       <c r="CB316" s="505" t="n">
-        <v>0.1222015390841674</v>
+        <v>0.1222015390841675</v>
       </c>
       <c r="CC316" s="492" t="n">
         <v>0</v>
@@ -64771,7 +64771,7 @@
         <v>321199.6701993461</v>
       </c>
       <c r="BV326" s="420" t="n">
-        <v>412577.7432856461</v>
+        <v>412577.743285646</v>
       </c>
       <c r="BW326" s="421" t="n">
         <v>446422.2989725422</v>
@@ -64966,7 +64966,7 @@
         <v>321199.6701993461</v>
       </c>
       <c r="BV327" s="440" t="n">
-        <v>412577.7432856461</v>
+        <v>412577.743285646</v>
       </c>
       <c r="BW327" s="441" t="n">
         <v>446422.2989725422</v>
@@ -67669,7 +67669,7 @@
         <v>321199.6701993461</v>
       </c>
       <c r="BV344" s="420" t="n">
-        <v>412577.7432856461</v>
+        <v>412577.743285646</v>
       </c>
       <c r="BW344" s="421" t="n">
         <v>446422.2989725422</v>
@@ -67864,7 +67864,7 @@
         <v>321199.6701993461</v>
       </c>
       <c r="BV345" s="440" t="n">
-        <v>412577.7432856461</v>
+        <v>412577.743285646</v>
       </c>
       <c r="BW345" s="441" t="n">
         <v>446422.2989725422</v>
@@ -68425,16 +68425,16 @@
         <v>3204.861308971688</v>
       </c>
       <c r="AL350" s="368" t="n">
-        <v>3254.321893974605</v>
+        <v>3254.321893974604</v>
       </c>
       <c r="AM350" s="368" t="n">
-        <v>3301.672431208349</v>
+        <v>3301.672431208348</v>
       </c>
       <c r="AN350" s="368" t="n">
-        <v>3345.010306312381</v>
+        <v>3345.010306312382</v>
       </c>
       <c r="AO350" s="380" t="n">
-        <v>3391.381220487523</v>
+        <v>3391.381220487522</v>
       </c>
       <c r="AP350" s="381" t="n">
         <v>183.6360911050139</v>
@@ -68449,7 +68449,7 @@
         <v>199.8046824253809</v>
       </c>
       <c r="AT350" s="382" t="n">
-        <v>205.2845030980126</v>
+        <v>205.2845030980125</v>
       </c>
       <c r="BA350" s="83" t="inlineStr">
         <is>
@@ -68460,16 +68460,16 @@
         <v>3204.861308971688</v>
       </c>
       <c r="BC350" s="375" t="n">
-        <v>3254.321893974605</v>
+        <v>3254.321893974604</v>
       </c>
       <c r="BD350" s="375" t="n">
-        <v>3301.672431208349</v>
+        <v>3301.672431208348</v>
       </c>
       <c r="BE350" s="375" t="n">
-        <v>3345.010306312381</v>
+        <v>3345.010306312382</v>
       </c>
       <c r="BF350" s="392" t="n">
-        <v>3391.381220487523</v>
+        <v>3391.381220487522</v>
       </c>
       <c r="BG350" s="386" t="n">
         <v>183.6360911050139</v>
@@ -68484,7 +68484,7 @@
         <v>199.8046824253809</v>
       </c>
       <c r="BK350" s="387" t="n">
-        <v>205.2845030980126</v>
+        <v>205.2845030980125</v>
       </c>
       <c r="BR350" s="83" t="inlineStr">
         <is>
@@ -68492,34 +68492,34 @@
         </is>
       </c>
       <c r="BS350" s="391" t="n">
-        <v>11005.84284323029</v>
+        <v>11005.84284323033</v>
       </c>
       <c r="BT350" s="375" t="n">
-        <v>3971.299184621568</v>
+        <v>3971.29918462157</v>
       </c>
       <c r="BU350" s="375" t="n">
-        <v>4027.73397970867</v>
+        <v>4027.733979708672</v>
       </c>
       <c r="BV350" s="375" t="n">
-        <v>4067.985565486489</v>
+        <v>4067.985565486492</v>
       </c>
       <c r="BW350" s="392" t="n">
-        <v>4100.881810478877</v>
+        <v>4100.881810478879</v>
       </c>
       <c r="BX350" s="386" t="n">
-        <v>459.6319332106141</v>
+        <v>459.6319332106149</v>
       </c>
       <c r="BY350" s="372" t="n">
-        <v>223.4646126126869</v>
+        <v>223.464612612687</v>
       </c>
       <c r="BZ350" s="372" t="n">
-        <v>229.658175666998</v>
+        <v>229.6581756669981</v>
       </c>
       <c r="CA350" s="372" t="n">
-        <v>235.2649619496411</v>
+        <v>235.2649619496412</v>
       </c>
       <c r="CB350" s="387" t="n">
-        <v>240.4233187227052</v>
+        <v>240.4233187227053</v>
       </c>
       <c r="CI350" s="225" t="n"/>
       <c r="CJ350" s="225" t="n"/>
@@ -68601,7 +68601,7 @@
         </is>
       </c>
       <c r="AK351" s="506" t="n">
-        <v>2074.032206997822</v>
+        <v>2074.032206997823</v>
       </c>
       <c r="AL351" s="368" t="n">
         <v>2111.869947368715</v>
@@ -68610,16 +68610,16 @@
         <v>2138.18030463691</v>
       </c>
       <c r="AN351" s="368" t="n">
-        <v>2149.491111393343</v>
+        <v>2149.491111393342</v>
       </c>
       <c r="AO351" s="380" t="n">
         <v>2160.882642602675</v>
       </c>
       <c r="AP351" s="381" t="n">
-        <v>149.7239363924464</v>
+        <v>149.7239363924465</v>
       </c>
       <c r="AQ351" s="372" t="n">
-        <v>158.8499803385697</v>
+        <v>158.8499803385698</v>
       </c>
       <c r="AR351" s="372" t="n">
         <v>167.8732314029652</v>
@@ -68636,7 +68636,7 @@
         </is>
       </c>
       <c r="BB351" s="391" t="n">
-        <v>2074.032206997822</v>
+        <v>2074.032206997823</v>
       </c>
       <c r="BC351" s="375" t="n">
         <v>2111.869947368715</v>
@@ -68645,16 +68645,16 @@
         <v>2138.18030463691</v>
       </c>
       <c r="BE351" s="375" t="n">
-        <v>2149.491111393343</v>
+        <v>2149.491111393342</v>
       </c>
       <c r="BF351" s="392" t="n">
         <v>2160.882642602675</v>
       </c>
       <c r="BG351" s="386" t="n">
-        <v>149.7239363924464</v>
+        <v>149.7239363924465</v>
       </c>
       <c r="BH351" s="372" t="n">
-        <v>158.8499803385697</v>
+        <v>158.8499803385698</v>
       </c>
       <c r="BI351" s="372" t="n">
         <v>167.8732314029652</v>
@@ -68671,34 +68671,34 @@
         </is>
       </c>
       <c r="BS351" s="391" t="n">
-        <v>3060.302267409852</v>
+        <v>3060.302267409855</v>
       </c>
       <c r="BT351" s="375" t="n">
-        <v>2343.584759410195</v>
+        <v>2343.584759410197</v>
       </c>
       <c r="BU351" s="375" t="n">
-        <v>2390.968356595467</v>
+        <v>2390.968356595468</v>
       </c>
       <c r="BV351" s="375" t="n">
-        <v>2420.33770774767</v>
+        <v>2420.337707747671</v>
       </c>
       <c r="BW351" s="392" t="n">
-        <v>2405.099486836619</v>
+        <v>2405.099486836621</v>
       </c>
       <c r="BX351" s="386" t="n">
-        <v>214.637606658035</v>
+        <v>214.6376066580352</v>
       </c>
       <c r="BY351" s="372" t="n">
-        <v>175.2143618113035</v>
+        <v>175.2143618113036</v>
       </c>
       <c r="BZ351" s="372" t="n">
-        <v>186.507815298339</v>
+        <v>186.5078152983391</v>
       </c>
       <c r="CA351" s="372" t="n">
         <v>197.5546038198527</v>
       </c>
       <c r="CB351" s="387" t="n">
-        <v>205.6042943747987</v>
+        <v>205.6042943747989</v>
       </c>
       <c r="CI351" s="225" t="n"/>
       <c r="CJ351" s="225" t="n"/>
@@ -68783,31 +68783,31 @@
         <v>30615.84446232376</v>
       </c>
       <c r="AL352" s="368" t="n">
-        <v>35394.85263249839</v>
+        <v>35394.8526324984</v>
       </c>
       <c r="AM352" s="368" t="n">
         <v>42128.44967839478</v>
       </c>
       <c r="AN352" s="368" t="n">
-        <v>51798.10656705894</v>
+        <v>51798.10656705895</v>
       </c>
       <c r="AO352" s="380" t="n">
         <v>65974.12315801576</v>
       </c>
       <c r="AP352" s="381" t="n">
-        <v>378.4351032632466</v>
+        <v>378.4351032632464</v>
       </c>
       <c r="AQ352" s="372" t="n">
-        <v>440.380140305585</v>
+        <v>440.3801403055851</v>
       </c>
       <c r="AR352" s="372" t="n">
-        <v>523.9289202796824</v>
+        <v>523.9289202796823</v>
       </c>
       <c r="AS352" s="372" t="n">
-        <v>637.8576697978308</v>
+        <v>637.8576697978309</v>
       </c>
       <c r="AT352" s="382" t="n">
-        <v>791.5301064240449</v>
+        <v>791.530106424045</v>
       </c>
       <c r="BA352" s="111" t="inlineStr">
         <is>
@@ -68818,31 +68818,31 @@
         <v>30615.84446232376</v>
       </c>
       <c r="BC352" s="375" t="n">
-        <v>35394.85263249839</v>
+        <v>35394.8526324984</v>
       </c>
       <c r="BD352" s="375" t="n">
         <v>42128.44967839478</v>
       </c>
       <c r="BE352" s="375" t="n">
-        <v>51798.10656705894</v>
+        <v>51798.10656705895</v>
       </c>
       <c r="BF352" s="392" t="n">
         <v>65974.12315801576</v>
       </c>
       <c r="BG352" s="386" t="n">
-        <v>378.4351032632466</v>
+        <v>378.4351032632464</v>
       </c>
       <c r="BH352" s="372" t="n">
-        <v>440.380140305585</v>
+        <v>440.3801403055851</v>
       </c>
       <c r="BI352" s="372" t="n">
-        <v>523.9289202796824</v>
+        <v>523.9289202796823</v>
       </c>
       <c r="BJ352" s="372" t="n">
-        <v>637.8576697978308</v>
+        <v>637.8576697978309</v>
       </c>
       <c r="BK352" s="387" t="n">
-        <v>791.5301064240449</v>
+        <v>791.530106424045</v>
       </c>
       <c r="BR352" s="111" t="inlineStr">
         <is>
@@ -68853,19 +68853,19 @@
         <v>31194.64853456656</v>
       </c>
       <c r="BT352" s="375" t="n">
-        <v>35577.50339943102</v>
+        <v>35577.50339943103</v>
       </c>
       <c r="BU352" s="375" t="n">
         <v>42320.33539807169</v>
       </c>
       <c r="BV352" s="375" t="n">
-        <v>52001.74829620225</v>
+        <v>52001.74829620226</v>
       </c>
       <c r="BW352" s="392" t="n">
         <v>66182.01770698407</v>
       </c>
       <c r="BX352" s="386" t="n">
-        <v>384.3349083439446</v>
+        <v>384.3349083439445</v>
       </c>
       <c r="BY352" s="372" t="n">
         <v>442.2360020397604</v>
@@ -68874,10 +68874,10 @@
         <v>525.8232162336361</v>
       </c>
       <c r="CA352" s="372" t="n">
-        <v>639.7726191430498</v>
+        <v>639.7726191430501</v>
       </c>
       <c r="CB352" s="387" t="n">
-        <v>793.3130728849978</v>
+        <v>793.313072884998</v>
       </c>
       <c r="CI352" s="225" t="n"/>
       <c r="CJ352" s="225" t="n"/>
@@ -68962,7 +68962,7 @@
         <v>391675.330177594</v>
       </c>
       <c r="AL353" s="408" t="n">
-        <v>416617.9124999696</v>
+        <v>416617.9124999697</v>
       </c>
       <c r="AM353" s="408" t="n">
         <v>314136.8067779624</v>
@@ -68977,10 +68977,10 @@
         <v>17639.01218549907</v>
       </c>
       <c r="AQ353" s="411" t="n">
-        <v>18384.2360227976</v>
+        <v>18384.23602279761</v>
       </c>
       <c r="AR353" s="411" t="n">
-        <v>18338.5752131058</v>
+        <v>18338.57521310579</v>
       </c>
       <c r="AS353" s="411" t="n">
         <v>17853.88837568331</v>
@@ -68997,7 +68997,7 @@
         <v>391675.330177594</v>
       </c>
       <c r="BC353" s="420" t="n">
-        <v>416617.9124999696</v>
+        <v>416617.9124999697</v>
       </c>
       <c r="BD353" s="420" t="n">
         <v>314136.8067779624</v>
@@ -69012,10 +69012,10 @@
         <v>17639.01218549907</v>
       </c>
       <c r="BH353" s="417" t="n">
-        <v>18384.2360227976</v>
+        <v>18384.23602279761</v>
       </c>
       <c r="BI353" s="417" t="n">
-        <v>18338.5752131058</v>
+        <v>18338.57521310579</v>
       </c>
       <c r="BJ353" s="417" t="n">
         <v>17853.88837568331</v>
@@ -69029,31 +69029,31 @@
         </is>
       </c>
       <c r="BS353" s="419" t="n">
-        <v>392870.6611876373</v>
+        <v>392870.6611876372</v>
       </c>
       <c r="BT353" s="420" t="n">
         <v>418457.6758984351</v>
       </c>
       <c r="BU353" s="420" t="n">
-        <v>316602.9484016792</v>
+        <v>316602.9484016791</v>
       </c>
       <c r="BV353" s="420" t="n">
-        <v>260487.9894193752</v>
+        <v>260487.9894193751</v>
       </c>
       <c r="BW353" s="421" t="n">
         <v>270025.4799898149</v>
       </c>
       <c r="BX353" s="416" t="n">
-        <v>17643.94531684612</v>
+        <v>17643.94531684611</v>
       </c>
       <c r="BY353" s="417" t="n">
-        <v>18387.98917409554</v>
+        <v>18387.98917409555</v>
       </c>
       <c r="BZ353" s="417" t="n">
-        <v>18343.88673948645</v>
+        <v>18343.88673948644</v>
       </c>
       <c r="CA353" s="417" t="n">
-        <v>17860.99905421551</v>
+        <v>17860.9990542155</v>
       </c>
       <c r="CB353" s="418" t="n">
         <v>18302.44144567959</v>
@@ -69138,16 +69138,16 @@
         </is>
       </c>
       <c r="AK354" s="435" t="n">
-        <v>427570.0681558873</v>
+        <v>427570.0681558872</v>
       </c>
       <c r="AL354" s="408" t="n">
-        <v>457378.9569738113</v>
+        <v>457378.9569738114</v>
       </c>
       <c r="AM354" s="408" t="n">
         <v>361705.1091922024</v>
       </c>
       <c r="AN354" s="408" t="n">
-        <v>314741.6778722474</v>
+        <v>314741.6778722473</v>
       </c>
       <c r="AO354" s="409" t="n">
         <v>337757.0494690707</v>
@@ -69162,7 +69162,7 @@
         <v>2842.312675205743</v>
       </c>
       <c r="AS354" s="437" t="n">
-        <v>2527.356565481375</v>
+        <v>2527.356565481374</v>
       </c>
       <c r="AT354" s="438" t="n">
         <v>2679.627516824331</v>
@@ -69173,16 +69173,16 @@
         </is>
       </c>
       <c r="BB354" s="439" t="n">
-        <v>427570.0681558873</v>
+        <v>427570.0681558872</v>
       </c>
       <c r="BC354" s="440" t="n">
-        <v>457378.9569738113</v>
+        <v>457378.9569738114</v>
       </c>
       <c r="BD354" s="440" t="n">
         <v>361705.1091922024</v>
       </c>
       <c r="BE354" s="440" t="n">
-        <v>314741.6778722474</v>
+        <v>314741.6778722473</v>
       </c>
       <c r="BF354" s="441" t="n">
         <v>337757.0494690707</v>
@@ -69197,7 +69197,7 @@
         <v>2842.312675205743</v>
       </c>
       <c r="BJ354" s="443" t="n">
-        <v>2527.356565481375</v>
+        <v>2527.356565481374</v>
       </c>
       <c r="BK354" s="444" t="n">
         <v>2679.627516824331</v>
@@ -69211,10 +69211,10 @@
         <v>438131.454832844</v>
       </c>
       <c r="BT354" s="440" t="n">
-        <v>460350.0632418978</v>
+        <v>460350.0632418979</v>
       </c>
       <c r="BU354" s="440" t="n">
-        <v>365341.9861360551</v>
+        <v>365341.986136055</v>
       </c>
       <c r="BV354" s="440" t="n">
         <v>318978.0609888115</v>
@@ -69223,19 +69223,19 @@
         <v>342713.4789941144</v>
       </c>
       <c r="BX354" s="442" t="n">
-        <v>3093.388983986586</v>
+        <v>3093.388983986584</v>
       </c>
       <c r="BY354" s="443" t="n">
         <v>3426.41494636526</v>
       </c>
       <c r="BZ354" s="443" t="n">
-        <v>2851.986144131951</v>
+        <v>2851.98614413195</v>
       </c>
       <c r="CA354" s="443" t="n">
-        <v>2543.515208080339</v>
+        <v>2543.515208080338</v>
       </c>
       <c r="CB354" s="444" t="n">
-        <v>2699.955785295573</v>
+        <v>2699.955785295574</v>
       </c>
       <c r="CI354" s="225" t="n"/>
       <c r="CJ354" s="225" t="n"/>
@@ -71116,16 +71116,16 @@
         <v>3204.861308971688</v>
       </c>
       <c r="AL368" s="368" t="n">
-        <v>3254.321893974605</v>
+        <v>3254.321893974604</v>
       </c>
       <c r="AM368" s="368" t="n">
-        <v>3301.672431208349</v>
+        <v>3301.672431208348</v>
       </c>
       <c r="AN368" s="368" t="n">
-        <v>3345.010306312381</v>
+        <v>3345.010306312382</v>
       </c>
       <c r="AO368" s="380" t="n">
-        <v>3391.381220487523</v>
+        <v>3391.381220487522</v>
       </c>
       <c r="AP368" s="381" t="n">
         <v>183.6360911050139</v>
@@ -71140,7 +71140,7 @@
         <v>199.8046824253809</v>
       </c>
       <c r="AT368" s="382" t="n">
-        <v>205.2845030980126</v>
+        <v>205.2845030980125</v>
       </c>
       <c r="BA368" s="83" t="inlineStr">
         <is>
@@ -71151,16 +71151,16 @@
         <v>3204.861308971688</v>
       </c>
       <c r="BC368" s="375" t="n">
-        <v>3254.321893974605</v>
+        <v>3254.321893974604</v>
       </c>
       <c r="BD368" s="375" t="n">
-        <v>3301.672431208349</v>
+        <v>3301.672431208348</v>
       </c>
       <c r="BE368" s="375" t="n">
-        <v>3345.010306312381</v>
+        <v>3345.010306312382</v>
       </c>
       <c r="BF368" s="392" t="n">
-        <v>3391.381220487523</v>
+        <v>3391.381220487522</v>
       </c>
       <c r="BG368" s="386" t="n">
         <v>183.6360911050139</v>
@@ -71175,7 +71175,7 @@
         <v>199.8046824253809</v>
       </c>
       <c r="BK368" s="387" t="n">
-        <v>205.2845030980126</v>
+        <v>205.2845030980125</v>
       </c>
       <c r="BR368" s="83" t="inlineStr">
         <is>
@@ -71183,49 +71183,49 @@
         </is>
       </c>
       <c r="BS368" s="391" t="n">
-        <v>11005.84284323029</v>
+        <v>11005.84284323033</v>
       </c>
       <c r="BT368" s="375" t="n">
-        <v>3971.299184621568</v>
+        <v>3971.29918462157</v>
       </c>
       <c r="BU368" s="375" t="n">
-        <v>4027.73397970867</v>
+        <v>4027.733979708672</v>
       </c>
       <c r="BV368" s="375" t="n">
-        <v>4067.985565486489</v>
+        <v>4067.985565486492</v>
       </c>
       <c r="BW368" s="392" t="n">
-        <v>4100.881810478877</v>
+        <v>4100.881810478879</v>
       </c>
       <c r="BX368" s="386" t="n">
-        <v>459.6319332106141</v>
+        <v>459.6319332106149</v>
       </c>
       <c r="BY368" s="372" t="n">
-        <v>223.4646126126869</v>
+        <v>223.464612612687</v>
       </c>
       <c r="BZ368" s="372" t="n">
-        <v>229.658175666998</v>
+        <v>229.6581756669981</v>
       </c>
       <c r="CA368" s="372" t="n">
-        <v>235.2649619496411</v>
+        <v>235.2649619496412</v>
       </c>
       <c r="CB368" s="387" t="n">
-        <v>240.4233187227052</v>
+        <v>240.4233187227053</v>
       </c>
       <c r="CW368" s="511" t="n">
-        <v>7800.981534258605</v>
+        <v>7800.981534258638</v>
       </c>
       <c r="CX368" s="512" t="n">
-        <v>716.977290646963</v>
+        <v>716.9772906469652</v>
       </c>
       <c r="CY368" s="512" t="n">
-        <v>726.0615485003209</v>
+        <v>726.0615485003239</v>
       </c>
       <c r="CZ368" s="512" t="n">
-        <v>722.9752591741083</v>
+        <v>722.9752591741109</v>
       </c>
       <c r="DA368" s="513" t="n">
-        <v>709.5005899913541</v>
+        <v>709.5005899913565</v>
       </c>
     </row>
     <row r="369">
@@ -71305,7 +71305,7 @@
         </is>
       </c>
       <c r="AK369" s="506" t="n">
-        <v>2074.032206997822</v>
+        <v>2074.032206997823</v>
       </c>
       <c r="AL369" s="368" t="n">
         <v>2111.869947368715</v>
@@ -71314,16 +71314,16 @@
         <v>2138.18030463691</v>
       </c>
       <c r="AN369" s="368" t="n">
-        <v>2149.491111393343</v>
+        <v>2149.491111393342</v>
       </c>
       <c r="AO369" s="380" t="n">
         <v>2160.882642602675</v>
       </c>
       <c r="AP369" s="381" t="n">
-        <v>149.7239363924464</v>
+        <v>149.7239363924465</v>
       </c>
       <c r="AQ369" s="372" t="n">
-        <v>158.8499803385697</v>
+        <v>158.8499803385698</v>
       </c>
       <c r="AR369" s="372" t="n">
         <v>167.8732314029652</v>
@@ -71340,7 +71340,7 @@
         </is>
       </c>
       <c r="BB369" s="391" t="n">
-        <v>2074.032206997822</v>
+        <v>2074.032206997823</v>
       </c>
       <c r="BC369" s="375" t="n">
         <v>2111.869947368715</v>
@@ -71349,16 +71349,16 @@
         <v>2138.18030463691</v>
       </c>
       <c r="BE369" s="375" t="n">
-        <v>2149.491111393343</v>
+        <v>2149.491111393342</v>
       </c>
       <c r="BF369" s="392" t="n">
         <v>2160.882642602675</v>
       </c>
       <c r="BG369" s="386" t="n">
-        <v>149.7239363924464</v>
+        <v>149.7239363924465</v>
       </c>
       <c r="BH369" s="372" t="n">
-        <v>158.8499803385697</v>
+        <v>158.8499803385698</v>
       </c>
       <c r="BI369" s="372" t="n">
         <v>167.8732314029652</v>
@@ -71375,49 +71375,49 @@
         </is>
       </c>
       <c r="BS369" s="391" t="n">
-        <v>3060.302267409852</v>
+        <v>3060.302267409855</v>
       </c>
       <c r="BT369" s="375" t="n">
-        <v>2343.584759410196</v>
+        <v>2343.584759410197</v>
       </c>
       <c r="BU369" s="375" t="n">
-        <v>2390.968356595467</v>
+        <v>2390.968356595468</v>
       </c>
       <c r="BV369" s="375" t="n">
-        <v>2420.33770774767</v>
+        <v>2420.337707747671</v>
       </c>
       <c r="BW369" s="392" t="n">
-        <v>2405.099486836619</v>
+        <v>2405.099486836621</v>
       </c>
       <c r="BX369" s="386" t="n">
-        <v>214.637606658035</v>
+        <v>214.6376066580352</v>
       </c>
       <c r="BY369" s="372" t="n">
-        <v>175.2143618113035</v>
+        <v>175.2143618113036</v>
       </c>
       <c r="BZ369" s="372" t="n">
-        <v>186.507815298339</v>
+        <v>186.5078152983391</v>
       </c>
       <c r="CA369" s="372" t="n">
         <v>197.5546038198527</v>
       </c>
       <c r="CB369" s="387" t="n">
-        <v>205.6042943747987</v>
+        <v>205.6042943747989</v>
       </c>
       <c r="CW369" s="391" t="n">
-        <v>986.2700604120295</v>
+        <v>986.2700604120316</v>
       </c>
       <c r="CX369" s="375" t="n">
-        <v>231.7148120414808</v>
+        <v>231.7148120414818</v>
       </c>
       <c r="CY369" s="375" t="n">
-        <v>252.7880519585568</v>
+        <v>252.788051958558</v>
       </c>
       <c r="CZ369" s="375" t="n">
-        <v>270.8465963543271</v>
+        <v>270.8465963543285</v>
       </c>
       <c r="DA369" s="392" t="n">
-        <v>244.2168442339436</v>
+        <v>244.216844233945</v>
       </c>
     </row>
     <row r="370">
@@ -71500,31 +71500,31 @@
         <v>30615.84446232376</v>
       </c>
       <c r="AL370" s="368" t="n">
-        <v>35394.85263249839</v>
+        <v>35394.8526324984</v>
       </c>
       <c r="AM370" s="368" t="n">
         <v>42128.44967839478</v>
       </c>
       <c r="AN370" s="368" t="n">
-        <v>51798.10656705894</v>
+        <v>51798.10656705895</v>
       </c>
       <c r="AO370" s="380" t="n">
         <v>65974.12315801576</v>
       </c>
       <c r="AP370" s="381" t="n">
-        <v>378.4351032632466</v>
+        <v>378.4351032632464</v>
       </c>
       <c r="AQ370" s="372" t="n">
-        <v>440.380140305585</v>
+        <v>440.3801403055851</v>
       </c>
       <c r="AR370" s="372" t="n">
-        <v>523.9289202796824</v>
+        <v>523.9289202796823</v>
       </c>
       <c r="AS370" s="372" t="n">
-        <v>637.8576697978308</v>
+        <v>637.8576697978309</v>
       </c>
       <c r="AT370" s="382" t="n">
-        <v>791.5301064240449</v>
+        <v>791.530106424045</v>
       </c>
       <c r="BA370" s="111" t="inlineStr">
         <is>
@@ -71535,31 +71535,31 @@
         <v>30615.84446232376</v>
       </c>
       <c r="BC370" s="375" t="n">
-        <v>35394.85263249839</v>
+        <v>35394.8526324984</v>
       </c>
       <c r="BD370" s="375" t="n">
         <v>42128.44967839478</v>
       </c>
       <c r="BE370" s="375" t="n">
-        <v>51798.10656705894</v>
+        <v>51798.10656705895</v>
       </c>
       <c r="BF370" s="392" t="n">
         <v>65974.12315801576</v>
       </c>
       <c r="BG370" s="386" t="n">
-        <v>378.4351032632466</v>
+        <v>378.4351032632464</v>
       </c>
       <c r="BH370" s="372" t="n">
-        <v>440.380140305585</v>
+        <v>440.3801403055851</v>
       </c>
       <c r="BI370" s="372" t="n">
-        <v>523.9289202796824</v>
+        <v>523.9289202796823</v>
       </c>
       <c r="BJ370" s="372" t="n">
-        <v>637.8576697978308</v>
+        <v>637.8576697978309</v>
       </c>
       <c r="BK370" s="387" t="n">
-        <v>791.5301064240449</v>
+        <v>791.530106424045</v>
       </c>
       <c r="BR370" s="111" t="inlineStr">
         <is>
@@ -71570,19 +71570,19 @@
         <v>31194.64853456656</v>
       </c>
       <c r="BT370" s="375" t="n">
-        <v>35577.50339943102</v>
+        <v>35577.50339943103</v>
       </c>
       <c r="BU370" s="375" t="n">
         <v>42320.3353980717</v>
       </c>
       <c r="BV370" s="375" t="n">
-        <v>52001.74829620226</v>
+        <v>52001.74829620227</v>
       </c>
       <c r="BW370" s="392" t="n">
         <v>66182.01770698407</v>
       </c>
       <c r="BX370" s="386" t="n">
-        <v>384.3349083439446</v>
+        <v>384.3349083439445</v>
       </c>
       <c r="BY370" s="372" t="n">
         <v>442.2360020397604</v>
@@ -71591,25 +71591,25 @@
         <v>525.8232162336361</v>
       </c>
       <c r="CA370" s="372" t="n">
-        <v>639.7726191430498</v>
+        <v>639.7726191430501</v>
       </c>
       <c r="CB370" s="387" t="n">
-        <v>793.3130728849978</v>
+        <v>793.313072884998</v>
       </c>
       <c r="CW370" s="391" t="n">
-        <v>578.804072242802</v>
+        <v>578.8040722428102</v>
       </c>
       <c r="CX370" s="375" t="n">
-        <v>182.6507669326291</v>
+        <v>182.6507669326341</v>
       </c>
       <c r="CY370" s="375" t="n">
-        <v>191.885719676917</v>
+        <v>191.8857196769227</v>
       </c>
       <c r="CZ370" s="375" t="n">
-        <v>203.6417291433183</v>
+        <v>203.641729143325</v>
       </c>
       <c r="DA370" s="392" t="n">
-        <v>207.8945489683034</v>
+        <v>207.8945489683101</v>
       </c>
     </row>
     <row r="371" ht="15.75" customHeight="1" thickBot="1">
@@ -71692,7 +71692,7 @@
         <v>391675.330177594</v>
       </c>
       <c r="AL371" s="408" t="n">
-        <v>416617.9124999696</v>
+        <v>416617.9124999697</v>
       </c>
       <c r="AM371" s="408" t="n">
         <v>314136.8067779624</v>
@@ -71707,10 +71707,10 @@
         <v>17639.01218549907</v>
       </c>
       <c r="AQ371" s="411" t="n">
-        <v>18384.2360227976</v>
+        <v>18384.23602279761</v>
       </c>
       <c r="AR371" s="411" t="n">
-        <v>18338.5752131058</v>
+        <v>18338.57521310579</v>
       </c>
       <c r="AS371" s="411" t="n">
         <v>17853.88837568331</v>
@@ -71727,7 +71727,7 @@
         <v>391675.330177594</v>
       </c>
       <c r="BC371" s="420" t="n">
-        <v>416617.9124999696</v>
+        <v>416617.9124999697</v>
       </c>
       <c r="BD371" s="420" t="n">
         <v>314136.8067779624</v>
@@ -71742,10 +71742,10 @@
         <v>17639.01218549907</v>
       </c>
       <c r="BH371" s="417" t="n">
-        <v>18384.2360227976</v>
+        <v>18384.23602279761</v>
       </c>
       <c r="BI371" s="417" t="n">
-        <v>18338.5752131058</v>
+        <v>18338.57521310579</v>
       </c>
       <c r="BJ371" s="417" t="n">
         <v>17853.88837568331</v>
@@ -71759,13 +71759,13 @@
         </is>
       </c>
       <c r="BS371" s="419" t="n">
-        <v>392870.6611876373</v>
+        <v>392870.6611876372</v>
       </c>
       <c r="BT371" s="420" t="n">
-        <v>418457.6758984351</v>
+        <v>418457.6758984353</v>
       </c>
       <c r="BU371" s="420" t="n">
-        <v>316602.9484016792</v>
+        <v>316602.9484016791</v>
       </c>
       <c r="BV371" s="420" t="n">
         <v>260487.9894193751</v>
@@ -71774,34 +71774,34 @@
         <v>270025.4799898149</v>
       </c>
       <c r="BX371" s="416" t="n">
-        <v>17643.94531684612</v>
+        <v>17643.94531684611</v>
       </c>
       <c r="BY371" s="417" t="n">
-        <v>18387.98917409554</v>
+        <v>18387.98917409555</v>
       </c>
       <c r="BZ371" s="417" t="n">
-        <v>18343.88673948645</v>
+        <v>18343.88673948644</v>
       </c>
       <c r="CA371" s="417" t="n">
-        <v>17860.99905421551</v>
+        <v>17860.9990542155</v>
       </c>
       <c r="CB371" s="418" t="n">
         <v>18302.44144567959</v>
       </c>
       <c r="CW371" s="419" t="n">
-        <v>219.8088549232851</v>
+        <v>219.8088549232836</v>
       </c>
       <c r="CX371" s="420" t="n">
-        <v>202.9991552983071</v>
+        <v>202.9991552983055</v>
       </c>
       <c r="CY371" s="420" t="n">
-        <v>212.5341341601032</v>
+        <v>212.5341341601017</v>
       </c>
       <c r="CZ371" s="420" t="n">
-        <v>223.7561562555321</v>
+        <v>223.7561562555306</v>
       </c>
       <c r="DA371" s="421" t="n">
-        <v>236.365981331564</v>
+        <v>236.3659813315624</v>
       </c>
     </row>
     <row r="372" ht="15.75" customHeight="1" thickBot="1">
@@ -71881,16 +71881,16 @@
         </is>
       </c>
       <c r="AK372" s="435" t="n">
-        <v>427570.0681558873</v>
+        <v>427570.0681558872</v>
       </c>
       <c r="AL372" s="408" t="n">
-        <v>457378.9569738113</v>
+        <v>457378.9569738114</v>
       </c>
       <c r="AM372" s="408" t="n">
         <v>361705.1091922024</v>
       </c>
       <c r="AN372" s="408" t="n">
-        <v>314741.6778722474</v>
+        <v>314741.6778722473</v>
       </c>
       <c r="AO372" s="409" t="n">
         <v>337757.0494690707</v>
@@ -71905,7 +71905,7 @@
         <v>2842.312675205743</v>
       </c>
       <c r="AS372" s="437" t="n">
-        <v>2527.356565481375</v>
+        <v>2527.356565481374</v>
       </c>
       <c r="AT372" s="438" t="n">
         <v>2679.627516824331</v>
@@ -71916,16 +71916,16 @@
         </is>
       </c>
       <c r="BB372" s="439" t="n">
-        <v>427570.0681558873</v>
+        <v>427570.0681558872</v>
       </c>
       <c r="BC372" s="440" t="n">
-        <v>457378.9569738113</v>
+        <v>457378.9569738114</v>
       </c>
       <c r="BD372" s="440" t="n">
         <v>361705.1091922024</v>
       </c>
       <c r="BE372" s="440" t="n">
-        <v>314741.6778722474</v>
+        <v>314741.6778722473</v>
       </c>
       <c r="BF372" s="441" t="n">
         <v>337757.0494690707</v>
@@ -71940,7 +71940,7 @@
         <v>2842.312675205743</v>
       </c>
       <c r="BJ372" s="443" t="n">
-        <v>2527.356565481375</v>
+        <v>2527.356565481374</v>
       </c>
       <c r="BK372" s="444" t="n">
         <v>2679.627516824331</v>
@@ -71954,10 +71954,10 @@
         <v>438131.454832844</v>
       </c>
       <c r="BT372" s="440" t="n">
-        <v>460350.0632418979</v>
+        <v>460350.0632418981</v>
       </c>
       <c r="BU372" s="440" t="n">
-        <v>365341.9861360551</v>
+        <v>365341.986136055</v>
       </c>
       <c r="BV372" s="440" t="n">
         <v>318978.0609888115</v>
@@ -71966,34 +71966,34 @@
         <v>342713.4789941144</v>
       </c>
       <c r="BX372" s="442" t="n">
-        <v>3093.388983986586</v>
+        <v>3093.388983986584</v>
       </c>
       <c r="BY372" s="443" t="n">
-        <v>3426.41494636526</v>
+        <v>3426.414946365262</v>
       </c>
       <c r="BZ372" s="443" t="n">
-        <v>2851.986144131951</v>
+        <v>2851.98614413195</v>
       </c>
       <c r="CA372" s="443" t="n">
         <v>2543.515208080338</v>
       </c>
       <c r="CB372" s="444" t="n">
-        <v>2699.955785295573</v>
+        <v>2699.955785295574</v>
       </c>
       <c r="CW372" s="419" t="n">
-        <v>9585.864521836722</v>
+        <v>9585.864521836764</v>
       </c>
       <c r="CX372" s="420" t="n">
-        <v>1334.34202491938</v>
+        <v>1334.342024919387</v>
       </c>
       <c r="CY372" s="420" t="n">
-        <v>1383.269454295898</v>
+        <v>1383.269454295906</v>
       </c>
       <c r="CZ372" s="420" t="n">
-        <v>1421.219740927286</v>
+        <v>1421.219740927295</v>
       </c>
       <c r="DA372" s="421" t="n">
-        <v>1397.977964525165</v>
+        <v>1397.977964525174</v>
       </c>
     </row>
     <row r="375">
